--- a/data/processed/panel_base.xlsx
+++ b/data/processed/panel_base.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="105">
   <si>
     <t>iso</t>
   </si>
@@ -110,9 +110,6 @@
   </si>
   <si>
     <t>ingreso_publico</t>
-  </si>
-  <si>
-    <t>embig</t>
   </si>
   <si>
     <t>ABW</t>
@@ -689,10 +686,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG307"/>
+  <dimension ref="A1:AF307"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -789,22 +786,19 @@
       <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:32">
+      <c r="A2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:33">
-      <c r="A2" t="s">
-        <v>33</v>
-      </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" t="s">
         <v>101</v>
-      </c>
-      <c r="D2" t="s">
-        <v>102</v>
       </c>
       <c r="E2">
         <v>2015</v>
@@ -864,18 +858,18 @@
         <v>52.32</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" t="s">
         <v>101</v>
-      </c>
-      <c r="D3" t="s">
-        <v>102</v>
       </c>
       <c r="E3">
         <v>2016</v>
@@ -935,18 +929,18 @@
         <v>43.64</v>
       </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" t="s">
         <v>101</v>
-      </c>
-      <c r="D4" t="s">
-        <v>102</v>
       </c>
       <c r="E4">
         <v>2017</v>
@@ -1006,18 +1000,18 @@
         <v>54.13</v>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" t="s">
         <v>101</v>
-      </c>
-      <c r="D5" t="s">
-        <v>102</v>
       </c>
       <c r="E5">
         <v>2018</v>
@@ -1077,18 +1071,18 @@
         <v>71.34</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" t="s">
         <v>101</v>
-      </c>
-      <c r="D6" t="s">
-        <v>102</v>
       </c>
       <c r="E6">
         <v>2019</v>
@@ -1148,18 +1142,18 @@
         <v>64.3</v>
       </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" t="s">
         <v>101</v>
-      </c>
-      <c r="D7" t="s">
-        <v>102</v>
       </c>
       <c r="E7">
         <v>2020</v>
@@ -1219,18 +1213,18 @@
         <v>41.96</v>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" t="s">
         <v>101</v>
-      </c>
-      <c r="D8" t="s">
-        <v>102</v>
       </c>
       <c r="E8">
         <v>2021</v>
@@ -1284,18 +1278,18 @@
         <v>70.86</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" t="s">
         <v>101</v>
-      </c>
-      <c r="D9" t="s">
-        <v>102</v>
       </c>
       <c r="E9">
         <v>2022</v>
@@ -1349,18 +1343,18 @@
         <v>100.93</v>
       </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" t="s">
         <v>101</v>
-      </c>
-      <c r="D10" t="s">
-        <v>102</v>
       </c>
       <c r="E10">
         <v>2023</v>
@@ -1414,18 +1408,18 @@
         <v>82.48999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" t="s">
         <v>101</v>
-      </c>
-      <c r="D11" t="s">
-        <v>102</v>
       </c>
       <c r="E11">
         <v>2015</v>
@@ -1508,22 +1502,19 @@
       <c r="AF11">
         <v>22.1490803040164</v>
       </c>
-      <c r="AG11">
-        <v>589.8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33">
+    </row>
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" t="s">
         <v>101</v>
-      </c>
-      <c r="D12" t="s">
-        <v>102</v>
       </c>
       <c r="E12">
         <v>2016</v>
@@ -1606,22 +1597,19 @@
       <c r="AF12">
         <v>21.2567013071388</v>
       </c>
-      <c r="AG12">
-        <v>475.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33">
+    </row>
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" t="s">
         <v>101</v>
-      </c>
-      <c r="D13" t="s">
-        <v>102</v>
       </c>
       <c r="E13">
         <v>2017</v>
@@ -1704,22 +1692,19 @@
       <c r="AF13">
         <v>19.3371239744582</v>
       </c>
-      <c r="AG13">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33">
+    </row>
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" t="s">
         <v>101</v>
-      </c>
-      <c r="D14" t="s">
-        <v>102</v>
       </c>
       <c r="E14">
         <v>2018</v>
@@ -1802,22 +1787,19 @@
       <c r="AF14">
         <v>17.7024488717292</v>
       </c>
-      <c r="AG14">
-        <v>547.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33">
+    </row>
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" t="s">
         <v>101</v>
-      </c>
-      <c r="D15" t="s">
-        <v>102</v>
       </c>
       <c r="E15">
         <v>2019</v>
@@ -1900,22 +1882,19 @@
       <c r="AF15">
         <v>17.7888990504455</v>
       </c>
-      <c r="AG15">
-        <v>1316.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33">
+    </row>
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" t="s">
         <v>101</v>
-      </c>
-      <c r="D16" t="s">
-        <v>102</v>
       </c>
       <c r="E16">
         <v>2020</v>
@@ -1998,22 +1977,19 @@
       <c r="AF16">
         <v>17.4777322783093</v>
       </c>
-      <c r="AG16">
-        <v>2235.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33">
+    </row>
+    <row r="17" spans="1:32">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" t="s">
         <v>101</v>
-      </c>
-      <c r="D17" t="s">
-        <v>102</v>
       </c>
       <c r="E17">
         <v>2021</v>
@@ -2096,22 +2072,19 @@
       <c r="AF17">
         <v>18.0764989044589</v>
       </c>
-      <c r="AG17">
-        <v>1578</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33">
+    </row>
+    <row r="18" spans="1:32">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" t="s">
         <v>101</v>
-      </c>
-      <c r="D18" t="s">
-        <v>102</v>
       </c>
       <c r="E18">
         <v>2022</v>
@@ -2194,22 +2167,19 @@
       <c r="AF18">
         <v>17.893195301026</v>
       </c>
-      <c r="AG18">
-        <v>2174.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:33">
+    </row>
+    <row r="19" spans="1:32">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" t="s">
         <v>101</v>
-      </c>
-      <c r="D19" t="s">
-        <v>102</v>
       </c>
       <c r="E19">
         <v>2023</v>
@@ -2292,22 +2262,19 @@
       <c r="AF19">
         <v>17.7753274051522</v>
       </c>
-      <c r="AG19">
-        <v>2223</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33">
+    </row>
+    <row r="20" spans="1:32">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" t="s">
         <v>101</v>
-      </c>
-      <c r="D20" t="s">
-        <v>102</v>
       </c>
       <c r="E20">
         <v>2015</v>
@@ -2367,18 +2334,18 @@
         <v>52.32</v>
       </c>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:32">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" t="s">
         <v>101</v>
-      </c>
-      <c r="D21" t="s">
-        <v>102</v>
       </c>
       <c r="E21">
         <v>2016</v>
@@ -2438,18 +2405,18 @@
         <v>43.64</v>
       </c>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" spans="1:32">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" t="s">
         <v>101</v>
-      </c>
-      <c r="D22" t="s">
-        <v>102</v>
       </c>
       <c r="E22">
         <v>2017</v>
@@ -2509,18 +2476,18 @@
         <v>54.13</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" spans="1:32">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" t="s">
         <v>101</v>
-      </c>
-      <c r="D23" t="s">
-        <v>102</v>
       </c>
       <c r="E23">
         <v>2018</v>
@@ -2580,18 +2547,18 @@
         <v>71.34</v>
       </c>
     </row>
-    <row r="24" spans="1:33">
+    <row r="24" spans="1:32">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" t="s">
         <v>101</v>
-      </c>
-      <c r="D24" t="s">
-        <v>102</v>
       </c>
       <c r="E24">
         <v>2019</v>
@@ -2651,18 +2618,18 @@
         <v>64.3</v>
       </c>
     </row>
-    <row r="25" spans="1:33">
+    <row r="25" spans="1:32">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" t="s">
         <v>101</v>
-      </c>
-      <c r="D25" t="s">
-        <v>102</v>
       </c>
       <c r="E25">
         <v>2020</v>
@@ -2722,18 +2689,18 @@
         <v>41.96</v>
       </c>
     </row>
-    <row r="26" spans="1:33">
+    <row r="26" spans="1:32">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" t="s">
         <v>101</v>
-      </c>
-      <c r="D26" t="s">
-        <v>102</v>
       </c>
       <c r="E26">
         <v>2021</v>
@@ -2811,18 +2778,18 @@
         <v>70.86</v>
       </c>
     </row>
-    <row r="27" spans="1:33">
+    <row r="27" spans="1:32">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D27" t="s">
         <v>101</v>
-      </c>
-      <c r="D27" t="s">
-        <v>102</v>
       </c>
       <c r="E27">
         <v>2022</v>
@@ -2900,18 +2867,18 @@
         <v>100.93</v>
       </c>
     </row>
-    <row r="28" spans="1:33">
+    <row r="28" spans="1:32">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" t="s">
         <v>101</v>
-      </c>
-      <c r="D28" t="s">
-        <v>102</v>
       </c>
       <c r="E28">
         <v>2023</v>
@@ -2989,18 +2956,18 @@
         <v>82.48999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:33">
+    <row r="29" spans="1:32">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" t="s">
         <v>101</v>
-      </c>
-      <c r="D29" t="s">
-        <v>102</v>
       </c>
       <c r="E29">
         <v>2015</v>
@@ -3087,18 +3054,18 @@
         <v>14.6273782452524</v>
       </c>
     </row>
-    <row r="30" spans="1:33">
+    <row r="30" spans="1:32">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C30" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" t="s">
         <v>101</v>
-      </c>
-      <c r="D30" t="s">
-        <v>102</v>
       </c>
       <c r="E30">
         <v>2016</v>
@@ -3185,18 +3152,18 @@
         <v>16.7435935230496</v>
       </c>
     </row>
-    <row r="31" spans="1:33">
+    <row r="31" spans="1:32">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" t="s">
         <v>101</v>
-      </c>
-      <c r="D31" t="s">
-        <v>102</v>
       </c>
       <c r="E31">
         <v>2017</v>
@@ -3283,18 +3250,18 @@
         <v>16.6326878235545</v>
       </c>
     </row>
-    <row r="32" spans="1:33">
+    <row r="32" spans="1:32">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C32" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" t="s">
         <v>101</v>
-      </c>
-      <c r="D32" t="s">
-        <v>102</v>
       </c>
       <c r="E32">
         <v>2018</v>
@@ -3383,16 +3350,16 @@
     </row>
     <row r="33" spans="1:32">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C33" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" t="s">
         <v>101</v>
-      </c>
-      <c r="D33" t="s">
-        <v>102</v>
       </c>
       <c r="E33">
         <v>2019</v>
@@ -3481,16 +3448,16 @@
     </row>
     <row r="34" spans="1:32">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C34" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" t="s">
         <v>101</v>
-      </c>
-      <c r="D34" t="s">
-        <v>102</v>
       </c>
       <c r="E34">
         <v>2020</v>
@@ -3579,16 +3546,16 @@
     </row>
     <row r="35" spans="1:32">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
+        <v>100</v>
+      </c>
+      <c r="D35" t="s">
         <v>101</v>
-      </c>
-      <c r="D35" t="s">
-        <v>102</v>
       </c>
       <c r="E35">
         <v>2021</v>
@@ -3677,16 +3644,16 @@
     </row>
     <row r="36" spans="1:32">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C36" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" t="s">
         <v>101</v>
-      </c>
-      <c r="D36" t="s">
-        <v>102</v>
       </c>
       <c r="E36">
         <v>2022</v>
@@ -3775,16 +3742,16 @@
     </row>
     <row r="37" spans="1:32">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C37" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" t="s">
         <v>101</v>
-      </c>
-      <c r="D37" t="s">
-        <v>102</v>
       </c>
       <c r="E37">
         <v>2023</v>
@@ -3873,16 +3840,16 @@
     </row>
     <row r="38" spans="1:32">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E38">
         <v>2015</v>
@@ -3968,16 +3935,16 @@
     </row>
     <row r="39" spans="1:32">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E39">
         <v>2016</v>
@@ -4063,16 +4030,16 @@
     </row>
     <row r="40" spans="1:32">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D40" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E40">
         <v>2017</v>
@@ -4158,16 +4125,16 @@
     </row>
     <row r="41" spans="1:32">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E41">
         <v>2018</v>
@@ -4247,16 +4214,16 @@
     </row>
     <row r="42" spans="1:32">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E42">
         <v>2019</v>
@@ -4336,16 +4303,16 @@
     </row>
     <row r="43" spans="1:32">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E43">
         <v>2020</v>
@@ -4425,16 +4392,16 @@
     </row>
     <row r="44" spans="1:32">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E44">
         <v>2021</v>
@@ -4514,16 +4481,16 @@
     </row>
     <row r="45" spans="1:32">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E45">
         <v>2022</v>
@@ -4603,16 +4570,16 @@
     </row>
     <row r="46" spans="1:32">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D46" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E46">
         <v>2023</v>
@@ -4692,16 +4659,16 @@
     </row>
     <row r="47" spans="1:32">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D47" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E47">
         <v>2015</v>
@@ -4781,16 +4748,16 @@
     </row>
     <row r="48" spans="1:32">
       <c r="A48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B48" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E48">
         <v>2016</v>
@@ -4868,18 +4835,18 @@
         <v>43.64</v>
       </c>
     </row>
-    <row r="49" spans="1:33">
+    <row r="49" spans="1:32">
       <c r="A49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B49" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D49" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E49">
         <v>2017</v>
@@ -4957,18 +4924,18 @@
         <v>54.13</v>
       </c>
     </row>
-    <row r="50" spans="1:33">
+    <row r="50" spans="1:32">
       <c r="A50" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E50">
         <v>2018</v>
@@ -5046,18 +5013,18 @@
         <v>71.34</v>
       </c>
     </row>
-    <row r="51" spans="1:33">
+    <row r="51" spans="1:32">
       <c r="A51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D51" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E51">
         <v>2019</v>
@@ -5135,18 +5102,18 @@
         <v>64.3</v>
       </c>
     </row>
-    <row r="52" spans="1:33">
+    <row r="52" spans="1:32">
       <c r="A52" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D52" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E52">
         <v>2020</v>
@@ -5224,18 +5191,18 @@
         <v>41.96</v>
       </c>
     </row>
-    <row r="53" spans="1:33">
+    <row r="53" spans="1:32">
       <c r="A53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D53" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E53">
         <v>2021</v>
@@ -5313,18 +5280,18 @@
         <v>70.86</v>
       </c>
     </row>
-    <row r="54" spans="1:33">
+    <row r="54" spans="1:32">
       <c r="A54" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E54">
         <v>2022</v>
@@ -5402,18 +5369,18 @@
         <v>100.93</v>
       </c>
     </row>
-    <row r="55" spans="1:33">
+    <row r="55" spans="1:32">
       <c r="A55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B55" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D55" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E55">
         <v>2023</v>
@@ -5491,18 +5458,18 @@
         <v>82.48999999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:33">
+    <row r="56" spans="1:32">
       <c r="A56" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B56" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D56" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E56">
         <v>2015</v>
@@ -5588,22 +5555,19 @@
       <c r="AF56">
         <v>25.8123252140431</v>
       </c>
-      <c r="AG56">
-        <v>360.3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:33">
+    </row>
+    <row r="57" spans="1:32">
       <c r="A57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B57" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C57" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D57" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E57">
         <v>2016</v>
@@ -5689,22 +5653,19 @@
       <c r="AF57">
         <v>26.173225388189</v>
       </c>
-      <c r="AG57">
-        <v>395.4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:33">
+    </row>
+    <row r="58" spans="1:32">
       <c r="A58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B58" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C58" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D58" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E58">
         <v>2017</v>
@@ -5790,22 +5751,19 @@
       <c r="AF58">
         <v>24.3609920782892</v>
       </c>
-      <c r="AG58">
-        <v>263.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:33">
+    </row>
+    <row r="59" spans="1:32">
       <c r="A59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B59" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C59" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E59">
         <v>2018</v>
@@ -5891,22 +5849,19 @@
       <c r="AF59">
         <v>25.2724385286024</v>
       </c>
-      <c r="AG59">
-        <v>264.5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:33">
+    </row>
+    <row r="60" spans="1:32">
       <c r="A60" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B60" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C60" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D60" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E60">
         <v>2019</v>
@@ -5992,22 +5947,19 @@
       <c r="AF60">
         <v>25.5600401306072</v>
       </c>
-      <c r="AG60">
-        <v>235.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:33">
+    </row>
+    <row r="61" spans="1:32">
       <c r="A61" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C61" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D61" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E61">
         <v>2020</v>
@@ -6093,22 +6045,19 @@
       <c r="AF61">
         <v>22.1948673455795</v>
       </c>
-      <c r="AG61">
-        <v>316.5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:33">
+    </row>
+    <row r="62" spans="1:32">
       <c r="A62" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B62" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C62" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D62" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E62">
         <v>2021</v>
@@ -6194,22 +6143,19 @@
       <c r="AF62">
         <v>24.6358299212806</v>
       </c>
-      <c r="AG62">
-        <v>281.2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:33">
+    </row>
+    <row r="63" spans="1:32">
       <c r="A63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C63" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D63" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E63">
         <v>2022</v>
@@ -6295,22 +6241,19 @@
       <c r="AF63">
         <v>26.9365134620331</v>
       </c>
-      <c r="AG63">
-        <v>296.7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:33">
+    </row>
+    <row r="64" spans="1:32">
       <c r="A64" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C64" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E64">
         <v>2023</v>
@@ -6396,22 +6339,19 @@
       <c r="AF64">
         <v>25.3707484836752</v>
       </c>
-      <c r="AG64">
-        <v>229.4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:33">
+    </row>
+    <row r="65" spans="1:32">
       <c r="A65" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C65" t="s">
+        <v>100</v>
+      </c>
+      <c r="D65" t="s">
         <v>101</v>
-      </c>
-      <c r="D65" t="s">
-        <v>102</v>
       </c>
       <c r="E65">
         <v>2015</v>
@@ -6498,18 +6438,18 @@
         <v>22.10491944754</v>
       </c>
     </row>
-    <row r="66" spans="1:33">
+    <row r="66" spans="1:32">
       <c r="A66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C66" t="s">
+        <v>100</v>
+      </c>
+      <c r="D66" t="s">
         <v>101</v>
-      </c>
-      <c r="D66" t="s">
-        <v>102</v>
       </c>
       <c r="E66">
         <v>2016</v>
@@ -6596,18 +6536,18 @@
         <v>25.2273067617101</v>
       </c>
     </row>
-    <row r="67" spans="1:33">
+    <row r="67" spans="1:32">
       <c r="A67" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C67" t="s">
+        <v>100</v>
+      </c>
+      <c r="D67" t="s">
         <v>101</v>
-      </c>
-      <c r="D67" t="s">
-        <v>102</v>
       </c>
       <c r="E67">
         <v>2017</v>
@@ -6685,18 +6625,18 @@
         <v>54.13</v>
       </c>
     </row>
-    <row r="68" spans="1:33">
+    <row r="68" spans="1:32">
       <c r="A68" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C68" t="s">
+        <v>100</v>
+      </c>
+      <c r="D68" t="s">
         <v>101</v>
-      </c>
-      <c r="D68" t="s">
-        <v>102</v>
       </c>
       <c r="E68">
         <v>2018</v>
@@ -6774,18 +6714,18 @@
         <v>71.34</v>
       </c>
     </row>
-    <row r="69" spans="1:33">
+    <row r="69" spans="1:32">
       <c r="A69" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C69" t="s">
+        <v>100</v>
+      </c>
+      <c r="D69" t="s">
         <v>101</v>
-      </c>
-      <c r="D69" t="s">
-        <v>102</v>
       </c>
       <c r="E69">
         <v>2019</v>
@@ -6863,18 +6803,18 @@
         <v>64.3</v>
       </c>
     </row>
-    <row r="70" spans="1:33">
+    <row r="70" spans="1:32">
       <c r="A70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C70" t="s">
+        <v>100</v>
+      </c>
+      <c r="D70" t="s">
         <v>101</v>
-      </c>
-      <c r="D70" t="s">
-        <v>102</v>
       </c>
       <c r="E70">
         <v>2020</v>
@@ -6952,18 +6892,18 @@
         <v>41.96</v>
       </c>
     </row>
-    <row r="71" spans="1:33">
+    <row r="71" spans="1:32">
       <c r="A71" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C71" t="s">
+        <v>100</v>
+      </c>
+      <c r="D71" t="s">
         <v>101</v>
-      </c>
-      <c r="D71" t="s">
-        <v>102</v>
       </c>
       <c r="E71">
         <v>2021</v>
@@ -7041,18 +6981,18 @@
         <v>70.86</v>
       </c>
     </row>
-    <row r="72" spans="1:33">
+    <row r="72" spans="1:32">
       <c r="A72" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B72" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C72" t="s">
+        <v>100</v>
+      </c>
+      <c r="D72" t="s">
         <v>101</v>
-      </c>
-      <c r="D72" t="s">
-        <v>102</v>
       </c>
       <c r="E72">
         <v>2022</v>
@@ -7130,18 +7070,18 @@
         <v>100.93</v>
       </c>
     </row>
-    <row r="73" spans="1:33">
+    <row r="73" spans="1:32">
       <c r="A73" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B73" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C73" t="s">
+        <v>100</v>
+      </c>
+      <c r="D73" t="s">
         <v>101</v>
-      </c>
-      <c r="D73" t="s">
-        <v>102</v>
       </c>
       <c r="E73">
         <v>2023</v>
@@ -7219,18 +7159,18 @@
         <v>82.48999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:33">
+    <row r="74" spans="1:32">
       <c r="A74" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C74" t="s">
+        <v>100</v>
+      </c>
+      <c r="D74" t="s">
         <v>101</v>
-      </c>
-      <c r="D74" t="s">
-        <v>102</v>
       </c>
       <c r="E74">
         <v>2015</v>
@@ -7314,18 +7254,18 @@
         <v>21.1423576597254</v>
       </c>
     </row>
-    <row r="75" spans="1:33">
+    <row r="75" spans="1:32">
       <c r="A75" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C75" t="s">
+        <v>100</v>
+      </c>
+      <c r="D75" t="s">
         <v>101</v>
-      </c>
-      <c r="D75" t="s">
-        <v>102</v>
       </c>
       <c r="E75">
         <v>2016</v>
@@ -7409,18 +7349,18 @@
         <v>20.8570992758656</v>
       </c>
     </row>
-    <row r="76" spans="1:33">
+    <row r="76" spans="1:32">
       <c r="A76" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C76" t="s">
+        <v>100</v>
+      </c>
+      <c r="D76" t="s">
         <v>101</v>
-      </c>
-      <c r="D76" t="s">
-        <v>102</v>
       </c>
       <c r="E76">
         <v>2017</v>
@@ -7503,22 +7443,19 @@
       <c r="AF76">
         <v>21.1680432165628</v>
       </c>
-      <c r="AG76">
-        <v>130.2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:33">
+    </row>
+    <row r="77" spans="1:32">
       <c r="A77" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C77" t="s">
+        <v>100</v>
+      </c>
+      <c r="D77" t="s">
         <v>101</v>
-      </c>
-      <c r="D77" t="s">
-        <v>102</v>
       </c>
       <c r="E77">
         <v>2018</v>
@@ -7601,22 +7538,19 @@
       <c r="AF77">
         <v>22.1740306166793</v>
       </c>
-      <c r="AG77">
-        <v>132.8</v>
-      </c>
-    </row>
-    <row r="78" spans="1:33">
+    </row>
+    <row r="78" spans="1:32">
       <c r="A78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B78" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C78" t="s">
+        <v>100</v>
+      </c>
+      <c r="D78" t="s">
         <v>101</v>
-      </c>
-      <c r="D78" t="s">
-        <v>102</v>
       </c>
       <c r="E78">
         <v>2019</v>
@@ -7699,22 +7633,19 @@
       <c r="AF78">
         <v>21.739927149931</v>
       </c>
-      <c r="AG78">
-        <v>136.3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:33">
+    </row>
+    <row r="79" spans="1:32">
       <c r="A79" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B79" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C79" t="s">
+        <v>100</v>
+      </c>
+      <c r="D79" t="s">
         <v>101</v>
-      </c>
-      <c r="D79" t="s">
-        <v>102</v>
       </c>
       <c r="E79">
         <v>2020</v>
@@ -7797,22 +7728,19 @@
       <c r="AF79">
         <v>19.9382667510933</v>
       </c>
-      <c r="AG79">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="80" spans="1:33">
+    </row>
+    <row r="80" spans="1:32">
       <c r="A80" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C80" t="s">
+        <v>100</v>
+      </c>
+      <c r="D80" t="s">
         <v>101</v>
-      </c>
-      <c r="D80" t="s">
-        <v>102</v>
       </c>
       <c r="E80">
         <v>2021</v>
@@ -7895,22 +7823,19 @@
       <c r="AF80">
         <v>24.1674095479002</v>
       </c>
-      <c r="AG80">
-        <v>140.8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:33">
+    </row>
+    <row r="81" spans="1:32">
       <c r="A81" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B81" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D81" t="s">
         <v>101</v>
-      </c>
-      <c r="D81" t="s">
-        <v>102</v>
       </c>
       <c r="E81">
         <v>2022</v>
@@ -7993,22 +7918,19 @@
       <c r="AF81">
         <v>26.0812426572599</v>
       </c>
-      <c r="AG81">
-        <v>177.8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:33">
+    </row>
+    <row r="82" spans="1:32">
       <c r="A82" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C82" t="s">
+        <v>100</v>
+      </c>
+      <c r="D82" t="s">
         <v>101</v>
-      </c>
-      <c r="D82" t="s">
-        <v>102</v>
       </c>
       <c r="E82">
         <v>2023</v>
@@ -8091,22 +8013,19 @@
       <c r="AF82">
         <v>22.9465317535315</v>
       </c>
-      <c r="AG82">
-        <v>140.1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:33">
+    </row>
+    <row r="83" spans="1:32">
       <c r="A83" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B83" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C83" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D83" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E83">
         <v>2015</v>
@@ -8192,22 +8111,19 @@
       <c r="AF83">
         <v>24.1024162766989</v>
       </c>
-      <c r="AG83">
-        <v>249.5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:33">
+    </row>
+    <row r="84" spans="1:32">
       <c r="A84" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B84" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C84" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E84">
         <v>2016</v>
@@ -8293,22 +8209,19 @@
       <c r="AF84">
         <v>24.2234212780588</v>
       </c>
-      <c r="AG84">
-        <v>279.6</v>
-      </c>
-    </row>
-    <row r="85" spans="1:33">
+    </row>
+    <row r="85" spans="1:32">
       <c r="A85" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B85" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C85" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D85" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E85">
         <v>2017</v>
@@ -8394,22 +8307,19 @@
       <c r="AF85">
         <v>22.5842861999584</v>
       </c>
-      <c r="AG85">
-        <v>193.9</v>
-      </c>
-    </row>
-    <row r="86" spans="1:33">
+    </row>
+    <row r="86" spans="1:32">
       <c r="A86" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C86" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E86">
         <v>2018</v>
@@ -8495,22 +8405,19 @@
       <c r="AF86">
         <v>23.4751871722398</v>
       </c>
-      <c r="AG86">
-        <v>183.4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:33">
+    </row>
+    <row r="87" spans="1:32">
       <c r="A87" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B87" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C87" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D87" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E87">
         <v>2019</v>
@@ -8596,22 +8503,19 @@
       <c r="AF87">
         <v>25.575368512731</v>
       </c>
-      <c r="AG87">
-        <v>183.7</v>
-      </c>
-    </row>
-    <row r="88" spans="1:33">
+    </row>
+    <row r="88" spans="1:32">
       <c r="A88" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B88" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C88" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D88" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E88">
         <v>2020</v>
@@ -8697,22 +8601,19 @@
       <c r="AF88">
         <v>23.6871303712315</v>
       </c>
-      <c r="AG88">
-        <v>261.4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:33">
+    </row>
+    <row r="89" spans="1:32">
       <c r="A89" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B89" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C89" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D89" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E89">
         <v>2021</v>
@@ -8798,22 +8699,19 @@
       <c r="AF89">
         <v>24.1312117221098</v>
       </c>
-      <c r="AG89">
-        <v>261.3</v>
-      </c>
-    </row>
-    <row r="90" spans="1:33">
+    </row>
+    <row r="90" spans="1:32">
       <c r="A90" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B90" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C90" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D90" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E90">
         <v>2022</v>
@@ -8899,22 +8797,19 @@
       <c r="AF90">
         <v>25.4074707206706</v>
       </c>
-      <c r="AG90">
-        <v>394.6</v>
-      </c>
-    </row>
-    <row r="91" spans="1:33">
+    </row>
+    <row r="91" spans="1:32">
       <c r="A91" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B91" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C91" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D91" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E91">
         <v>2023</v>
@@ -9000,22 +8895,19 @@
       <c r="AF91">
         <v>28.4136914959886</v>
       </c>
-      <c r="AG91">
-        <v>357.6</v>
-      </c>
-    </row>
-    <row r="92" spans="1:33">
+    </row>
+    <row r="92" spans="1:32">
       <c r="A92" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B92" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C92" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D92" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E92">
         <v>2015</v>
@@ -9096,18 +8988,18 @@
         <v>23.4572080583441</v>
       </c>
     </row>
-    <row r="93" spans="1:33">
+    <row r="93" spans="1:32">
       <c r="A93" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B93" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C93" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D93" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E93">
         <v>2016</v>
@@ -9188,18 +9080,18 @@
         <v>24.0079934600948</v>
       </c>
     </row>
-    <row r="94" spans="1:33">
+    <row r="94" spans="1:32">
       <c r="A94" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B94" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C94" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D94" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E94">
         <v>2017</v>
@@ -9280,18 +9172,18 @@
         <v>23.3185966619773</v>
       </c>
     </row>
-    <row r="95" spans="1:33">
+    <row r="95" spans="1:32">
       <c r="A95" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B95" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C95" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D95" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E95">
         <v>2018</v>
@@ -9372,18 +9264,18 @@
         <v>24.3167782701782</v>
       </c>
     </row>
-    <row r="96" spans="1:33">
+    <row r="96" spans="1:32">
       <c r="A96" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B96" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C96" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D96" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E96">
         <v>2019</v>
@@ -9469,16 +9361,16 @@
     </row>
     <row r="97" spans="1:32">
       <c r="A97" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B97" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C97" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D97" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E97">
         <v>2020</v>
@@ -9564,16 +9456,16 @@
     </row>
     <row r="98" spans="1:32">
       <c r="A98" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B98" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C98" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D98" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E98">
         <v>2021</v>
@@ -9659,16 +9551,16 @@
     </row>
     <row r="99" spans="1:32">
       <c r="A99" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B99" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C99" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E99">
         <v>2022</v>
@@ -9754,16 +9646,16 @@
     </row>
     <row r="100" spans="1:32">
       <c r="A100" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B100" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C100" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D100" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E100">
         <v>2023</v>
@@ -9849,16 +9741,16 @@
     </row>
     <row r="101" spans="1:32">
       <c r="A101" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B101" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C101" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D101" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E101">
         <v>2015</v>
@@ -9920,16 +9812,16 @@
     </row>
     <row r="102" spans="1:32">
       <c r="A102" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B102" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C102" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D102" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E102">
         <v>2016</v>
@@ -9991,16 +9883,16 @@
     </row>
     <row r="103" spans="1:32">
       <c r="A103" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B103" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C103" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D103" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E103">
         <v>2017</v>
@@ -10062,16 +9954,16 @@
     </row>
     <row r="104" spans="1:32">
       <c r="A104" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B104" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C104" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D104" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E104">
         <v>2018</v>
@@ -10133,16 +10025,16 @@
     </row>
     <row r="105" spans="1:32">
       <c r="A105" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B105" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C105" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D105" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E105">
         <v>2019</v>
@@ -10204,16 +10096,16 @@
     </row>
     <row r="106" spans="1:32">
       <c r="A106" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B106" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C106" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D106" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E106">
         <v>2020</v>
@@ -10275,16 +10167,16 @@
     </row>
     <row r="107" spans="1:32">
       <c r="A107" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B107" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C107" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D107" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E107">
         <v>2021</v>
@@ -10364,16 +10256,16 @@
     </row>
     <row r="108" spans="1:32">
       <c r="A108" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B108" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C108" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D108" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E108">
         <v>2022</v>
@@ -10453,16 +10345,16 @@
     </row>
     <row r="109" spans="1:32">
       <c r="A109" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B109" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C109" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D109" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E109">
         <v>2023</v>
@@ -10542,16 +10434,16 @@
     </row>
     <row r="110" spans="1:32">
       <c r="A110" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B110" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C110" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D110" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E110">
         <v>2015</v>
@@ -10637,16 +10529,16 @@
     </row>
     <row r="111" spans="1:32">
       <c r="A111" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B111" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C111" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D111" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E111">
         <v>2016</v>
@@ -10732,16 +10624,16 @@
     </row>
     <row r="112" spans="1:32">
       <c r="A112" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B112" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C112" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D112" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E112">
         <v>2017</v>
@@ -10825,18 +10717,18 @@
         <v>14.9920997503639</v>
       </c>
     </row>
-    <row r="113" spans="1:33">
+    <row r="113" spans="1:32">
       <c r="A113" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B113" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C113" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D113" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E113">
         <v>2018</v>
@@ -10920,18 +10812,18 @@
         <v>15.269462908084</v>
       </c>
     </row>
-    <row r="114" spans="1:33">
+    <row r="114" spans="1:32">
       <c r="A114" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B114" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C114" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D114" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E114">
         <v>2019</v>
@@ -11015,18 +10907,18 @@
         <v>15.5470600045533</v>
       </c>
     </row>
-    <row r="115" spans="1:33">
+    <row r="115" spans="1:32">
       <c r="A115" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B115" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C115" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D115" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E115">
         <v>2020</v>
@@ -11110,18 +11002,18 @@
         <v>14.8813590480588</v>
       </c>
     </row>
-    <row r="116" spans="1:33">
+    <row r="116" spans="1:32">
       <c r="A116" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B116" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C116" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D116" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E116">
         <v>2021</v>
@@ -11205,18 +11097,18 @@
         <v>16.4297863174204</v>
       </c>
     </row>
-    <row r="117" spans="1:33">
+    <row r="117" spans="1:32">
       <c r="A117" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B117" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C117" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D117" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E117">
         <v>2022</v>
@@ -11300,18 +11192,18 @@
         <v>16.3623217477379</v>
       </c>
     </row>
-    <row r="118" spans="1:33">
+    <row r="118" spans="1:32">
       <c r="A118" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B118" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C118" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D118" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E118">
         <v>2023</v>
@@ -11395,18 +11287,18 @@
         <v>17.015284341071</v>
       </c>
     </row>
-    <row r="119" spans="1:33">
+    <row r="119" spans="1:32">
       <c r="A119" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B119" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C119" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D119" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E119">
         <v>2015</v>
@@ -11489,22 +11381,19 @@
       <c r="AF119">
         <v>30.8458833789351</v>
       </c>
-      <c r="AG119">
-        <v>995.2</v>
-      </c>
-    </row>
-    <row r="120" spans="1:33">
+    </row>
+    <row r="120" spans="1:32">
       <c r="A120" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B120" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C120" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D120" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E120">
         <v>2016</v>
@@ -11587,22 +11476,19 @@
       <c r="AF120">
         <v>28.6412079584013</v>
       </c>
-      <c r="AG120">
-        <v>998.3</v>
-      </c>
-    </row>
-    <row r="121" spans="1:33">
+    </row>
+    <row r="121" spans="1:32">
       <c r="A121" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B121" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C121" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D121" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E121">
         <v>2017</v>
@@ -11685,22 +11571,19 @@
       <c r="AF121">
         <v>27.9863154861129</v>
       </c>
-      <c r="AG121">
-        <v>621.4</v>
-      </c>
-    </row>
-    <row r="122" spans="1:33">
+    </row>
+    <row r="122" spans="1:32">
       <c r="A122" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B122" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C122" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D122" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E122">
         <v>2018</v>
@@ -11783,22 +11666,19 @@
       <c r="AF122">
         <v>31.2062328120813</v>
       </c>
-      <c r="AG122">
-        <v>639.8</v>
-      </c>
-    </row>
-    <row r="123" spans="1:33">
+    </row>
+    <row r="123" spans="1:32">
       <c r="A123" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B123" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C123" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D123" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E123">
         <v>2019</v>
@@ -11881,22 +11761,19 @@
       <c r="AF123">
         <v>29.6599984642663</v>
       </c>
-      <c r="AG123">
-        <v>693.9</v>
-      </c>
-    </row>
-    <row r="124" spans="1:33">
+    </row>
+    <row r="124" spans="1:32">
       <c r="A124" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B124" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C124" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D124" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E124">
         <v>2020</v>
@@ -11979,22 +11856,19 @@
       <c r="AF124">
         <v>27.1210867326524</v>
       </c>
-      <c r="AG124">
-        <v>2371.9</v>
-      </c>
-    </row>
-    <row r="125" spans="1:33">
+    </row>
+    <row r="125" spans="1:32">
       <c r="A125" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B125" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C125" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D125" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E125">
         <v>2021</v>
@@ -12077,22 +11951,19 @@
       <c r="AF125">
         <v>29.6714820409688</v>
       </c>
-      <c r="AG125">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="126" spans="1:33">
+    </row>
+    <row r="126" spans="1:32">
       <c r="A126" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B126" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C126" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D126" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E126">
         <v>2022</v>
@@ -12175,22 +12046,19 @@
       <c r="AF126">
         <v>30.9625405355437</v>
       </c>
-      <c r="AG126">
-        <v>1137.8</v>
-      </c>
-    </row>
-    <row r="127" spans="1:33">
+    </row>
+    <row r="127" spans="1:32">
       <c r="A127" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B127" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C127" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D127" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E127">
         <v>2023</v>
@@ -12267,22 +12135,19 @@
       <c r="AC127">
         <v>82.48999999999999</v>
       </c>
-      <c r="AG127">
-        <v>1774.7</v>
-      </c>
-    </row>
-    <row r="128" spans="1:33">
+    </row>
+    <row r="128" spans="1:32">
       <c r="A128" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B128" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C128" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D128" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E128">
         <v>2015</v>
@@ -12362,16 +12227,16 @@
     </row>
     <row r="129" spans="1:32">
       <c r="A129" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B129" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C129" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D129" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E129">
         <v>2016</v>
@@ -12451,16 +12316,16 @@
     </row>
     <row r="130" spans="1:32">
       <c r="A130" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B130" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C130" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D130" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E130">
         <v>2017</v>
@@ -12540,16 +12405,16 @@
     </row>
     <row r="131" spans="1:32">
       <c r="A131" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B131" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C131" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D131" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E131">
         <v>2018</v>
@@ -12629,16 +12494,16 @@
     </row>
     <row r="132" spans="1:32">
       <c r="A132" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B132" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C132" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D132" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E132">
         <v>2019</v>
@@ -12718,16 +12583,16 @@
     </row>
     <row r="133" spans="1:32">
       <c r="A133" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B133" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C133" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D133" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E133">
         <v>2020</v>
@@ -12807,16 +12672,16 @@
     </row>
     <row r="134" spans="1:32">
       <c r="A134" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B134" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C134" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D134" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E134">
         <v>2021</v>
@@ -12896,16 +12761,16 @@
     </row>
     <row r="135" spans="1:32">
       <c r="A135" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B135" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C135" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D135" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E135">
         <v>2022</v>
@@ -12985,16 +12850,16 @@
     </row>
     <row r="136" spans="1:32">
       <c r="A136" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B136" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C136" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D136" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E136">
         <v>2023</v>
@@ -13074,16 +12939,16 @@
     </row>
     <row r="137" spans="1:32">
       <c r="A137" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B137" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C137" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D137" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E137">
         <v>2015</v>
@@ -13169,16 +13034,16 @@
     </row>
     <row r="138" spans="1:32">
       <c r="A138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B138" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C138" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D138" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E138">
         <v>2016</v>
@@ -13264,16 +13129,16 @@
     </row>
     <row r="139" spans="1:32">
       <c r="A139" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B139" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C139" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D139" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E139">
         <v>2017</v>
@@ -13359,16 +13224,16 @@
     </row>
     <row r="140" spans="1:32">
       <c r="A140" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B140" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C140" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D140" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E140">
         <v>2018</v>
@@ -13454,16 +13319,16 @@
     </row>
     <row r="141" spans="1:32">
       <c r="A141" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B141" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C141" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D141" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E141">
         <v>2019</v>
@@ -13549,16 +13414,16 @@
     </row>
     <row r="142" spans="1:32">
       <c r="A142" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B142" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C142" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D142" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E142">
         <v>2020</v>
@@ -13644,16 +13509,16 @@
     </row>
     <row r="143" spans="1:32">
       <c r="A143" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B143" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C143" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D143" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E143">
         <v>2021</v>
@@ -13739,16 +13604,16 @@
     </row>
     <row r="144" spans="1:32">
       <c r="A144" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B144" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C144" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D144" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E144">
         <v>2022</v>
@@ -13834,16 +13699,16 @@
     </row>
     <row r="145" spans="1:32">
       <c r="A145" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B145" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C145" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D145" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E145">
         <v>2023</v>
@@ -13929,16 +13794,16 @@
     </row>
     <row r="146" spans="1:32">
       <c r="A146" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B146" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C146" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D146" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E146">
         <v>2015</v>
@@ -14018,16 +13883,16 @@
     </row>
     <row r="147" spans="1:32">
       <c r="A147" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B147" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C147" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D147" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E147">
         <v>2016</v>
@@ -14107,16 +13972,16 @@
     </row>
     <row r="148" spans="1:32">
       <c r="A148" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B148" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C148" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D148" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E148">
         <v>2017</v>
@@ -14196,16 +14061,16 @@
     </row>
     <row r="149" spans="1:32">
       <c r="A149" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B149" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C149" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D149" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E149">
         <v>2018</v>
@@ -14285,16 +14150,16 @@
     </row>
     <row r="150" spans="1:32">
       <c r="A150" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B150" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C150" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D150" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E150">
         <v>2019</v>
@@ -14374,16 +14239,16 @@
     </row>
     <row r="151" spans="1:32">
       <c r="A151" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B151" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C151" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D151" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E151">
         <v>2020</v>
@@ -14463,16 +14328,16 @@
     </row>
     <row r="152" spans="1:32">
       <c r="A152" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B152" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C152" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D152" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E152">
         <v>2021</v>
@@ -14552,16 +14417,16 @@
     </row>
     <row r="153" spans="1:32">
       <c r="A153" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B153" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C153" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D153" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E153">
         <v>2022</v>
@@ -14641,16 +14506,16 @@
     </row>
     <row r="154" spans="1:32">
       <c r="A154" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B154" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C154" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D154" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E154">
         <v>2023</v>
@@ -14730,16 +14595,16 @@
     </row>
     <row r="155" spans="1:32">
       <c r="A155" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B155" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C155" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D155" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E155">
         <v>2015</v>
@@ -14825,16 +14690,16 @@
     </row>
     <row r="156" spans="1:32">
       <c r="A156" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B156" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C156" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D156" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E156">
         <v>2016</v>
@@ -14914,16 +14779,16 @@
     </row>
     <row r="157" spans="1:32">
       <c r="A157" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B157" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C157" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D157" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E157">
         <v>2017</v>
@@ -15003,16 +14868,16 @@
     </row>
     <row r="158" spans="1:32">
       <c r="A158" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B158" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C158" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D158" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E158">
         <v>2018</v>
@@ -15092,16 +14957,16 @@
     </row>
     <row r="159" spans="1:32">
       <c r="A159" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B159" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C159" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D159" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E159">
         <v>2019</v>
@@ -15181,16 +15046,16 @@
     </row>
     <row r="160" spans="1:32">
       <c r="A160" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B160" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C160" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D160" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E160">
         <v>2020</v>
@@ -15276,16 +15141,16 @@
     </row>
     <row r="161" spans="1:32">
       <c r="A161" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B161" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C161" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D161" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E161">
         <v>2021</v>
@@ -15365,16 +15230,16 @@
     </row>
     <row r="162" spans="1:32">
       <c r="A162" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B162" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C162" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D162" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E162">
         <v>2022</v>
@@ -15454,16 +15319,16 @@
     </row>
     <row r="163" spans="1:32">
       <c r="A163" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B163" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C163" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D163" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E163">
         <v>2023</v>
@@ -15543,16 +15408,16 @@
     </row>
     <row r="164" spans="1:32">
       <c r="A164" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B164" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C164" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D164" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E164">
         <v>2015</v>
@@ -15632,16 +15497,16 @@
     </row>
     <row r="165" spans="1:32">
       <c r="A165" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B165" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C165" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D165" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E165">
         <v>2016</v>
@@ -15721,16 +15586,16 @@
     </row>
     <row r="166" spans="1:32">
       <c r="A166" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B166" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C166" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D166" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E166">
         <v>2017</v>
@@ -15810,16 +15675,16 @@
     </row>
     <row r="167" spans="1:32">
       <c r="A167" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B167" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C167" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D167" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E167">
         <v>2018</v>
@@ -15899,16 +15764,16 @@
     </row>
     <row r="168" spans="1:32">
       <c r="A168" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B168" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C168" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D168" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E168">
         <v>2019</v>
@@ -15988,16 +15853,16 @@
     </row>
     <row r="169" spans="1:32">
       <c r="A169" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B169" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C169" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D169" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E169">
         <v>2020</v>
@@ -16077,16 +15942,16 @@
     </row>
     <row r="170" spans="1:32">
       <c r="A170" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B170" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C170" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D170" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E170">
         <v>2021</v>
@@ -16166,16 +16031,16 @@
     </row>
     <row r="171" spans="1:32">
       <c r="A171" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B171" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C171" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D171" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E171">
         <v>2022</v>
@@ -16255,16 +16120,16 @@
     </row>
     <row r="172" spans="1:32">
       <c r="A172" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B172" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C172" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D172" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E172">
         <v>2023</v>
@@ -16344,16 +16209,16 @@
     </row>
     <row r="173" spans="1:32">
       <c r="A173" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B173" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C173" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D173" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E173">
         <v>2015</v>
@@ -16442,16 +16307,16 @@
     </row>
     <row r="174" spans="1:32">
       <c r="A174" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B174" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C174" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D174" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E174">
         <v>2016</v>
@@ -16540,16 +16405,16 @@
     </row>
     <row r="175" spans="1:32">
       <c r="A175" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B175" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C175" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D175" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E175">
         <v>2017</v>
@@ -16638,16 +16503,16 @@
     </row>
     <row r="176" spans="1:32">
       <c r="A176" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B176" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C176" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D176" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E176">
         <v>2018</v>
@@ -16733,16 +16598,16 @@
     </row>
     <row r="177" spans="1:32">
       <c r="A177" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B177" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C177" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D177" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E177">
         <v>2019</v>
@@ -16831,16 +16696,16 @@
     </row>
     <row r="178" spans="1:32">
       <c r="A178" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B178" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C178" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D178" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E178">
         <v>2020</v>
@@ -16929,16 +16794,16 @@
     </row>
     <row r="179" spans="1:32">
       <c r="A179" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B179" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C179" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D179" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E179">
         <v>2021</v>
@@ -17018,16 +16883,16 @@
     </row>
     <row r="180" spans="1:32">
       <c r="A180" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B180" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C180" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D180" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E180">
         <v>2022</v>
@@ -17107,16 +16972,16 @@
     </row>
     <row r="181" spans="1:32">
       <c r="A181" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B181" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C181" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D181" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E181">
         <v>2023</v>
@@ -17196,16 +17061,16 @@
     </row>
     <row r="182" spans="1:32">
       <c r="A182" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B182" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C182" t="s">
+        <v>100</v>
+      </c>
+      <c r="D182" t="s">
         <v>101</v>
-      </c>
-      <c r="D182" t="s">
-        <v>102</v>
       </c>
       <c r="E182">
         <v>2015</v>
@@ -17273,16 +17138,16 @@
     </row>
     <row r="183" spans="1:32">
       <c r="A183" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B183" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C183" t="s">
+        <v>100</v>
+      </c>
+      <c r="D183" t="s">
         <v>101</v>
-      </c>
-      <c r="D183" t="s">
-        <v>102</v>
       </c>
       <c r="E183">
         <v>2016</v>
@@ -17350,16 +17215,16 @@
     </row>
     <row r="184" spans="1:32">
       <c r="A184" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B184" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C184" t="s">
+        <v>100</v>
+      </c>
+      <c r="D184" t="s">
         <v>101</v>
-      </c>
-      <c r="D184" t="s">
-        <v>102</v>
       </c>
       <c r="E184">
         <v>2017</v>
@@ -17427,16 +17292,16 @@
     </row>
     <row r="185" spans="1:32">
       <c r="A185" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B185" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C185" t="s">
+        <v>100</v>
+      </c>
+      <c r="D185" t="s">
         <v>101</v>
-      </c>
-      <c r="D185" t="s">
-        <v>102</v>
       </c>
       <c r="E185">
         <v>2018</v>
@@ -17498,16 +17363,16 @@
     </row>
     <row r="186" spans="1:32">
       <c r="A186" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B186" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C186" t="s">
+        <v>100</v>
+      </c>
+      <c r="D186" t="s">
         <v>101</v>
-      </c>
-      <c r="D186" t="s">
-        <v>102</v>
       </c>
       <c r="E186">
         <v>2019</v>
@@ -17569,16 +17434,16 @@
     </row>
     <row r="187" spans="1:32">
       <c r="A187" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B187" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C187" t="s">
+        <v>100</v>
+      </c>
+      <c r="D187" t="s">
         <v>101</v>
-      </c>
-      <c r="D187" t="s">
-        <v>102</v>
       </c>
       <c r="E187">
         <v>2020</v>
@@ -17646,16 +17511,16 @@
     </row>
     <row r="188" spans="1:32">
       <c r="A188" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B188" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C188" t="s">
+        <v>100</v>
+      </c>
+      <c r="D188" t="s">
         <v>101</v>
-      </c>
-      <c r="D188" t="s">
-        <v>102</v>
       </c>
       <c r="E188">
         <v>2021</v>
@@ -17711,16 +17576,16 @@
     </row>
     <row r="189" spans="1:32">
       <c r="A189" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B189" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C189" t="s">
+        <v>100</v>
+      </c>
+      <c r="D189" t="s">
         <v>101</v>
-      </c>
-      <c r="D189" t="s">
-        <v>102</v>
       </c>
       <c r="E189">
         <v>2022</v>
@@ -17776,16 +17641,16 @@
     </row>
     <row r="190" spans="1:32">
       <c r="A190" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B190" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C190" t="s">
+        <v>100</v>
+      </c>
+      <c r="D190" t="s">
         <v>101</v>
-      </c>
-      <c r="D190" t="s">
-        <v>102</v>
       </c>
       <c r="E190">
         <v>2023</v>
@@ -17841,16 +17706,16 @@
     </row>
     <row r="191" spans="1:32">
       <c r="A191" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B191" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C191" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D191" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E191">
         <v>2015</v>
@@ -17936,16 +17801,16 @@
     </row>
     <row r="192" spans="1:32">
       <c r="A192" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B192" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C192" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D192" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E192">
         <v>2016</v>
@@ -18029,18 +17894,18 @@
         <v>20.1305432828484</v>
       </c>
     </row>
-    <row r="193" spans="1:33">
+    <row r="193" spans="1:32">
       <c r="A193" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B193" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C193" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D193" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E193">
         <v>2017</v>
@@ -18124,18 +17989,18 @@
         <v>19.4078532828264</v>
       </c>
     </row>
-    <row r="194" spans="1:33">
+    <row r="194" spans="1:32">
       <c r="A194" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B194" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C194" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D194" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E194">
         <v>2018</v>
@@ -18213,18 +18078,18 @@
         <v>71.34</v>
       </c>
     </row>
-    <row r="195" spans="1:33">
+    <row r="195" spans="1:32">
       <c r="A195" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B195" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C195" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D195" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E195">
         <v>2019</v>
@@ -18302,18 +18167,18 @@
         <v>64.3</v>
       </c>
     </row>
-    <row r="196" spans="1:33">
+    <row r="196" spans="1:32">
       <c r="A196" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B196" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C196" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D196" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E196">
         <v>2020</v>
@@ -18391,18 +18256,18 @@
         <v>41.96</v>
       </c>
     </row>
-    <row r="197" spans="1:33">
+    <row r="197" spans="1:32">
       <c r="A197" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B197" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C197" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D197" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E197">
         <v>2021</v>
@@ -18480,18 +18345,18 @@
         <v>70.86</v>
       </c>
     </row>
-    <row r="198" spans="1:33">
+    <row r="198" spans="1:32">
       <c r="A198" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B198" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C198" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D198" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E198">
         <v>2022</v>
@@ -18569,18 +18434,18 @@
         <v>100.93</v>
       </c>
     </row>
-    <row r="199" spans="1:33">
+    <row r="199" spans="1:32">
       <c r="A199" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B199" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C199" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D199" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E199">
         <v>2023</v>
@@ -18658,18 +18523,18 @@
         <v>82.48999999999999</v>
       </c>
     </row>
-    <row r="200" spans="1:33">
+    <row r="200" spans="1:32">
       <c r="A200" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B200" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C200" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D200" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E200">
         <v>2015</v>
@@ -18752,22 +18617,19 @@
       <c r="AF200">
         <v>18.3681968714647</v>
       </c>
-      <c r="AG200">
-        <v>250.9</v>
-      </c>
-    </row>
-    <row r="201" spans="1:33">
+    </row>
+    <row r="201" spans="1:32">
       <c r="A201" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B201" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C201" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D201" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E201">
         <v>2016</v>
@@ -18850,22 +18712,19 @@
       <c r="AF201">
         <v>19.1915888785393</v>
       </c>
-      <c r="AG201">
-        <v>303.7</v>
-      </c>
-    </row>
-    <row r="202" spans="1:33">
+    </row>
+    <row r="202" spans="1:32">
       <c r="A202" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B202" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C202" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D202" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E202">
         <v>2017</v>
@@ -18948,22 +18807,19 @@
       <c r="AF202">
         <v>19.4469058462512</v>
       </c>
-      <c r="AG202">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="203" spans="1:33">
+    </row>
+    <row r="203" spans="1:32">
       <c r="A203" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B203" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C203" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D203" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E203">
         <v>2018</v>
@@ -19046,22 +18902,19 @@
       <c r="AF203">
         <v>18.3342427407296</v>
       </c>
-      <c r="AG203">
-        <v>272.2</v>
-      </c>
-    </row>
-    <row r="204" spans="1:33">
+    </row>
+    <row r="204" spans="1:32">
       <c r="A204" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B204" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C204" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D204" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E204">
         <v>2019</v>
@@ -19147,22 +19000,19 @@
       <c r="AF204">
         <v>18.5191670625259</v>
       </c>
-      <c r="AG204">
-        <v>318.3</v>
-      </c>
-    </row>
-    <row r="205" spans="1:33">
+    </row>
+    <row r="205" spans="1:32">
       <c r="A205" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B205" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C205" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D205" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E205">
         <v>2020</v>
@@ -19248,22 +19098,19 @@
       <c r="AF205">
         <v>18.6445328298003</v>
       </c>
-      <c r="AG205">
-        <v>474.5</v>
-      </c>
-    </row>
-    <row r="206" spans="1:33">
+    </row>
+    <row r="206" spans="1:32">
       <c r="A206" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B206" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C206" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D206" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E206">
         <v>2021</v>
@@ -19349,22 +19196,19 @@
       <c r="AF206">
         <v>18.3430886486889</v>
       </c>
-      <c r="AG206">
-        <v>354.2</v>
-      </c>
-    </row>
-    <row r="207" spans="1:33">
+    </row>
+    <row r="207" spans="1:32">
       <c r="A207" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B207" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C207" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D207" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E207">
         <v>2022</v>
@@ -19450,22 +19294,19 @@
       <c r="AF207">
         <v>19.2711611449441</v>
       </c>
-      <c r="AG207">
-        <v>403.8</v>
-      </c>
-    </row>
-    <row r="208" spans="1:33">
+    </row>
+    <row r="208" spans="1:32">
       <c r="A208" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B208" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C208" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D208" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E208">
         <v>2023</v>
@@ -19551,22 +19392,19 @@
       <c r="AF208">
         <v>19.0449981034342</v>
       </c>
-      <c r="AG208">
-        <v>377.3</v>
-      </c>
     </row>
     <row r="209" spans="1:32">
       <c r="A209" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B209" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C209" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D209" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E209">
         <v>2015</v>
@@ -19652,16 +19490,16 @@
     </row>
     <row r="210" spans="1:32">
       <c r="A210" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B210" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C210" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D210" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E210">
         <v>2016</v>
@@ -19747,16 +19585,16 @@
     </row>
     <row r="211" spans="1:32">
       <c r="A211" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B211" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C211" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D211" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E211">
         <v>2017</v>
@@ -19842,16 +19680,16 @@
     </row>
     <row r="212" spans="1:32">
       <c r="A212" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B212" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C212" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D212" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E212">
         <v>2018</v>
@@ -19937,16 +19775,16 @@
     </row>
     <row r="213" spans="1:32">
       <c r="A213" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B213" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C213" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D213" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E213">
         <v>2019</v>
@@ -20032,16 +19870,16 @@
     </row>
     <row r="214" spans="1:32">
       <c r="A214" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B214" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C214" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D214" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E214">
         <v>2020</v>
@@ -20127,16 +19965,16 @@
     </row>
     <row r="215" spans="1:32">
       <c r="A215" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B215" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C215" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D215" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E215">
         <v>2021</v>
@@ -20222,16 +20060,16 @@
     </row>
     <row r="216" spans="1:32">
       <c r="A216" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B216" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C216" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D216" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E216">
         <v>2022</v>
@@ -20317,16 +20155,16 @@
     </row>
     <row r="217" spans="1:32">
       <c r="A217" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B217" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C217" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D217" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E217">
         <v>2023</v>
@@ -20412,16 +20250,16 @@
     </row>
     <row r="218" spans="1:32">
       <c r="A218" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B218" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C218" t="s">
+        <v>100</v>
+      </c>
+      <c r="D218" t="s">
         <v>101</v>
-      </c>
-      <c r="D218" t="s">
-        <v>102</v>
       </c>
       <c r="E218">
         <v>2015</v>
@@ -20507,16 +20345,16 @@
     </row>
     <row r="219" spans="1:32">
       <c r="A219" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B219" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C219" t="s">
+        <v>100</v>
+      </c>
+      <c r="D219" t="s">
         <v>101</v>
-      </c>
-      <c r="D219" t="s">
-        <v>102</v>
       </c>
       <c r="E219">
         <v>2016</v>
@@ -20602,16 +20440,16 @@
     </row>
     <row r="220" spans="1:32">
       <c r="A220" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B220" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C220" t="s">
+        <v>100</v>
+      </c>
+      <c r="D220" t="s">
         <v>101</v>
-      </c>
-      <c r="D220" t="s">
-        <v>102</v>
       </c>
       <c r="E220">
         <v>2017</v>
@@ -20697,16 +20535,16 @@
     </row>
     <row r="221" spans="1:32">
       <c r="A221" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B221" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C221" t="s">
+        <v>100</v>
+      </c>
+      <c r="D221" t="s">
         <v>101</v>
-      </c>
-      <c r="D221" t="s">
-        <v>102</v>
       </c>
       <c r="E221">
         <v>2018</v>
@@ -20792,16 +20630,16 @@
     </row>
     <row r="222" spans="1:32">
       <c r="A222" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B222" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C222" t="s">
+        <v>100</v>
+      </c>
+      <c r="D222" t="s">
         <v>101</v>
-      </c>
-      <c r="D222" t="s">
-        <v>102</v>
       </c>
       <c r="E222">
         <v>2019</v>
@@ -20887,16 +20725,16 @@
     </row>
     <row r="223" spans="1:32">
       <c r="A223" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B223" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C223" t="s">
+        <v>100</v>
+      </c>
+      <c r="D223" t="s">
         <v>101</v>
-      </c>
-      <c r="D223" t="s">
-        <v>102</v>
       </c>
       <c r="E223">
         <v>2020</v>
@@ -20982,16 +20820,16 @@
     </row>
     <row r="224" spans="1:32">
       <c r="A224" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B224" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C224" t="s">
+        <v>100</v>
+      </c>
+      <c r="D224" t="s">
         <v>101</v>
-      </c>
-      <c r="D224" t="s">
-        <v>102</v>
       </c>
       <c r="E224">
         <v>2021</v>
@@ -21075,18 +20913,18 @@
         <v>11.1554031256111</v>
       </c>
     </row>
-    <row r="225" spans="1:33">
+    <row r="225" spans="1:32">
       <c r="A225" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B225" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C225" t="s">
+        <v>100</v>
+      </c>
+      <c r="D225" t="s">
         <v>101</v>
-      </c>
-      <c r="D225" t="s">
-        <v>102</v>
       </c>
       <c r="E225">
         <v>2022</v>
@@ -21164,18 +21002,18 @@
         <v>100.93</v>
       </c>
     </row>
-    <row r="226" spans="1:33">
+    <row r="226" spans="1:32">
       <c r="A226" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B226" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C226" t="s">
+        <v>100</v>
+      </c>
+      <c r="D226" t="s">
         <v>101</v>
-      </c>
-      <c r="D226" t="s">
-        <v>102</v>
       </c>
       <c r="E226">
         <v>2023</v>
@@ -21253,18 +21091,18 @@
         <v>82.48999999999999</v>
       </c>
     </row>
-    <row r="227" spans="1:33">
+    <row r="227" spans="1:32">
       <c r="A227" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B227" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C227" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D227" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E227">
         <v>2015</v>
@@ -21350,22 +21188,19 @@
       <c r="AF227">
         <v>19.679565807863</v>
       </c>
-      <c r="AG227">
-        <v>200.7</v>
-      </c>
-    </row>
-    <row r="228" spans="1:33">
+    </row>
+    <row r="228" spans="1:32">
       <c r="A228" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B228" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C228" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D228" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E228">
         <v>2016</v>
@@ -21451,22 +21286,19 @@
       <c r="AF228">
         <v>18.2765652206734</v>
       </c>
-      <c r="AG228">
-        <v>199.9</v>
-      </c>
-    </row>
-    <row r="229" spans="1:33">
+    </row>
+    <row r="229" spans="1:32">
       <c r="A229" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B229" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C229" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D229" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E229">
         <v>2017</v>
@@ -21552,22 +21384,19 @@
       <c r="AF229">
         <v>17.8234033989894</v>
       </c>
-      <c r="AG229">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="230" spans="1:33">
+    </row>
+    <row r="230" spans="1:32">
       <c r="A230" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B230" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C230" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D230" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E230">
         <v>2018</v>
@@ -21653,22 +21482,19 @@
       <c r="AF230">
         <v>19.0379642707319</v>
       </c>
-      <c r="AG230">
-        <v>147.2</v>
-      </c>
-    </row>
-    <row r="231" spans="1:33">
+    </row>
+    <row r="231" spans="1:32">
       <c r="A231" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B231" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C231" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D231" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E231">
         <v>2019</v>
@@ -21754,22 +21580,19 @@
       <c r="AF231">
         <v>19.5290026661565</v>
       </c>
-      <c r="AG231">
-        <v>128.7</v>
-      </c>
-    </row>
-    <row r="232" spans="1:33">
+    </row>
+    <row r="232" spans="1:32">
       <c r="A232" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B232" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C232" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D232" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E232">
         <v>2020</v>
@@ -21855,22 +21678,19 @@
       <c r="AF232">
         <v>18.0501223065786</v>
       </c>
-      <c r="AG232">
-        <v>173.4</v>
-      </c>
-    </row>
-    <row r="233" spans="1:33">
+    </row>
+    <row r="233" spans="1:32">
       <c r="A233" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B233" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C233" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D233" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E233">
         <v>2021</v>
@@ -21956,22 +21776,19 @@
       <c r="AF233">
         <v>20.6771966687553</v>
       </c>
-      <c r="AG233">
-        <v>165.4</v>
-      </c>
-    </row>
-    <row r="234" spans="1:33">
+    </row>
+    <row r="234" spans="1:32">
       <c r="A234" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B234" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C234" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D234" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E234">
         <v>2022</v>
@@ -22048,22 +21865,19 @@
       <c r="AC234">
         <v>100.93</v>
       </c>
-      <c r="AG234">
-        <v>208.9</v>
-      </c>
-    </row>
-    <row r="235" spans="1:33">
+    </row>
+    <row r="235" spans="1:32">
       <c r="A235" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B235" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C235" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D235" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E235">
         <v>2023</v>
@@ -22140,22 +21954,19 @@
       <c r="AC235">
         <v>82.48999999999999</v>
       </c>
-      <c r="AG235">
-        <v>183.9</v>
-      </c>
-    </row>
-    <row r="236" spans="1:33">
+    </row>
+    <row r="236" spans="1:32">
       <c r="A236" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B236" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C236" t="s">
+        <v>100</v>
+      </c>
+      <c r="D236" t="s">
         <v>101</v>
-      </c>
-      <c r="D236" t="s">
-        <v>102</v>
       </c>
       <c r="E236">
         <v>2015</v>
@@ -22209,18 +22020,18 @@
         <v>52.32</v>
       </c>
     </row>
-    <row r="237" spans="1:33">
+    <row r="237" spans="1:32">
       <c r="A237" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B237" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C237" t="s">
+        <v>100</v>
+      </c>
+      <c r="D237" t="s">
         <v>101</v>
-      </c>
-      <c r="D237" t="s">
-        <v>102</v>
       </c>
       <c r="E237">
         <v>2016</v>
@@ -22274,18 +22085,18 @@
         <v>43.64</v>
       </c>
     </row>
-    <row r="238" spans="1:33">
+    <row r="238" spans="1:32">
       <c r="A238" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B238" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C238" t="s">
+        <v>100</v>
+      </c>
+      <c r="D238" t="s">
         <v>101</v>
-      </c>
-      <c r="D238" t="s">
-        <v>102</v>
       </c>
       <c r="E238">
         <v>2017</v>
@@ -22339,18 +22150,18 @@
         <v>54.13</v>
       </c>
     </row>
-    <row r="239" spans="1:33">
+    <row r="239" spans="1:32">
       <c r="A239" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B239" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C239" t="s">
+        <v>100</v>
+      </c>
+      <c r="D239" t="s">
         <v>101</v>
-      </c>
-      <c r="D239" t="s">
-        <v>102</v>
       </c>
       <c r="E239">
         <v>2018</v>
@@ -22410,18 +22221,18 @@
         <v>71.34</v>
       </c>
     </row>
-    <row r="240" spans="1:33">
+    <row r="240" spans="1:32">
       <c r="A240" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B240" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C240" t="s">
+        <v>100</v>
+      </c>
+      <c r="D240" t="s">
         <v>101</v>
-      </c>
-      <c r="D240" t="s">
-        <v>102</v>
       </c>
       <c r="E240">
         <v>2019</v>
@@ -22483,16 +22294,16 @@
     </row>
     <row r="241" spans="1:32">
       <c r="A241" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B241" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C241" t="s">
+        <v>100</v>
+      </c>
+      <c r="D241" t="s">
         <v>101</v>
-      </c>
-      <c r="D241" t="s">
-        <v>102</v>
       </c>
       <c r="E241">
         <v>2020</v>
@@ -22554,16 +22365,16 @@
     </row>
     <row r="242" spans="1:32">
       <c r="A242" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B242" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C242" t="s">
+        <v>100</v>
+      </c>
+      <c r="D242" t="s">
         <v>101</v>
-      </c>
-      <c r="D242" t="s">
-        <v>102</v>
       </c>
       <c r="E242">
         <v>2021</v>
@@ -22619,16 +22430,16 @@
     </row>
     <row r="243" spans="1:32">
       <c r="A243" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B243" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C243" t="s">
+        <v>100</v>
+      </c>
+      <c r="D243" t="s">
         <v>101</v>
-      </c>
-      <c r="D243" t="s">
-        <v>102</v>
       </c>
       <c r="E243">
         <v>2022</v>
@@ -22684,16 +22495,16 @@
     </row>
     <row r="244" spans="1:32">
       <c r="A244" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B244" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C244" t="s">
+        <v>100</v>
+      </c>
+      <c r="D244" t="s">
         <v>101</v>
-      </c>
-      <c r="D244" t="s">
-        <v>102</v>
       </c>
       <c r="E244">
         <v>2023</v>
@@ -22749,16 +22560,16 @@
     </row>
     <row r="245" spans="1:32">
       <c r="A245" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B245" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C245" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D245" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E245">
         <v>2015</v>
@@ -22844,16 +22655,16 @@
     </row>
     <row r="246" spans="1:32">
       <c r="A246" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B246" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C246" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D246" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E246">
         <v>2016</v>
@@ -22939,16 +22750,16 @@
     </row>
     <row r="247" spans="1:32">
       <c r="A247" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B247" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C247" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D247" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E247">
         <v>2017</v>
@@ -23034,16 +22845,16 @@
     </row>
     <row r="248" spans="1:32">
       <c r="A248" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B248" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C248" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D248" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E248">
         <v>2018</v>
@@ -23129,16 +22940,16 @@
     </row>
     <row r="249" spans="1:32">
       <c r="A249" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B249" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C249" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D249" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E249">
         <v>2019</v>
@@ -23224,16 +23035,16 @@
     </row>
     <row r="250" spans="1:32">
       <c r="A250" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B250" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C250" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D250" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E250">
         <v>2020</v>
@@ -23319,16 +23130,16 @@
     </row>
     <row r="251" spans="1:32">
       <c r="A251" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B251" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C251" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D251" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E251">
         <v>2021</v>
@@ -23414,16 +23225,16 @@
     </row>
     <row r="252" spans="1:32">
       <c r="A252" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B252" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C252" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D252" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E252">
         <v>2022</v>
@@ -23509,16 +23320,16 @@
     </row>
     <row r="253" spans="1:32">
       <c r="A253" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B253" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C253" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D253" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E253">
         <v>2023</v>
@@ -23604,16 +23415,16 @@
     </row>
     <row r="254" spans="1:32">
       <c r="A254" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B254" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C254" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D254" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E254">
         <v>2015</v>
@@ -23702,16 +23513,16 @@
     </row>
     <row r="255" spans="1:32">
       <c r="A255" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B255" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C255" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D255" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E255">
         <v>2016</v>
@@ -23800,16 +23611,16 @@
     </row>
     <row r="256" spans="1:32">
       <c r="A256" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B256" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C256" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D256" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E256">
         <v>2017</v>
@@ -23898,16 +23709,16 @@
     </row>
     <row r="257" spans="1:32">
       <c r="A257" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B257" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C257" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D257" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E257">
         <v>2018</v>
@@ -23996,16 +23807,16 @@
     </row>
     <row r="258" spans="1:32">
       <c r="A258" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B258" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C258" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D258" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E258">
         <v>2019</v>
@@ -24094,16 +23905,16 @@
     </row>
     <row r="259" spans="1:32">
       <c r="A259" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B259" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C259" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D259" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E259">
         <v>2020</v>
@@ -24192,16 +24003,16 @@
     </row>
     <row r="260" spans="1:32">
       <c r="A260" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B260" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C260" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D260" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E260">
         <v>2021</v>
@@ -24290,16 +24101,16 @@
     </row>
     <row r="261" spans="1:32">
       <c r="A261" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B261" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C261" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D261" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E261">
         <v>2022</v>
@@ -24388,16 +24199,16 @@
     </row>
     <row r="262" spans="1:32">
       <c r="A262" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B262" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C262" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D262" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E262">
         <v>2023</v>
@@ -24486,16 +24297,16 @@
     </row>
     <row r="263" spans="1:32">
       <c r="A263" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B263" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C263" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D263" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E263">
         <v>2015</v>
@@ -24557,16 +24368,16 @@
     </row>
     <row r="264" spans="1:32">
       <c r="A264" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B264" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C264" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D264" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E264">
         <v>2016</v>
@@ -24628,16 +24439,16 @@
     </row>
     <row r="265" spans="1:32">
       <c r="A265" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B265" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C265" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D265" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E265">
         <v>2017</v>
@@ -24699,16 +24510,16 @@
     </row>
     <row r="266" spans="1:32">
       <c r="A266" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B266" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C266" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D266" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E266">
         <v>2018</v>
@@ -24770,16 +24581,16 @@
     </row>
     <row r="267" spans="1:32">
       <c r="A267" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B267" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C267" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D267" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E267">
         <v>2019</v>
@@ -24841,16 +24652,16 @@
     </row>
     <row r="268" spans="1:32">
       <c r="A268" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B268" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C268" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D268" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E268">
         <v>2020</v>
@@ -24912,16 +24723,16 @@
     </row>
     <row r="269" spans="1:32">
       <c r="A269" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B269" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C269" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D269" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E269">
         <v>2021</v>
@@ -24977,16 +24788,16 @@
     </row>
     <row r="270" spans="1:32">
       <c r="A270" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B270" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C270" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D270" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E270">
         <v>2022</v>
@@ -25042,16 +24853,16 @@
     </row>
     <row r="271" spans="1:32">
       <c r="A271" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B271" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C271" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D271" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E271">
         <v>2023</v>
@@ -25107,16 +24918,16 @@
     </row>
     <row r="272" spans="1:32">
       <c r="A272" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B272" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C272" t="s">
+        <v>100</v>
+      </c>
+      <c r="D272" t="s">
         <v>101</v>
-      </c>
-      <c r="D272" t="s">
-        <v>102</v>
       </c>
       <c r="E272">
         <v>2015</v>
@@ -25202,16 +25013,16 @@
     </row>
     <row r="273" spans="1:32">
       <c r="A273" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B273" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C273" t="s">
+        <v>100</v>
+      </c>
+      <c r="D273" t="s">
         <v>101</v>
-      </c>
-      <c r="D273" t="s">
-        <v>102</v>
       </c>
       <c r="E273">
         <v>2016</v>
@@ -25297,16 +25108,16 @@
     </row>
     <row r="274" spans="1:32">
       <c r="A274" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B274" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C274" t="s">
+        <v>100</v>
+      </c>
+      <c r="D274" t="s">
         <v>101</v>
-      </c>
-      <c r="D274" t="s">
-        <v>102</v>
       </c>
       <c r="E274">
         <v>2017</v>
@@ -25392,16 +25203,16 @@
     </row>
     <row r="275" spans="1:32">
       <c r="A275" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B275" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C275" t="s">
+        <v>100</v>
+      </c>
+      <c r="D275" t="s">
         <v>101</v>
-      </c>
-      <c r="D275" t="s">
-        <v>102</v>
       </c>
       <c r="E275">
         <v>2018</v>
@@ -25487,16 +25298,16 @@
     </row>
     <row r="276" spans="1:32">
       <c r="A276" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B276" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C276" t="s">
+        <v>100</v>
+      </c>
+      <c r="D276" t="s">
         <v>101</v>
-      </c>
-      <c r="D276" t="s">
-        <v>102</v>
       </c>
       <c r="E276">
         <v>2019</v>
@@ -25582,16 +25393,16 @@
     </row>
     <row r="277" spans="1:32">
       <c r="A277" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B277" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C277" t="s">
+        <v>100</v>
+      </c>
+      <c r="D277" t="s">
         <v>101</v>
-      </c>
-      <c r="D277" t="s">
-        <v>102</v>
       </c>
       <c r="E277">
         <v>2020</v>
@@ -25671,16 +25482,16 @@
     </row>
     <row r="278" spans="1:32">
       <c r="A278" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B278" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C278" t="s">
+        <v>100</v>
+      </c>
+      <c r="D278" t="s">
         <v>101</v>
-      </c>
-      <c r="D278" t="s">
-        <v>102</v>
       </c>
       <c r="E278">
         <v>2021</v>
@@ -25760,16 +25571,16 @@
     </row>
     <row r="279" spans="1:32">
       <c r="A279" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B279" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C279" t="s">
+        <v>100</v>
+      </c>
+      <c r="D279" t="s">
         <v>101</v>
-      </c>
-      <c r="D279" t="s">
-        <v>102</v>
       </c>
       <c r="E279">
         <v>2022</v>
@@ -25849,16 +25660,16 @@
     </row>
     <row r="280" spans="1:32">
       <c r="A280" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B280" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C280" t="s">
+        <v>100</v>
+      </c>
+      <c r="D280" t="s">
         <v>101</v>
-      </c>
-      <c r="D280" t="s">
-        <v>102</v>
       </c>
       <c r="E280">
         <v>2023</v>
@@ -25938,16 +25749,16 @@
     </row>
     <row r="281" spans="1:32">
       <c r="A281" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B281" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C281" t="s">
+        <v>100</v>
+      </c>
+      <c r="D281" t="s">
         <v>101</v>
-      </c>
-      <c r="D281" t="s">
-        <v>102</v>
       </c>
       <c r="E281">
         <v>2015</v>
@@ -26033,16 +25844,16 @@
     </row>
     <row r="282" spans="1:32">
       <c r="A282" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B282" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C282" t="s">
+        <v>100</v>
+      </c>
+      <c r="D282" t="s">
         <v>101</v>
-      </c>
-      <c r="D282" t="s">
-        <v>102</v>
       </c>
       <c r="E282">
         <v>2016</v>
@@ -26128,16 +25939,16 @@
     </row>
     <row r="283" spans="1:32">
       <c r="A283" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B283" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C283" t="s">
+        <v>100</v>
+      </c>
+      <c r="D283" t="s">
         <v>101</v>
-      </c>
-      <c r="D283" t="s">
-        <v>102</v>
       </c>
       <c r="E283">
         <v>2017</v>
@@ -26223,16 +26034,16 @@
     </row>
     <row r="284" spans="1:32">
       <c r="A284" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B284" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C284" t="s">
+        <v>100</v>
+      </c>
+      <c r="D284" t="s">
         <v>101</v>
-      </c>
-      <c r="D284" t="s">
-        <v>102</v>
       </c>
       <c r="E284">
         <v>2018</v>
@@ -26318,16 +26129,16 @@
     </row>
     <row r="285" spans="1:32">
       <c r="A285" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B285" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C285" t="s">
+        <v>100</v>
+      </c>
+      <c r="D285" t="s">
         <v>101</v>
-      </c>
-      <c r="D285" t="s">
-        <v>102</v>
       </c>
       <c r="E285">
         <v>2019</v>
@@ -26413,16 +26224,16 @@
     </row>
     <row r="286" spans="1:32">
       <c r="A286" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B286" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C286" t="s">
+        <v>100</v>
+      </c>
+      <c r="D286" t="s">
         <v>101</v>
-      </c>
-      <c r="D286" t="s">
-        <v>102</v>
       </c>
       <c r="E286">
         <v>2020</v>
@@ -26508,16 +26319,16 @@
     </row>
     <row r="287" spans="1:32">
       <c r="A287" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B287" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C287" t="s">
+        <v>100</v>
+      </c>
+      <c r="D287" t="s">
         <v>101</v>
-      </c>
-      <c r="D287" t="s">
-        <v>102</v>
       </c>
       <c r="E287">
         <v>2021</v>
@@ -26603,16 +26414,16 @@
     </row>
     <row r="288" spans="1:32">
       <c r="A288" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B288" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C288" t="s">
+        <v>100</v>
+      </c>
+      <c r="D288" t="s">
         <v>101</v>
-      </c>
-      <c r="D288" t="s">
-        <v>102</v>
       </c>
       <c r="E288">
         <v>2022</v>
@@ -26696,18 +26507,18 @@
         <v>29.6888696320693</v>
       </c>
     </row>
-    <row r="289" spans="1:33">
+    <row r="289" spans="1:32">
       <c r="A289" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B289" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C289" t="s">
+        <v>100</v>
+      </c>
+      <c r="D289" t="s">
         <v>101</v>
-      </c>
-      <c r="D289" t="s">
-        <v>102</v>
       </c>
       <c r="E289">
         <v>2023</v>
@@ -26791,18 +26602,18 @@
         <v>30.8302778846325</v>
       </c>
     </row>
-    <row r="290" spans="1:33">
+    <row r="290" spans="1:32">
       <c r="A290" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B290" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C290" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D290" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E290">
         <v>2015</v>
@@ -26886,18 +26697,18 @@
         <v>24.4295333615859</v>
       </c>
     </row>
-    <row r="291" spans="1:33">
+    <row r="291" spans="1:32">
       <c r="A291" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B291" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C291" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D291" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E291">
         <v>2016</v>
@@ -26981,18 +26792,18 @@
         <v>26.9523610264621</v>
       </c>
     </row>
-    <row r="292" spans="1:33">
+    <row r="292" spans="1:32">
       <c r="A292" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B292" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C292" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D292" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E292">
         <v>2017</v>
@@ -27076,18 +26887,18 @@
         <v>25.5657309854272</v>
       </c>
     </row>
-    <row r="293" spans="1:33">
+    <row r="293" spans="1:32">
       <c r="A293" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B293" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C293" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D293" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E293">
         <v>2018</v>
@@ -27165,18 +26976,18 @@
         <v>71.34</v>
       </c>
     </row>
-    <row r="294" spans="1:33">
+    <row r="294" spans="1:32">
       <c r="A294" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B294" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C294" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D294" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E294">
         <v>2019</v>
@@ -27254,18 +27065,18 @@
         <v>64.3</v>
       </c>
     </row>
-    <row r="295" spans="1:33">
+    <row r="295" spans="1:32">
       <c r="A295" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B295" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C295" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D295" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E295">
         <v>2020</v>
@@ -27343,18 +27154,18 @@
         <v>41.96</v>
       </c>
     </row>
-    <row r="296" spans="1:33">
+    <row r="296" spans="1:32">
       <c r="A296" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B296" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C296" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D296" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E296">
         <v>2021</v>
@@ -27432,18 +27243,18 @@
         <v>70.86</v>
       </c>
     </row>
-    <row r="297" spans="1:33">
+    <row r="297" spans="1:32">
       <c r="A297" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B297" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C297" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D297" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E297">
         <v>2022</v>
@@ -27521,18 +27332,18 @@
         <v>100.93</v>
       </c>
     </row>
-    <row r="298" spans="1:33">
+    <row r="298" spans="1:32">
       <c r="A298" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B298" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C298" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D298" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E298">
         <v>2023</v>
@@ -27610,18 +27421,18 @@
         <v>82.48999999999999</v>
       </c>
     </row>
-    <row r="299" spans="1:33">
+    <row r="299" spans="1:32">
       <c r="A299" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B299" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C299" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D299" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E299">
         <v>2015</v>
@@ -27698,22 +27509,19 @@
       <c r="AC299">
         <v>52.32</v>
       </c>
-      <c r="AG299">
-        <v>2772.3</v>
-      </c>
-    </row>
-    <row r="300" spans="1:33">
+    </row>
+    <row r="300" spans="1:32">
       <c r="A300" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B300" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C300" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D300" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E300">
         <v>2016</v>
@@ -27790,22 +27598,19 @@
       <c r="AC300">
         <v>43.64</v>
       </c>
-      <c r="AG300">
-        <v>2750.6</v>
-      </c>
-    </row>
-    <row r="301" spans="1:33">
+    </row>
+    <row r="301" spans="1:32">
       <c r="A301" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B301" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C301" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D301" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E301">
         <v>2017</v>
@@ -27882,22 +27687,19 @@
       <c r="AC301">
         <v>54.13</v>
       </c>
-      <c r="AG301">
-        <v>2845</v>
-      </c>
-    </row>
-    <row r="302" spans="1:33">
+    </row>
+    <row r="302" spans="1:32">
       <c r="A302" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B302" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C302" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D302" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E302">
         <v>2018</v>
@@ -27974,22 +27776,19 @@
       <c r="AC302">
         <v>71.34</v>
       </c>
-      <c r="AG302">
-        <v>5162.6</v>
-      </c>
-    </row>
-    <row r="303" spans="1:33">
+    </row>
+    <row r="303" spans="1:32">
       <c r="A303" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B303" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C303" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D303" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E303">
         <v>2019</v>
@@ -28066,22 +27865,19 @@
       <c r="AC303">
         <v>64.3</v>
       </c>
-      <c r="AG303">
-        <v>9828.5</v>
-      </c>
-    </row>
-    <row r="304" spans="1:33">
+    </row>
+    <row r="304" spans="1:32">
       <c r="A304" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B304" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C304" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D304" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E304">
         <v>2020</v>
@@ -28158,22 +27954,19 @@
       <c r="AC304">
         <v>41.96</v>
       </c>
-      <c r="AG304">
-        <v>23796.5</v>
-      </c>
-    </row>
-    <row r="305" spans="1:33">
+    </row>
+    <row r="305" spans="1:29">
       <c r="A305" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B305" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C305" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D305" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E305">
         <v>2021</v>
@@ -28250,22 +28043,19 @@
       <c r="AC305">
         <v>70.86</v>
       </c>
-      <c r="AG305">
-        <v>29062</v>
-      </c>
-    </row>
-    <row r="306" spans="1:33">
+    </row>
+    <row r="306" spans="1:29">
       <c r="A306" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B306" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C306" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D306" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E306">
         <v>2022</v>
@@ -28342,22 +28132,19 @@
       <c r="AC306">
         <v>100.93</v>
       </c>
-      <c r="AG306">
-        <v>41978.9</v>
-      </c>
-    </row>
-    <row r="307" spans="1:33">
+    </row>
+    <row r="307" spans="1:29">
       <c r="A307" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B307" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C307" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D307" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E307">
         <v>2023</v>
@@ -28433,9 +28220,6 @@
       </c>
       <c r="AC307">
         <v>82.48999999999999</v>
-      </c>
-      <c r="AG307">
-        <v>35109.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/panel_base.xlsx
+++ b/data/processed/panel_base.xlsx
@@ -857,6 +857,15 @@
       <c r="AC2">
         <v>52.32</v>
       </c>
+      <c r="AD2">
+        <v>-1.5</v>
+      </c>
+      <c r="AE2">
+        <v>74.2</v>
+      </c>
+      <c r="AF2">
+        <v>23.897997199527</v>
+      </c>
     </row>
     <row r="3" spans="1:32">
       <c r="A3" t="s">
@@ -928,6 +937,15 @@
       <c r="AC3">
         <v>43.64</v>
       </c>
+      <c r="AD3">
+        <v>-1.5</v>
+      </c>
+      <c r="AE3">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AF3">
+        <v>23.664061083824</v>
+      </c>
     </row>
     <row r="4" spans="1:32">
       <c r="A4" t="s">
@@ -999,6 +1017,15 @@
       <c r="AC4">
         <v>54.13</v>
       </c>
+      <c r="AD4">
+        <v>-2.6</v>
+      </c>
+      <c r="AE4">
+        <v>75.8</v>
+      </c>
+      <c r="AF4">
+        <v>21.971289135942</v>
+      </c>
     </row>
     <row r="5" spans="1:32">
       <c r="A5" t="s">
@@ -1070,6 +1097,15 @@
       <c r="AC5">
         <v>71.34</v>
       </c>
+      <c r="AD5">
+        <v>-2.6</v>
+      </c>
+      <c r="AE5">
+        <v>73.3</v>
+      </c>
+      <c r="AF5">
+        <v>22.221713107356</v>
+      </c>
     </row>
     <row r="6" spans="1:32">
       <c r="A6" t="s">
@@ -1141,6 +1177,15 @@
       <c r="AC6">
         <v>64.3</v>
       </c>
+      <c r="AD6">
+        <v>-0.2</v>
+      </c>
+      <c r="AE6">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AF6">
+        <v>23.789750239214</v>
+      </c>
     </row>
     <row r="7" spans="1:32">
       <c r="A7" t="s">
@@ -1212,6 +1257,15 @@
       <c r="AC7">
         <v>41.96</v>
       </c>
+      <c r="AD7">
+        <v>-16.8</v>
+      </c>
+      <c r="AE7">
+        <v>116.3</v>
+      </c>
+      <c r="AF7">
+        <v>24.856368048573</v>
+      </c>
     </row>
     <row r="8" spans="1:32">
       <c r="A8" t="s">
@@ -1277,6 +1331,15 @@
       <c r="AC8">
         <v>70.86</v>
       </c>
+      <c r="AD8">
+        <v>-9.9</v>
+      </c>
+      <c r="AE8">
+        <v>109.7</v>
+      </c>
+      <c r="AF8">
+        <v>21.217848834359</v>
+      </c>
     </row>
     <row r="9" spans="1:32">
       <c r="A9" t="s">
@@ -1342,6 +1405,15 @@
       <c r="AC9">
         <v>100.93</v>
       </c>
+      <c r="AD9">
+        <v>-0.5</v>
+      </c>
+      <c r="AE9">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="AF9">
+        <v>22.622022465937</v>
+      </c>
     </row>
     <row r="10" spans="1:32">
       <c r="A10" t="s">
@@ -1407,6 +1479,15 @@
       <c r="AC10">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD10">
+        <v>3</v>
+      </c>
+      <c r="AE10">
+        <v>80.3</v>
+      </c>
+      <c r="AF10">
+        <v>24.821835133372</v>
+      </c>
     </row>
     <row r="11" spans="1:32">
       <c r="A11" t="s">
@@ -1497,10 +1578,13 @@
         <v>52.32</v>
       </c>
       <c r="AD11">
-        <v>-3.39011034719535</v>
+        <v>-6</v>
+      </c>
+      <c r="AE11">
+        <v>52.6</v>
       </c>
       <c r="AF11">
-        <v>22.1490803040164</v>
+        <v>35.365772019338</v>
       </c>
     </row>
     <row r="12" spans="1:32">
@@ -1592,10 +1676,13 @@
         <v>43.64</v>
       </c>
       <c r="AD12">
-        <v>-5.33377782706346</v>
+        <v>-6.7</v>
+      </c>
+      <c r="AE12">
+        <v>53.1</v>
       </c>
       <c r="AF12">
-        <v>21.2567013071388</v>
+        <v>34.8673516945</v>
       </c>
     </row>
     <row r="13" spans="1:32">
@@ -1687,10 +1774,13 @@
         <v>54.13</v>
       </c>
       <c r="AD13">
-        <v>-5.51824569508007</v>
+        <v>-6.7</v>
+      </c>
+      <c r="AE13">
+        <v>57</v>
       </c>
       <c r="AF13">
-        <v>19.3371239744582</v>
+        <v>34.428112889621</v>
       </c>
     </row>
     <row r="14" spans="1:32">
@@ -1782,10 +1872,13 @@
         <v>71.34</v>
       </c>
       <c r="AD14">
-        <v>-5.33635226717988</v>
+        <v>-5.4</v>
+      </c>
+      <c r="AE14">
+        <v>85.2</v>
       </c>
       <c r="AF14">
-        <v>17.7024488717292</v>
+        <v>33.508062809874</v>
       </c>
     </row>
     <row r="15" spans="1:32">
@@ -1877,10 +1970,13 @@
         <v>64.3</v>
       </c>
       <c r="AD15">
-        <v>-4.92889704924096</v>
+        <v>-4.4</v>
+      </c>
+      <c r="AE15">
+        <v>89.8</v>
       </c>
       <c r="AF15">
-        <v>17.7888990504455</v>
+        <v>33.684299956878</v>
       </c>
     </row>
     <row r="16" spans="1:32">
@@ -1972,10 +2068,13 @@
         <v>41.96</v>
       </c>
       <c r="AD16">
-        <v>-8.6954919523039</v>
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="AE16">
+        <v>103.8</v>
       </c>
       <c r="AF16">
-        <v>17.4777322783093</v>
+        <v>33.805168381982</v>
       </c>
     </row>
     <row r="17" spans="1:32">
@@ -2067,10 +2166,13 @@
         <v>70.86</v>
       </c>
       <c r="AD17">
-        <v>-4.37239542495983</v>
+        <v>-4.3</v>
+      </c>
+      <c r="AE17">
+        <v>81</v>
       </c>
       <c r="AF17">
-        <v>18.0764989044589</v>
+        <v>33.550413326565</v>
       </c>
     </row>
     <row r="18" spans="1:32">
@@ -2162,10 +2264,13 @@
         <v>100.93</v>
       </c>
       <c r="AD18">
-        <v>-4.42708731934181</v>
+        <v>-3.8</v>
+      </c>
+      <c r="AE18">
+        <v>84.3</v>
       </c>
       <c r="AF18">
-        <v>17.893195301026</v>
+        <v>33.806737762499</v>
       </c>
     </row>
     <row r="19" spans="1:32">
@@ -2257,10 +2362,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD19">
-        <v>-3.59487367618527</v>
+        <v>-5.3</v>
+      </c>
+      <c r="AE19">
+        <v>154.6</v>
       </c>
       <c r="AF19">
-        <v>17.7753274051522</v>
+        <v>32.307759101982</v>
       </c>
     </row>
     <row r="20" spans="1:32">
@@ -2333,6 +2441,15 @@
       <c r="AC20">
         <v>52.32</v>
       </c>
+      <c r="AD20">
+        <v>-2.4</v>
+      </c>
+      <c r="AE20">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="AF20">
+        <v>22.414317846999</v>
+      </c>
     </row>
     <row r="21" spans="1:32">
       <c r="A21" t="s">
@@ -2404,6 +2521,15 @@
       <c r="AC21">
         <v>43.64</v>
       </c>
+      <c r="AD21">
+        <v>-0.1</v>
+      </c>
+      <c r="AE21">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="AF21">
+        <v>23.640050741808</v>
+      </c>
     </row>
     <row r="22" spans="1:32">
       <c r="A22" t="s">
@@ -2475,6 +2601,15 @@
       <c r="AC22">
         <v>54.13</v>
       </c>
+      <c r="AD22">
+        <v>-2.7</v>
+      </c>
+      <c r="AE22">
+        <v>88.2</v>
+      </c>
+      <c r="AF22">
+        <v>19.833040146135</v>
+      </c>
     </row>
     <row r="23" spans="1:32">
       <c r="A23" t="s">
@@ -2546,6 +2681,15 @@
       <c r="AC23">
         <v>71.34</v>
       </c>
+      <c r="AD23">
+        <v>-2.4</v>
+      </c>
+      <c r="AE23">
+        <v>84.3</v>
+      </c>
+      <c r="AF23">
+        <v>19.108963704351</v>
+      </c>
     </row>
     <row r="24" spans="1:32">
       <c r="A24" t="s">
@@ -2617,6 +2761,15 @@
       <c r="AC24">
         <v>64.3</v>
       </c>
+      <c r="AD24">
+        <v>-3.6</v>
+      </c>
+      <c r="AE24">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="AF24">
+        <v>18.468756982544</v>
+      </c>
     </row>
     <row r="25" spans="1:32">
       <c r="A25" t="s">
@@ -2688,6 +2841,15 @@
       <c r="AC25">
         <v>41.96</v>
       </c>
+      <c r="AD25">
+        <v>-6.2</v>
+      </c>
+      <c r="AE25">
+        <v>100.5</v>
+      </c>
+      <c r="AF25">
+        <v>19.750362974167</v>
+      </c>
     </row>
     <row r="26" spans="1:32">
       <c r="A26" t="s">
@@ -2777,6 +2939,15 @@
       <c r="AC26">
         <v>70.86</v>
       </c>
+      <c r="AD26">
+        <v>-4.5</v>
+      </c>
+      <c r="AE26">
+        <v>93</v>
+      </c>
+      <c r="AF26">
+        <v>18.86600842353</v>
+      </c>
     </row>
     <row r="27" spans="1:32">
       <c r="A27" t="s">
@@ -2866,6 +3037,15 @@
       <c r="AC27">
         <v>100.93</v>
       </c>
+      <c r="AD27">
+        <v>-2.9</v>
+      </c>
+      <c r="AE27">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="AF27">
+        <v>17.952924823252</v>
+      </c>
     </row>
     <row r="28" spans="1:32">
       <c r="A28" t="s">
@@ -2955,6 +3135,15 @@
       <c r="AC28">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD28">
+        <v>-1.7</v>
+      </c>
+      <c r="AE28">
+        <v>74.5</v>
+      </c>
+      <c r="AF28">
+        <v>16.695326097626</v>
+      </c>
     </row>
     <row r="29" spans="1:32">
       <c r="A29" t="s">
@@ -3045,13 +3234,13 @@
         <v>52.32</v>
       </c>
       <c r="AD29">
-        <v>-3.23821987412989</v>
+        <v>-3.3</v>
       </c>
       <c r="AE29">
-        <v>47.6225079407988</v>
+        <v>49.9</v>
       </c>
       <c r="AF29">
-        <v>14.6273782452524</v>
+        <v>15.075230484807</v>
       </c>
     </row>
     <row r="30" spans="1:32">
@@ -3143,13 +3332,13 @@
         <v>43.64</v>
       </c>
       <c r="AD30">
-        <v>-2.60907980439192</v>
+        <v>-2.6</v>
       </c>
       <c r="AE30">
-        <v>50.2046646297839</v>
+        <v>51.1</v>
       </c>
       <c r="AF30">
-        <v>16.7435935230496</v>
+        <v>16.747317985643</v>
       </c>
     </row>
     <row r="31" spans="1:32">
@@ -3241,13 +3430,13 @@
         <v>54.13</v>
       </c>
       <c r="AD31">
-        <v>-5.3083648775197</v>
+        <v>-6.1</v>
       </c>
       <c r="AE31">
-        <v>52.624565152769</v>
+        <v>54.6</v>
       </c>
       <c r="AF31">
-        <v>16.6326878235545</v>
+        <v>17.012789412406</v>
       </c>
     </row>
     <row r="32" spans="1:32">
@@ -3339,13 +3528,13 @@
         <v>71.34</v>
       </c>
       <c r="AD32">
-        <v>-3.23645001248128</v>
+        <v>-3.3</v>
       </c>
       <c r="AE32">
-        <v>56.5027068771842</v>
+        <v>61.5</v>
       </c>
       <c r="AF32">
-        <v>15.9117105591613</v>
+        <v>16.162863402244</v>
       </c>
     </row>
     <row r="33" spans="1:32">
@@ -3437,13 +3626,13 @@
         <v>64.3</v>
       </c>
       <c r="AD33">
-        <v>-1.65181140317843</v>
+        <v>-1.7</v>
       </c>
       <c r="AE33">
-        <v>56.6924606462303</v>
+        <v>60.3</v>
       </c>
       <c r="AF33">
-        <v>18.2742562325827</v>
+        <v>18.589552140907</v>
       </c>
     </row>
     <row r="34" spans="1:32">
@@ -3535,13 +3724,13 @@
         <v>41.96</v>
       </c>
       <c r="AD34">
-        <v>-7.83218419986105</v>
+        <v>-7.1</v>
       </c>
       <c r="AE34">
-        <v>79.0414158203086</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AF34">
-        <v>20.1369104813185</v>
+        <v>17.651674669686</v>
       </c>
     </row>
     <row r="35" spans="1:32">
@@ -3633,13 +3822,13 @@
         <v>70.86</v>
       </c>
       <c r="AD35">
-        <v>-11.0938698263687</v>
+        <v>-11.9</v>
       </c>
       <c r="AE35">
-        <v>82.5398306524293</v>
+        <v>90.7</v>
       </c>
       <c r="AF35">
-        <v>15.8516580958711</v>
+        <v>17.020530658428</v>
       </c>
     </row>
     <row r="36" spans="1:32">
@@ -3731,13 +3920,13 @@
         <v>100.93</v>
       </c>
       <c r="AD36">
-        <v>-5.19361424932359</v>
+        <v>-5.5</v>
       </c>
       <c r="AE36">
-        <v>77.6639776530748</v>
+        <v>84.7</v>
       </c>
       <c r="AF36">
-        <v>18.7489017543607</v>
+        <v>20.097953833585</v>
       </c>
     </row>
     <row r="37" spans="1:32">
@@ -3829,13 +4018,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD37">
-        <v>-3.4954019304185</v>
+        <v>-3.7</v>
       </c>
       <c r="AE37">
-        <v>73.7303208143</v>
+        <v>78.3</v>
       </c>
       <c r="AF37">
-        <v>18.691039629894</v>
+        <v>19.565696801666</v>
       </c>
     </row>
     <row r="38" spans="1:32">
@@ -3927,10 +4116,13 @@
         <v>52.32</v>
       </c>
       <c r="AD38">
-        <v>-3.75341494678653</v>
+        <v>-5.1</v>
+      </c>
+      <c r="AE38">
+        <v>65.09999999999999</v>
       </c>
       <c r="AF38">
-        <v>22.1980924438071</v>
+        <v>22.804556916074</v>
       </c>
     </row>
     <row r="39" spans="1:32">
@@ -4022,10 +4214,13 @@
         <v>43.64</v>
       </c>
       <c r="AD39">
-        <v>-3.39757154965879</v>
+        <v>-4.5</v>
+      </c>
+      <c r="AE39">
+        <v>70.5</v>
       </c>
       <c r="AF39">
-        <v>22.4029818854459</v>
+        <v>23.1889107414</v>
       </c>
     </row>
     <row r="40" spans="1:32">
@@ -4117,10 +4312,13 @@
         <v>54.13</v>
       </c>
       <c r="AD40">
-        <v>-1.16349962472886</v>
+        <v>-3.5</v>
+      </c>
+      <c r="AE40">
+        <v>78.09999999999999</v>
       </c>
       <c r="AF40">
-        <v>23.8070928559695</v>
+        <v>24.188046292838</v>
       </c>
     </row>
     <row r="41" spans="1:32">
@@ -4211,6 +4409,15 @@
       <c r="AC41">
         <v>71.34</v>
       </c>
+      <c r="AD41">
+        <v>-1.4</v>
+      </c>
+      <c r="AE41">
+        <v>79</v>
+      </c>
+      <c r="AF41">
+        <v>25.564256569904</v>
+      </c>
     </row>
     <row r="42" spans="1:32">
       <c r="A42" t="s">
@@ -4300,6 +4507,15 @@
       <c r="AC42">
         <v>64.3</v>
       </c>
+      <c r="AD42">
+        <v>-2.9</v>
+      </c>
+      <c r="AE42">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="AF42">
+        <v>24.629948712771</v>
+      </c>
     </row>
     <row r="43" spans="1:32">
       <c r="A43" t="s">
@@ -4389,6 +4605,15 @@
       <c r="AC43">
         <v>41.96</v>
       </c>
+      <c r="AD43">
+        <v>-8.6</v>
+      </c>
+      <c r="AE43">
+        <v>103</v>
+      </c>
+      <c r="AF43">
+        <v>24.586732518503</v>
+      </c>
     </row>
     <row r="44" spans="1:32">
       <c r="A44" t="s">
@@ -4478,6 +4703,15 @@
       <c r="AC44">
         <v>70.86</v>
       </c>
+      <c r="AD44">
+        <v>-3.3</v>
+      </c>
+      <c r="AE44">
+        <v>82.2</v>
+      </c>
+      <c r="AF44">
+        <v>22.442181361961</v>
+      </c>
     </row>
     <row r="45" spans="1:32">
       <c r="A45" t="s">
@@ -4567,6 +4801,15 @@
       <c r="AC45">
         <v>100.93</v>
       </c>
+      <c r="AD45">
+        <v>-1</v>
+      </c>
+      <c r="AE45">
+        <v>66.8</v>
+      </c>
+      <c r="AF45">
+        <v>22.380845077985</v>
+      </c>
     </row>
     <row r="46" spans="1:32">
       <c r="A46" t="s">
@@ -4656,6 +4899,15 @@
       <c r="AC46">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD46">
+        <v>-2.4</v>
+      </c>
+      <c r="AE46">
+        <v>67.5</v>
+      </c>
+      <c r="AF46">
+        <v>23.368431003274</v>
+      </c>
     </row>
     <row r="47" spans="1:32">
       <c r="A47" t="s">
@@ -4745,6 +4997,15 @@
       <c r="AC47">
         <v>52.32</v>
       </c>
+      <c r="AD47">
+        <v>-5.8</v>
+      </c>
+      <c r="AE47">
+        <v>34</v>
+      </c>
+      <c r="AF47">
+        <v>31.202820521003</v>
+      </c>
     </row>
     <row r="48" spans="1:32">
       <c r="A48" t="s">
@@ -4834,6 +5095,15 @@
       <c r="AC48">
         <v>43.64</v>
       </c>
+      <c r="AD48">
+        <v>-6</v>
+      </c>
+      <c r="AE48">
+        <v>38.2</v>
+      </c>
+      <c r="AF48">
+        <v>26.912766583408</v>
+      </c>
     </row>
     <row r="49" spans="1:32">
       <c r="A49" t="s">
@@ -4923,6 +5193,15 @@
       <c r="AC49">
         <v>54.13</v>
       </c>
+      <c r="AD49">
+        <v>-6.4</v>
+      </c>
+      <c r="AE49">
+        <v>41.9</v>
+      </c>
+      <c r="AF49">
+        <v>25.141716521227</v>
+      </c>
     </row>
     <row r="50" spans="1:32">
       <c r="A50" t="s">
@@ -5012,6 +5291,15 @@
       <c r="AC50">
         <v>71.34</v>
       </c>
+      <c r="AD50">
+        <v>-6.8</v>
+      </c>
+      <c r="AE50">
+        <v>44.2</v>
+      </c>
+      <c r="AF50">
+        <v>24.584680396171</v>
+      </c>
     </row>
     <row r="51" spans="1:32">
       <c r="A51" t="s">
@@ -5101,6 +5389,15 @@
       <c r="AC51">
         <v>64.3</v>
       </c>
+      <c r="AD51">
+        <v>-6</v>
+      </c>
+      <c r="AE51">
+        <v>48.9</v>
+      </c>
+      <c r="AF51">
+        <v>24.089524541762</v>
+      </c>
     </row>
     <row r="52" spans="1:32">
       <c r="A52" t="s">
@@ -5190,6 +5487,15 @@
       <c r="AC52">
         <v>41.96</v>
       </c>
+      <c r="AD52">
+        <v>-11</v>
+      </c>
+      <c r="AE52">
+        <v>67.5</v>
+      </c>
+      <c r="AF52">
+        <v>20.95223365009</v>
+      </c>
     </row>
     <row r="53" spans="1:32">
       <c r="A53" t="s">
@@ -5279,6 +5585,15 @@
       <c r="AC53">
         <v>70.86</v>
       </c>
+      <c r="AD53">
+        <v>-7.9</v>
+      </c>
+      <c r="AE53">
+        <v>68.7</v>
+      </c>
+      <c r="AF53">
+        <v>21.566382991637</v>
+      </c>
     </row>
     <row r="54" spans="1:32">
       <c r="A54" t="s">
@@ -5368,6 +5683,15 @@
       <c r="AC54">
         <v>100.93</v>
       </c>
+      <c r="AD54">
+        <v>-6.1</v>
+      </c>
+      <c r="AE54">
+        <v>69.2</v>
+      </c>
+      <c r="AF54">
+        <v>25.029699214225</v>
+      </c>
     </row>
     <row r="55" spans="1:32">
       <c r="A55" t="s">
@@ -5457,6 +5781,15 @@
       <c r="AC55">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD55">
+        <v>-9.5</v>
+      </c>
+      <c r="AE55">
+        <v>78.3</v>
+      </c>
+      <c r="AF55">
+        <v>24.024941165444</v>
+      </c>
     </row>
     <row r="56" spans="1:32">
       <c r="A56" t="s">
@@ -5547,13 +5880,13 @@
         <v>52.32</v>
       </c>
       <c r="AD56">
-        <v>-8.03019066677877</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="AE56">
-        <v>67.5375540307946</v>
+        <v>71.7</v>
       </c>
       <c r="AF56">
-        <v>25.8123252140431</v>
+        <v>36.909473687082</v>
       </c>
     </row>
     <row r="57" spans="1:32">
@@ -5645,13 +5978,13 @@
         <v>43.64</v>
       </c>
       <c r="AD57">
-        <v>-7.06027781099588</v>
+        <v>-8</v>
       </c>
       <c r="AE57">
-        <v>73.4188038019563</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AF57">
-        <v>26.173225388189</v>
+        <v>37.512310094404</v>
       </c>
     </row>
     <row r="58" spans="1:32">
@@ -5743,13 +6076,13 @@
         <v>54.13</v>
       </c>
       <c r="AD58">
-        <v>-7.7163015572921</v>
+        <v>-8</v>
       </c>
       <c r="AE58">
-        <v>83.6692026491606</v>
+        <v>82.7</v>
       </c>
       <c r="AF58">
-        <v>24.3609920782892</v>
+        <v>36.327653090882</v>
       </c>
     </row>
     <row r="59" spans="1:32">
@@ -5841,13 +6174,13 @@
         <v>71.34</v>
       </c>
       <c r="AD59">
-        <v>-6.78706251271256</v>
+        <v>-7</v>
       </c>
       <c r="AE59">
-        <v>86.6078841212333</v>
+        <v>84.8</v>
       </c>
       <c r="AF59">
-        <v>25.2724385286024</v>
+        <v>37.190521294663</v>
       </c>
     </row>
     <row r="60" spans="1:32">
@@ -5939,13 +6272,13 @@
         <v>64.3</v>
       </c>
       <c r="AD60">
-        <v>-5.30690433831975</v>
+        <v>-4.9</v>
       </c>
       <c r="AE60">
-        <v>92.5652531951269</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="AF60">
-        <v>25.5600401306072</v>
+        <v>38.184350196019</v>
       </c>
     </row>
     <row r="61" spans="1:32">
@@ -6037,13 +6370,13 @@
         <v>41.96</v>
       </c>
       <c r="AD61">
-        <v>-12.4363388244923</v>
+        <v>-11.6</v>
       </c>
       <c r="AE61">
-        <v>98.7098819471851</v>
+        <v>96</v>
       </c>
       <c r="AF61">
-        <v>22.1948673455795</v>
+        <v>34.541533904004</v>
       </c>
     </row>
     <row r="62" spans="1:32">
@@ -6135,13 +6468,13 @@
         <v>70.86</v>
       </c>
       <c r="AD62">
-        <v>-4.53656203172015</v>
+        <v>-2.6</v>
       </c>
       <c r="AE62">
-        <v>85.011503676948</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="AF62">
-        <v>24.6358299212806</v>
+        <v>37.740239873289</v>
       </c>
     </row>
     <row r="63" spans="1:32">
@@ -6233,13 +6566,13 @@
         <v>100.93</v>
       </c>
       <c r="AD63">
-        <v>-4.46637752028169</v>
+        <v>-4</v>
       </c>
       <c r="AE63">
-        <v>79.10232188803781</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="AF63">
-        <v>26.9365134620331</v>
+        <v>39.48063525235</v>
       </c>
     </row>
     <row r="64" spans="1:32">
@@ -6331,13 +6664,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD64">
-        <v>-6.86868984803199</v>
+        <v>-7.7</v>
       </c>
       <c r="AE64">
-        <v>83.0317498523499</v>
+        <v>84</v>
       </c>
       <c r="AF64">
-        <v>25.3707484836752</v>
+        <v>37.596855335807</v>
       </c>
     </row>
     <row r="65" spans="1:32">
@@ -6429,13 +6762,13 @@
         <v>52.32</v>
       </c>
       <c r="AD65">
-        <v>-7.21373287821486</v>
+        <v>-7.6</v>
       </c>
       <c r="AE65">
-        <v>117.275144046752</v>
+        <v>122.5</v>
       </c>
       <c r="AF65">
-        <v>22.10491944754</v>
+        <v>21.584969805442</v>
       </c>
     </row>
     <row r="66" spans="1:32">
@@ -6527,13 +6860,13 @@
         <v>43.64</v>
       </c>
       <c r="AD66">
-        <v>-4.15237850244951</v>
+        <v>-4.5</v>
       </c>
       <c r="AE66">
-        <v>125.131136441335</v>
+        <v>127.1</v>
       </c>
       <c r="AF66">
-        <v>25.2273067617101</v>
+        <v>24.068724445941</v>
       </c>
     </row>
     <row r="67" spans="1:32">
@@ -6624,6 +6957,15 @@
       <c r="AC67">
         <v>54.13</v>
       </c>
+      <c r="AD67">
+        <v>-3.6</v>
+      </c>
+      <c r="AE67">
+        <v>134.6</v>
+      </c>
+      <c r="AF67">
+        <v>24.332693576263</v>
+      </c>
     </row>
     <row r="68" spans="1:32">
       <c r="A68" t="s">
@@ -6713,6 +7055,15 @@
       <c r="AC68">
         <v>71.34</v>
       </c>
+      <c r="AD68">
+        <v>-0.3</v>
+      </c>
+      <c r="AE68">
+        <v>107.2</v>
+      </c>
+      <c r="AF68">
+        <v>24.702934808592</v>
+      </c>
     </row>
     <row r="69" spans="1:32">
       <c r="A69" t="s">
@@ -6802,6 +7153,15 @@
       <c r="AC69">
         <v>64.3</v>
       </c>
+      <c r="AD69">
+        <v>2.9</v>
+      </c>
+      <c r="AE69">
+        <v>101.6</v>
+      </c>
+      <c r="AF69">
+        <v>25.069676010518</v>
+      </c>
     </row>
     <row r="70" spans="1:32">
       <c r="A70" t="s">
@@ -6891,6 +7251,15 @@
       <c r="AC70">
         <v>41.96</v>
       </c>
+      <c r="AD70">
+        <v>-4.2</v>
+      </c>
+      <c r="AE70">
+        <v>129.6</v>
+      </c>
+      <c r="AF70">
+        <v>26.379915113614</v>
+      </c>
     </row>
     <row r="71" spans="1:32">
       <c r="A71" t="s">
@@ -6980,6 +7349,15 @@
       <c r="AC71">
         <v>70.86</v>
       </c>
+      <c r="AD71">
+        <v>-3.9</v>
+      </c>
+      <c r="AE71">
+        <v>108.6</v>
+      </c>
+      <c r="AF71">
+        <v>23.243306079547</v>
+      </c>
     </row>
     <row r="72" spans="1:32">
       <c r="A72" t="s">
@@ -7069,6 +7447,15 @@
       <c r="AC72">
         <v>100.93</v>
       </c>
+      <c r="AD72">
+        <v>-1.7</v>
+      </c>
+      <c r="AE72">
+        <v>104</v>
+      </c>
+      <c r="AF72">
+        <v>25.171871081612</v>
+      </c>
     </row>
     <row r="73" spans="1:32">
       <c r="A73" t="s">
@@ -7158,6 +7545,15 @@
       <c r="AC73">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD73">
+        <v>-1.6</v>
+      </c>
+      <c r="AE73">
+        <v>104.1</v>
+      </c>
+      <c r="AF73">
+        <v>24.878825347417</v>
+      </c>
     </row>
     <row r="74" spans="1:32">
       <c r="A74" t="s">
@@ -7248,10 +7644,13 @@
         <v>52.32</v>
       </c>
       <c r="AD74">
-        <v>-2.14568328960442</v>
+        <v>-2.1</v>
+      </c>
+      <c r="AE74">
+        <v>17.4</v>
       </c>
       <c r="AF74">
-        <v>21.1423576597254</v>
+        <v>22.93943628365</v>
       </c>
     </row>
     <row r="75" spans="1:32">
@@ -7343,10 +7742,13 @@
         <v>43.64</v>
       </c>
       <c r="AD75">
-        <v>-2.73388798624091</v>
+        <v>-2.7</v>
+      </c>
+      <c r="AE75">
+        <v>21.1</v>
       </c>
       <c r="AF75">
-        <v>20.8570992758656</v>
+        <v>22.706036756175</v>
       </c>
     </row>
     <row r="76" spans="1:32">
@@ -7438,10 +7840,13 @@
         <v>54.13</v>
       </c>
       <c r="AD76">
-        <v>-2.55814767454965</v>
+        <v>-2.6</v>
+      </c>
+      <c r="AE76">
+        <v>23.7</v>
       </c>
       <c r="AF76">
-        <v>21.1680432165628</v>
+        <v>22.865089482107</v>
       </c>
     </row>
     <row r="77" spans="1:32">
@@ -7533,10 +7938,13 @@
         <v>71.34</v>
       </c>
       <c r="AD77">
-        <v>-1.7258596181872</v>
+        <v>-1.5</v>
+      </c>
+      <c r="AE77">
+        <v>25.8</v>
       </c>
       <c r="AF77">
-        <v>22.1740306166793</v>
+        <v>24.133439910433</v>
       </c>
     </row>
     <row r="78" spans="1:32">
@@ -7628,10 +8036,13 @@
         <v>64.3</v>
       </c>
       <c r="AD78">
-        <v>-2.84519500863434</v>
+        <v>-2.7</v>
+      </c>
+      <c r="AE78">
+        <v>28.3</v>
       </c>
       <c r="AF78">
-        <v>21.739927149931</v>
+        <v>23.766623207823</v>
       </c>
     </row>
     <row r="79" spans="1:32">
@@ -7723,10 +8134,13 @@
         <v>41.96</v>
       </c>
       <c r="AD79">
-        <v>-7.21904641164918</v>
+        <v>-7.1</v>
+      </c>
+      <c r="AE79">
+        <v>32.4</v>
       </c>
       <c r="AF79">
-        <v>19.9382667510933</v>
+        <v>21.99304272478</v>
       </c>
     </row>
     <row r="80" spans="1:32">
@@ -7818,10 +8232,13 @@
         <v>70.86</v>
       </c>
       <c r="AD80">
-        <v>-7.72312323783927</v>
+        <v>-7.5</v>
+      </c>
+      <c r="AE80">
+        <v>36.4</v>
       </c>
       <c r="AF80">
-        <v>24.1674095479002</v>
+        <v>26.090307464747</v>
       </c>
     </row>
     <row r="81" spans="1:32">
@@ -7913,10 +8330,13 @@
         <v>100.93</v>
       </c>
       <c r="AD81">
-        <v>1.13200004002418</v>
+        <v>1.4</v>
+      </c>
+      <c r="AE81">
+        <v>37.9</v>
       </c>
       <c r="AF81">
-        <v>26.0812426572599</v>
+        <v>28.085085664301</v>
       </c>
     </row>
     <row r="82" spans="1:32">
@@ -8008,10 +8428,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD82">
-        <v>-2.39074850027879</v>
+        <v>-2.3</v>
+      </c>
+      <c r="AE82">
+        <v>39.4</v>
       </c>
       <c r="AF82">
-        <v>22.9465317535315</v>
+        <v>25.122697922888</v>
       </c>
     </row>
     <row r="83" spans="1:32">
@@ -8103,13 +8526,13 @@
         <v>52.32</v>
       </c>
       <c r="AD83">
-        <v>-1.40738619185838</v>
+        <v>-3.5</v>
       </c>
       <c r="AE83">
-        <v>53.2785874737167</v>
+        <v>50.4</v>
       </c>
       <c r="AF83">
-        <v>24.1024162766989</v>
+        <v>27.757127825676</v>
       </c>
     </row>
     <row r="84" spans="1:32">
@@ -8201,13 +8624,13 @@
         <v>43.64</v>
       </c>
       <c r="AD84">
-        <v>-3.04286241958897</v>
+        <v>-2.3</v>
       </c>
       <c r="AE84">
-        <v>66.9071609125065</v>
+        <v>49.9</v>
       </c>
       <c r="AF84">
-        <v>24.2234212780588</v>
+        <v>27.719668486621</v>
       </c>
     </row>
     <row r="85" spans="1:32">
@@ -8299,13 +8722,13 @@
         <v>54.13</v>
       </c>
       <c r="AD85">
-        <v>-2.19824409588726</v>
+        <v>-2.5</v>
       </c>
       <c r="AE85">
-        <v>66.7272478472146</v>
+        <v>49.4</v>
       </c>
       <c r="AF85">
-        <v>22.5842861999584</v>
+        <v>26.824972175386</v>
       </c>
     </row>
     <row r="86" spans="1:32">
@@ -8397,13 +8820,13 @@
         <v>71.34</v>
       </c>
       <c r="AD86">
-        <v>-2.61320674678311</v>
+        <v>-4.7</v>
       </c>
       <c r="AE86">
-        <v>71.65057024810559</v>
+        <v>51.8</v>
       </c>
       <c r="AF86">
-        <v>23.4751871722398</v>
+        <v>29.990242298186</v>
       </c>
     </row>
     <row r="87" spans="1:32">
@@ -8495,13 +8918,13 @@
         <v>64.3</v>
       </c>
       <c r="AD87">
-        <v>-2.23798643665382</v>
+        <v>-3.5</v>
       </c>
       <c r="AE87">
-        <v>72.70387857708219</v>
+        <v>51</v>
       </c>
       <c r="AF87">
-        <v>25.575368512731</v>
+        <v>29.397056421943</v>
       </c>
     </row>
     <row r="88" spans="1:32">
@@ -8593,13 +9016,13 @@
         <v>41.96</v>
       </c>
       <c r="AD88">
-        <v>-8.515533579082881</v>
+        <v>-7.1</v>
       </c>
       <c r="AE88">
-        <v>91.1566069449736</v>
+        <v>65.3</v>
       </c>
       <c r="AF88">
-        <v>23.6871303712315</v>
+        <v>26.588116220092</v>
       </c>
     </row>
     <row r="89" spans="1:32">
@@ -8691,13 +9114,13 @@
         <v>70.86</v>
       </c>
       <c r="AD89">
-        <v>-7.65394474545161</v>
+        <v>-7.3</v>
       </c>
       <c r="AE89">
-        <v>80.4259616037106</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AF89">
-        <v>24.1312117221098</v>
+        <v>27.198069120587</v>
       </c>
     </row>
     <row r="90" spans="1:32">
@@ -8789,13 +9212,13 @@
         <v>100.93</v>
       </c>
       <c r="AD90">
-        <v>-5.29929051233517</v>
+        <v>-6.4</v>
       </c>
       <c r="AE90">
-        <v>70.2611599864283</v>
+        <v>61.3</v>
       </c>
       <c r="AF90">
-        <v>25.4074707206706</v>
+        <v>27.727355990026</v>
       </c>
     </row>
     <row r="91" spans="1:32">
@@ -8887,13 +9310,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD91">
-        <v>-2.04098550110347</v>
+        <v>-2.9</v>
       </c>
       <c r="AE91">
-        <v>71.3312731896082</v>
+        <v>55.4</v>
       </c>
       <c r="AF91">
-        <v>28.4136914959886</v>
+        <v>32.170876746366</v>
       </c>
     </row>
     <row r="92" spans="1:32">
@@ -8984,8 +9407,14 @@
       <c r="AC92">
         <v>52.32</v>
       </c>
+      <c r="AD92">
+        <v>-5.5</v>
+      </c>
+      <c r="AE92">
+        <v>39.8</v>
+      </c>
       <c r="AF92">
-        <v>23.4572080583441</v>
+        <v>13.236865986922</v>
       </c>
     </row>
     <row r="93" spans="1:32">
@@ -9076,8 +9505,14 @@
       <c r="AC93">
         <v>43.64</v>
       </c>
+      <c r="AD93">
+        <v>-5.1</v>
+      </c>
+      <c r="AE93">
+        <v>44.1</v>
+      </c>
       <c r="AF93">
-        <v>24.0079934600948</v>
+        <v>13.661789188587</v>
       </c>
     </row>
     <row r="94" spans="1:32">
@@ -9168,8 +9603,14 @@
       <c r="AC94">
         <v>54.13</v>
       </c>
+      <c r="AD94">
+        <v>-5.9</v>
+      </c>
+      <c r="AE94">
+        <v>47.1</v>
+      </c>
       <c r="AF94">
-        <v>23.3185966619773</v>
+        <v>13.277753242279</v>
       </c>
     </row>
     <row r="95" spans="1:32">
@@ -9260,8 +9701,14 @@
       <c r="AC95">
         <v>71.34</v>
       </c>
+      <c r="AD95">
+        <v>-5.6</v>
+      </c>
+      <c r="AE95">
+        <v>51.7</v>
+      </c>
       <c r="AF95">
-        <v>24.3167782701782</v>
+        <v>13.203670943989</v>
       </c>
     </row>
     <row r="96" spans="1:32">
@@ -9353,10 +9800,13 @@
         <v>64.3</v>
       </c>
       <c r="AD96">
-        <v>-2.32627659299422</v>
+        <v>-6.6</v>
+      </c>
+      <c r="AE96">
+        <v>56.1</v>
       </c>
       <c r="AF96">
-        <v>27.5354175556737</v>
+        <v>14.924409769828</v>
       </c>
     </row>
     <row r="97" spans="1:32">
@@ -9448,10 +9898,13 @@
         <v>41.96</v>
       </c>
       <c r="AD97">
-        <v>-5.3522749947218</v>
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="AE97">
+        <v>66.5</v>
       </c>
       <c r="AF97">
-        <v>27.1843242899476</v>
+        <v>13.821369167821</v>
       </c>
     </row>
     <row r="98" spans="1:32">
@@ -9543,10 +9996,13 @@
         <v>70.86</v>
       </c>
       <c r="AD98">
-        <v>-2.77815643267862</v>
+        <v>-5</v>
+      </c>
+      <c r="AE98">
+        <v>67</v>
       </c>
       <c r="AF98">
-        <v>28.2061355248318</v>
+        <v>15.537181736499</v>
       </c>
     </row>
     <row r="99" spans="1:32">
@@ -9638,10 +10094,13 @@
         <v>100.93</v>
       </c>
       <c r="AD99">
-        <v>-0.0522988947716759</v>
+        <v>-2.7</v>
+      </c>
+      <c r="AE99">
+        <v>61.4</v>
       </c>
       <c r="AF99">
-        <v>28.8914258324714</v>
+        <v>15.977331501279</v>
       </c>
     </row>
     <row r="100" spans="1:32">
@@ -9733,10 +10192,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD100">
-        <v>0.439026284006009</v>
+        <v>-3.2</v>
+      </c>
+      <c r="AE100">
+        <v>60.4</v>
       </c>
       <c r="AF100">
-        <v>29.3390402864479</v>
+        <v>15.085134819363</v>
       </c>
     </row>
     <row r="101" spans="1:32">
@@ -9809,6 +10271,15 @@
       <c r="AC101">
         <v>52.32</v>
       </c>
+      <c r="AD101">
+        <v>11.4</v>
+      </c>
+      <c r="AE101">
+        <v>68.2</v>
+      </c>
+      <c r="AF101">
+        <v>43.772499235694</v>
+      </c>
     </row>
     <row r="102" spans="1:32">
       <c r="A102" t="s">
@@ -9880,6 +10351,15 @@
       <c r="AC102">
         <v>43.64</v>
       </c>
+      <c r="AD102">
+        <v>11.6</v>
+      </c>
+      <c r="AE102">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AF102">
+        <v>59.62812145843</v>
+      </c>
     </row>
     <row r="103" spans="1:32">
       <c r="A103" t="s">
@@ -9951,6 +10431,15 @@
       <c r="AC103">
         <v>54.13</v>
       </c>
+      <c r="AD103">
+        <v>-3.3</v>
+      </c>
+      <c r="AE103">
+        <v>84.2</v>
+      </c>
+      <c r="AF103">
+        <v>50.713663033788</v>
+      </c>
     </row>
     <row r="104" spans="1:32">
       <c r="A104" t="s">
@@ -10022,6 +10511,15 @@
       <c r="AC104">
         <v>71.34</v>
       </c>
+      <c r="AD104">
+        <v>-17.2</v>
+      </c>
+      <c r="AE104">
+        <v>85.7</v>
+      </c>
+      <c r="AF104">
+        <v>46.246532215317</v>
+      </c>
     </row>
     <row r="105" spans="1:32">
       <c r="A105" t="s">
@@ -10093,6 +10591,15 @@
       <c r="AC105">
         <v>64.3</v>
       </c>
+      <c r="AD105">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="AE105">
+        <v>97.8</v>
+      </c>
+      <c r="AF105">
+        <v>39.561846238309</v>
+      </c>
     </row>
     <row r="106" spans="1:32">
       <c r="A106" t="s">
@@ -10164,6 +10671,15 @@
       <c r="AC106">
         <v>41.96</v>
       </c>
+      <c r="AD106">
+        <v>-7.5</v>
+      </c>
+      <c r="AE106">
+        <v>118.4</v>
+      </c>
+      <c r="AF106">
+        <v>59.229712246998</v>
+      </c>
     </row>
     <row r="107" spans="1:32">
       <c r="A107" t="s">
@@ -10253,6 +10769,15 @@
       <c r="AC107">
         <v>70.86</v>
       </c>
+      <c r="AD107">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="AE107">
+        <v>116.3</v>
+      </c>
+      <c r="AF107">
+        <v>58.771622927148</v>
+      </c>
     </row>
     <row r="108" spans="1:32">
       <c r="A108" t="s">
@@ -10342,6 +10867,15 @@
       <c r="AC108">
         <v>100.93</v>
       </c>
+      <c r="AD108">
+        <v>-7.2</v>
+      </c>
+      <c r="AE108">
+        <v>110</v>
+      </c>
+      <c r="AF108">
+        <v>62.51442113462</v>
+      </c>
     </row>
     <row r="109" spans="1:32">
       <c r="A109" t="s">
@@ -10431,6 +10965,15 @@
       <c r="AC109">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD109">
+        <v>-4.5</v>
+      </c>
+      <c r="AE109">
+        <v>101.3</v>
+      </c>
+      <c r="AF109">
+        <v>60.306074773603</v>
+      </c>
     </row>
     <row r="110" spans="1:32">
       <c r="A110" t="s">
@@ -10521,10 +11064,13 @@
         <v>52.32</v>
       </c>
       <c r="AD110">
-        <v>-0.0137507698086695</v>
+        <v>0</v>
+      </c>
+      <c r="AE110">
+        <v>44.8</v>
       </c>
       <c r="AF110">
-        <v>14.5186216543802</v>
+        <v>16.694624294622</v>
       </c>
     </row>
     <row r="111" spans="1:32">
@@ -10616,10 +11162,13 @@
         <v>43.64</v>
       </c>
       <c r="AD111">
-        <v>-3.02646274607075</v>
+        <v>-3.1</v>
+      </c>
+      <c r="AE111">
+        <v>46.7</v>
       </c>
       <c r="AF111">
-        <v>14.827297566694</v>
+        <v>13.899066735488</v>
       </c>
     </row>
     <row r="112" spans="1:32">
@@ -10711,10 +11260,13 @@
         <v>54.13</v>
       </c>
       <c r="AD112">
-        <v>-3.38919282715608</v>
+        <v>-3.1</v>
+      </c>
+      <c r="AE112">
+        <v>49.5</v>
       </c>
       <c r="AF112">
-        <v>14.9920997503639</v>
+        <v>14.140596567288</v>
       </c>
     </row>
     <row r="113" spans="1:32">
@@ -10806,10 +11358,13 @@
         <v>71.34</v>
       </c>
       <c r="AD113">
-        <v>-2.43860550444748</v>
+        <v>-2.2</v>
+      </c>
+      <c r="AE113">
+        <v>50.8</v>
       </c>
       <c r="AF113">
-        <v>15.269462908084</v>
+        <v>14.284863256305</v>
       </c>
     </row>
     <row r="114" spans="1:32">
@@ -10901,10 +11456,13 @@
         <v>64.3</v>
       </c>
       <c r="AD114">
-        <v>-3.54751974530668</v>
+        <v>-3.5</v>
+      </c>
+      <c r="AE114">
+        <v>53.5</v>
       </c>
       <c r="AF114">
-        <v>15.5470600045533</v>
+        <v>14.363006832284</v>
       </c>
     </row>
     <row r="115" spans="1:32">
@@ -10996,10 +11554,13 @@
         <v>41.96</v>
       </c>
       <c r="AD115">
-        <v>-8.3098749631764</v>
+        <v>-7.9</v>
+      </c>
+      <c r="AE115">
+        <v>71.8</v>
       </c>
       <c r="AF115">
-        <v>14.8813590480588</v>
+        <v>14.240513311294</v>
       </c>
     </row>
     <row r="116" spans="1:32">
@@ -11091,10 +11652,13 @@
         <v>70.86</v>
       </c>
       <c r="AD116">
-        <v>-2.46543421523845</v>
+        <v>-2.9</v>
+      </c>
+      <c r="AE116">
+        <v>62.8</v>
       </c>
       <c r="AF116">
-        <v>16.4297863174204</v>
+        <v>15.498669615807</v>
       </c>
     </row>
     <row r="117" spans="1:32">
@@ -11186,10 +11750,13 @@
         <v>100.93</v>
       </c>
       <c r="AD117">
-        <v>-3.17762653492364</v>
+        <v>-3.2</v>
+      </c>
+      <c r="AE117">
+        <v>59.6</v>
       </c>
       <c r="AF117">
-        <v>16.3623217477379</v>
+        <v>15.273368095779</v>
       </c>
     </row>
     <row r="118" spans="1:32">
@@ -11281,10 +11848,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD118">
-        <v>-3.38217585157086</v>
+        <v>-3.3</v>
+      </c>
+      <c r="AE118">
+        <v>60.5</v>
       </c>
       <c r="AF118">
-        <v>17.015284341071</v>
+        <v>15.845492390768</v>
       </c>
     </row>
     <row r="119" spans="1:32">
@@ -11376,10 +11946,13 @@
         <v>52.32</v>
       </c>
       <c r="AD119">
-        <v>-5.69774311670289</v>
+        <v>-6.9</v>
+      </c>
+      <c r="AE119">
+        <v>36.4</v>
       </c>
       <c r="AF119">
-        <v>30.8458833789351</v>
+        <v>37.221683948517</v>
       </c>
     </row>
     <row r="120" spans="1:32">
@@ -11471,10 +12044,13 @@
         <v>43.64</v>
       </c>
       <c r="AD120">
-        <v>-8.57164995739415</v>
+        <v>-10.3</v>
+      </c>
+      <c r="AE120">
+        <v>46.1</v>
       </c>
       <c r="AF120">
-        <v>28.6412079584013</v>
+        <v>33.835649828911</v>
       </c>
     </row>
     <row r="121" spans="1:32">
@@ -11566,10 +12142,13 @@
         <v>54.13</v>
       </c>
       <c r="AD121">
-        <v>-6.36519719285874</v>
+        <v>-5.8</v>
+      </c>
+      <c r="AE121">
+        <v>47.4</v>
       </c>
       <c r="AF121">
-        <v>27.9863154861129</v>
+        <v>34.71377480203</v>
       </c>
     </row>
     <row r="122" spans="1:32">
@@ -11661,10 +12240,13 @@
         <v>71.34</v>
       </c>
       <c r="AD122">
-        <v>-3.52514850564392</v>
+        <v>-2.8</v>
+      </c>
+      <c r="AE122">
+        <v>49.5</v>
       </c>
       <c r="AF122">
-        <v>31.2062328120813</v>
+        <v>38.121948856836</v>
       </c>
     </row>
     <row r="123" spans="1:32">
@@ -11756,10 +12338,13 @@
         <v>64.3</v>
       </c>
       <c r="AD123">
-        <v>-4.27034595652833</v>
+        <v>-3.5</v>
+      </c>
+      <c r="AE123">
+        <v>52.1</v>
       </c>
       <c r="AF123">
-        <v>29.6599984642663</v>
+        <v>36.285547753875</v>
       </c>
     </row>
     <row r="124" spans="1:32">
@@ -11851,10 +12436,13 @@
         <v>41.96</v>
       </c>
       <c r="AD124">
-        <v>-7.49141811316719</v>
+        <v>-7.4</v>
+      </c>
+      <c r="AE124">
+        <v>63.6</v>
       </c>
       <c r="AF124">
-        <v>27.1210867326524</v>
+        <v>32.824706883009</v>
       </c>
     </row>
     <row r="125" spans="1:32">
@@ -11946,10 +12534,13 @@
         <v>70.86</v>
       </c>
       <c r="AD125">
-        <v>-2.90457512420842</v>
+        <v>-1.6</v>
+      </c>
+      <c r="AE125">
+        <v>61.8</v>
       </c>
       <c r="AF125">
-        <v>29.6714820409688</v>
+        <v>35.868237373976</v>
       </c>
     </row>
     <row r="126" spans="1:32">
@@ -12041,10 +12632,13 @@
         <v>100.93</v>
       </c>
       <c r="AD126">
-        <v>-0.0062162674566409</v>
+        <v>0</v>
+      </c>
+      <c r="AE126">
+        <v>57.2</v>
       </c>
       <c r="AF126">
-        <v>30.9625405355437</v>
+        <v>38.896372522219</v>
       </c>
     </row>
     <row r="127" spans="1:32">
@@ -12135,6 +12729,15 @@
       <c r="AC127">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD127">
+        <v>-3.5</v>
+      </c>
+      <c r="AE127">
+        <v>54.5</v>
+      </c>
+      <c r="AF127">
+        <v>36.077927677101</v>
+      </c>
     </row>
     <row r="128" spans="1:32">
       <c r="A128" t="s">
@@ -12224,6 +12827,15 @@
       <c r="AC128">
         <v>52.32</v>
       </c>
+      <c r="AD128">
+        <v>-0.8</v>
+      </c>
+      <c r="AE128">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="AF128">
+        <v>24.461028303516</v>
+      </c>
     </row>
     <row r="129" spans="1:32">
       <c r="A129" t="s">
@@ -12313,6 +12925,15 @@
       <c r="AC129">
         <v>43.64</v>
       </c>
+      <c r="AD129">
+        <v>2.7</v>
+      </c>
+      <c r="AE129">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="AF129">
+        <v>26.217607944237</v>
+      </c>
     </row>
     <row r="130" spans="1:32">
       <c r="A130" t="s">
@@ -12402,6 +13023,15 @@
       <c r="AC130">
         <v>54.13</v>
       </c>
+      <c r="AD130">
+        <v>3</v>
+      </c>
+      <c r="AE130">
+        <v>70.3</v>
+      </c>
+      <c r="AF130">
+        <v>25.602033976673</v>
+      </c>
     </row>
     <row r="131" spans="1:32">
       <c r="A131" t="s">
@@ -12491,6 +13121,15 @@
       <c r="AC131">
         <v>71.34</v>
       </c>
+      <c r="AD131">
+        <v>4.9</v>
+      </c>
+      <c r="AE131">
+        <v>68.5</v>
+      </c>
+      <c r="AF131">
+        <v>26.99163574497</v>
+      </c>
     </row>
     <row r="132" spans="1:32">
       <c r="A132" t="s">
@@ -12580,6 +13219,15 @@
       <c r="AC132">
         <v>64.3</v>
       </c>
+      <c r="AD132">
+        <v>5</v>
+      </c>
+      <c r="AE132">
+        <v>62.7</v>
+      </c>
+      <c r="AF132">
+        <v>26.599858875091</v>
+      </c>
     </row>
     <row r="133" spans="1:32">
       <c r="A133" t="s">
@@ -12669,6 +13317,15 @@
       <c r="AC133">
         <v>41.96</v>
       </c>
+      <c r="AD133">
+        <v>-4.5</v>
+      </c>
+      <c r="AE133">
+        <v>89.5</v>
+      </c>
+      <c r="AF133">
+        <v>28.137350865431</v>
+      </c>
     </row>
     <row r="134" spans="1:32">
       <c r="A134" t="s">
@@ -12758,6 +13415,15 @@
       <c r="AC134">
         <v>70.86</v>
       </c>
+      <c r="AD134">
+        <v>0.3</v>
+      </c>
+      <c r="AE134">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="AF134">
+        <v>31.587029727526</v>
+      </c>
     </row>
     <row r="135" spans="1:32">
       <c r="A135" t="s">
@@ -12847,6 +13513,15 @@
       <c r="AC135">
         <v>100.93</v>
       </c>
+      <c r="AD135">
+        <v>0.9</v>
+      </c>
+      <c r="AE135">
+        <v>79.3</v>
+      </c>
+      <c r="AF135">
+        <v>32.931708838352</v>
+      </c>
     </row>
     <row r="136" spans="1:32">
       <c r="A136" t="s">
@@ -12936,6 +13611,15 @@
       <c r="AC136">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD136">
+        <v>7.9</v>
+      </c>
+      <c r="AE136">
+        <v>74.5</v>
+      </c>
+      <c r="AF136">
+        <v>36.606647417346</v>
+      </c>
     </row>
     <row r="137" spans="1:32">
       <c r="A137" t="s">
@@ -13026,10 +13710,13 @@
         <v>52.32</v>
       </c>
       <c r="AD137">
-        <v>-1.47564487783448</v>
+        <v>-1.5</v>
+      </c>
+      <c r="AE137">
+        <v>24.8</v>
       </c>
       <c r="AF137">
-        <v>11.6684130766311</v>
+        <v>11.109482939281</v>
       </c>
     </row>
     <row r="138" spans="1:32">
@@ -13121,10 +13808,13 @@
         <v>43.64</v>
       </c>
       <c r="AD138">
-        <v>-1.11021822656786</v>
+        <v>-1.1</v>
+      </c>
+      <c r="AE138">
+        <v>24.9</v>
       </c>
       <c r="AF138">
-        <v>11.9784847026855</v>
+        <v>11.455671291385</v>
       </c>
     </row>
     <row r="139" spans="1:32">
@@ -13216,10 +13906,13 @@
         <v>54.13</v>
       </c>
       <c r="AD139">
-        <v>-1.37831049093858</v>
+        <v>-1.4</v>
+      </c>
+      <c r="AE139">
+        <v>25.1</v>
       </c>
       <c r="AF139">
-        <v>11.8855616228225</v>
+        <v>11.393366495901</v>
       </c>
     </row>
     <row r="140" spans="1:32">
@@ -13311,10 +14004,13 @@
         <v>71.34</v>
       </c>
       <c r="AD140">
-        <v>-1.87503523800931</v>
+        <v>-1.9</v>
+      </c>
+      <c r="AE140">
+        <v>26.4</v>
       </c>
       <c r="AF140">
-        <v>11.7783778069365</v>
+        <v>11.306780002907</v>
       </c>
     </row>
     <row r="141" spans="1:32">
@@ -13406,10 +14102,13 @@
         <v>64.3</v>
       </c>
       <c r="AD141">
-        <v>-2.23511034211637</v>
+        <v>-2.2</v>
+      </c>
+      <c r="AE141">
+        <v>26.4</v>
       </c>
       <c r="AF141">
-        <v>11.7162477369852</v>
+        <v>11.205035569749</v>
       </c>
     </row>
     <row r="142" spans="1:32">
@@ -13501,10 +14200,13 @@
         <v>41.96</v>
       </c>
       <c r="AD142">
-        <v>-4.35589779033159</v>
+        <v>-4.9</v>
+      </c>
+      <c r="AE142">
+        <v>31.5</v>
       </c>
       <c r="AF142">
-        <v>11.118681180436</v>
+        <v>10.675427078131</v>
       </c>
     </row>
     <row r="143" spans="1:32">
@@ -13596,10 +14298,13 @@
         <v>70.86</v>
       </c>
       <c r="AD143">
-        <v>-1.14900209815134</v>
+        <v>-1.2</v>
+      </c>
+      <c r="AE143">
+        <v>30.6</v>
       </c>
       <c r="AF143">
-        <v>12.6596673834992</v>
+        <v>12.30706957096</v>
       </c>
     </row>
     <row r="144" spans="1:32">
@@ -13691,10 +14396,13 @@
         <v>100.93</v>
       </c>
       <c r="AD144">
-        <v>-1.70787872719767</v>
+        <v>-1.7</v>
+      </c>
+      <c r="AE144">
+        <v>29</v>
       </c>
       <c r="AF144">
-        <v>12.8936854888585</v>
+        <v>12.571829383937</v>
       </c>
     </row>
     <row r="145" spans="1:32">
@@ -13786,10 +14494,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD145">
-        <v>-1.25751928033412</v>
+        <v>-1.3</v>
+      </c>
+      <c r="AE145">
+        <v>27.2</v>
       </c>
       <c r="AF145">
-        <v>12.8498936023601</v>
+        <v>12.480324589208</v>
       </c>
     </row>
     <row r="146" spans="1:32">
@@ -13880,6 +14591,15 @@
       <c r="AC146">
         <v>52.32</v>
       </c>
+      <c r="AD146">
+        <v>-0.7</v>
+      </c>
+      <c r="AE146">
+        <v>42.2</v>
+      </c>
+      <c r="AF146">
+        <v>20.991221398329</v>
+      </c>
     </row>
     <row r="147" spans="1:32">
       <c r="A147" t="s">
@@ -13969,6 +14689,15 @@
       <c r="AC147">
         <v>43.64</v>
       </c>
+      <c r="AD147">
+        <v>-3.2</v>
+      </c>
+      <c r="AE147">
+        <v>35.7</v>
+      </c>
+      <c r="AF147">
+        <v>21.970109225032</v>
+      </c>
     </row>
     <row r="148" spans="1:32">
       <c r="A148" t="s">
@@ -14058,6 +14787,15 @@
       <c r="AC148">
         <v>54.13</v>
       </c>
+      <c r="AD148">
+        <v>-3.1</v>
+      </c>
+      <c r="AE148">
+        <v>35.2</v>
+      </c>
+      <c r="AF148">
+        <v>23.168847424164</v>
+      </c>
     </row>
     <row r="149" spans="1:32">
       <c r="A149" t="s">
@@ -14147,6 +14885,15 @@
       <c r="AC149">
         <v>71.34</v>
       </c>
+      <c r="AD149">
+        <v>-2.5</v>
+      </c>
+      <c r="AE149">
+        <v>37.4</v>
+      </c>
+      <c r="AF149">
+        <v>25.035161994892</v>
+      </c>
     </row>
     <row r="150" spans="1:32">
       <c r="A150" t="s">
@@ -14236,6 +14983,15 @@
       <c r="AC150">
         <v>64.3</v>
       </c>
+      <c r="AD150">
+        <v>-2.5</v>
+      </c>
+      <c r="AE150">
+        <v>34.2</v>
+      </c>
+      <c r="AF150">
+        <v>25.609571776276</v>
+      </c>
     </row>
     <row r="151" spans="1:32">
       <c r="A151" t="s">
@@ -14325,6 +15081,15 @@
       <c r="AC151">
         <v>41.96</v>
       </c>
+      <c r="AD151">
+        <v>-7.8</v>
+      </c>
+      <c r="AE151">
+        <v>47.4</v>
+      </c>
+      <c r="AF151">
+        <v>22.762654689216</v>
+      </c>
     </row>
     <row r="152" spans="1:32">
       <c r="A152" t="s">
@@ -14414,6 +15179,15 @@
       <c r="AC152">
         <v>70.86</v>
       </c>
+      <c r="AD152">
+        <v>-6.9</v>
+      </c>
+      <c r="AE152">
+        <v>38.9</v>
+      </c>
+      <c r="AF152">
+        <v>17.842383004857</v>
+      </c>
     </row>
     <row r="153" spans="1:32">
       <c r="A153" t="s">
@@ -14503,6 +15277,15 @@
       <c r="AC153">
         <v>100.93</v>
       </c>
+      <c r="AD153">
+        <v>-5.1</v>
+      </c>
+      <c r="AE153">
+        <v>24.8</v>
+      </c>
+      <c r="AF153">
+        <v>15.2871510974</v>
+      </c>
     </row>
     <row r="154" spans="1:32">
       <c r="A154" t="s">
@@ -14592,6 +15375,15 @@
       <c r="AC154">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD154">
+        <v>-5.6</v>
+      </c>
+      <c r="AE154">
+        <v>26.7</v>
+      </c>
+      <c r="AF154">
+        <v>18.080887555583</v>
+      </c>
     </row>
     <row r="155" spans="1:32">
       <c r="A155" t="s">
@@ -14682,10 +15474,13 @@
         <v>52.32</v>
       </c>
       <c r="AD155">
-        <v>-0.859334595922316</v>
+        <v>-0.8</v>
+      </c>
+      <c r="AE155">
+        <v>38.3</v>
       </c>
       <c r="AF155">
-        <v>23.363155171353</v>
+        <v>25.240786936311</v>
       </c>
     </row>
     <row r="156" spans="1:32">
@@ -14776,6 +15571,15 @@
       <c r="AC156">
         <v>43.64</v>
       </c>
+      <c r="AD156">
+        <v>-0.4</v>
+      </c>
+      <c r="AE156">
+        <v>39.4</v>
+      </c>
+      <c r="AF156">
+        <v>26.985198207163</v>
+      </c>
     </row>
     <row r="157" spans="1:32">
       <c r="A157" t="s">
@@ -14865,6 +15669,15 @@
       <c r="AC157">
         <v>54.13</v>
       </c>
+      <c r="AD157">
+        <v>-0.4</v>
+      </c>
+      <c r="AE157">
+        <v>41.3</v>
+      </c>
+      <c r="AF157">
+        <v>26.450147459269</v>
+      </c>
     </row>
     <row r="158" spans="1:32">
       <c r="A158" t="s">
@@ -14954,6 +15767,15 @@
       <c r="AC158">
         <v>71.34</v>
       </c>
+      <c r="AD158">
+        <v>0.2</v>
+      </c>
+      <c r="AE158">
+        <v>42.4</v>
+      </c>
+      <c r="AF158">
+        <v>26.353339161148</v>
+      </c>
     </row>
     <row r="159" spans="1:32">
       <c r="A159" t="s">
@@ -15043,6 +15865,15 @@
       <c r="AC159">
         <v>64.3</v>
       </c>
+      <c r="AD159">
+        <v>0.1</v>
+      </c>
+      <c r="AE159">
+        <v>43.3</v>
+      </c>
+      <c r="AF159">
+        <v>26.028244602868</v>
+      </c>
     </row>
     <row r="160" spans="1:32">
       <c r="A160" t="s">
@@ -15133,10 +15964,13 @@
         <v>41.96</v>
       </c>
       <c r="AD160">
-        <v>-4.52977692141499</v>
+        <v>-4.6</v>
+      </c>
+      <c r="AE160">
+        <v>53.5</v>
       </c>
       <c r="AF160">
-        <v>22.2099126100845</v>
+        <v>23.843404732402</v>
       </c>
     </row>
     <row r="161" spans="1:32">
@@ -15227,6 +16061,15 @@
       <c r="AC161">
         <v>70.86</v>
       </c>
+      <c r="AD161">
+        <v>-3.2</v>
+      </c>
+      <c r="AE161">
+        <v>52.7</v>
+      </c>
+      <c r="AF161">
+        <v>25.635293741444</v>
+      </c>
     </row>
     <row r="162" spans="1:32">
       <c r="A162" t="s">
@@ -15316,6 +16159,15 @@
       <c r="AC162">
         <v>100.93</v>
       </c>
+      <c r="AD162">
+        <v>1.6</v>
+      </c>
+      <c r="AE162">
+        <v>46.9</v>
+      </c>
+      <c r="AF162">
+        <v>25.612971300675</v>
+      </c>
     </row>
     <row r="163" spans="1:32">
       <c r="A163" t="s">
@@ -15405,6 +16257,15 @@
       <c r="AC163">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD163">
+        <v>-2</v>
+      </c>
+      <c r="AE163">
+        <v>41.7</v>
+      </c>
+      <c r="AF163">
+        <v>25.255379900969</v>
+      </c>
     </row>
     <row r="164" spans="1:32">
       <c r="A164" t="s">
@@ -15494,6 +16355,15 @@
       <c r="AC164">
         <v>52.32</v>
       </c>
+      <c r="AD164">
+        <v>-1.5</v>
+      </c>
+      <c r="AE164">
+        <v>23.9</v>
+      </c>
+      <c r="AF164">
+        <v>11.275291030131</v>
+      </c>
     </row>
     <row r="165" spans="1:32">
       <c r="A165" t="s">
@@ -15583,6 +16453,15 @@
       <c r="AC165">
         <v>43.64</v>
       </c>
+      <c r="AD165">
+        <v>0.1</v>
+      </c>
+      <c r="AE165">
+        <v>24.4</v>
+      </c>
+      <c r="AF165">
+        <v>10.664629853207</v>
+      </c>
     </row>
     <row r="166" spans="1:32">
       <c r="A166" t="s">
@@ -15672,6 +16551,15 @@
       <c r="AC166">
         <v>54.13</v>
       </c>
+      <c r="AD166">
+        <v>-0.3</v>
+      </c>
+      <c r="AE166">
+        <v>22.5</v>
+      </c>
+      <c r="AF166">
+        <v>9.920365605589801</v>
+      </c>
     </row>
     <row r="167" spans="1:32">
       <c r="A167" t="s">
@@ -15761,6 +16649,15 @@
       <c r="AC167">
         <v>71.34</v>
       </c>
+      <c r="AD167">
+        <v>-1.1</v>
+      </c>
+      <c r="AE167">
+        <v>24.1</v>
+      </c>
+      <c r="AF167">
+        <v>10.136173560578</v>
+      </c>
     </row>
     <row r="168" spans="1:32">
       <c r="A168" t="s">
@@ -15850,6 +16747,15 @@
       <c r="AC168">
         <v>64.3</v>
       </c>
+      <c r="AD168">
+        <v>-2</v>
+      </c>
+      <c r="AE168">
+        <v>26.5</v>
+      </c>
+      <c r="AF168">
+        <v>7.593454585595</v>
+      </c>
     </row>
     <row r="169" spans="1:32">
       <c r="A169" t="s">
@@ -15939,6 +16845,15 @@
       <c r="AC169">
         <v>41.96</v>
       </c>
+      <c r="AD169">
+        <v>-2</v>
+      </c>
+      <c r="AE169">
+        <v>22.3</v>
+      </c>
+      <c r="AF169">
+        <v>7.9085409370117</v>
+      </c>
     </row>
     <row r="170" spans="1:32">
       <c r="A170" t="s">
@@ -16028,6 +16943,15 @@
       <c r="AC170">
         <v>70.86</v>
       </c>
+      <c r="AD170">
+        <v>-2.5</v>
+      </c>
+      <c r="AE170">
+        <v>28.4</v>
+      </c>
+      <c r="AF170">
+        <v>6.9644346691603</v>
+      </c>
     </row>
     <row r="171" spans="1:32">
       <c r="A171" t="s">
@@ -16117,6 +17041,15 @@
       <c r="AC171">
         <v>100.93</v>
       </c>
+      <c r="AD171">
+        <v>-1.8</v>
+      </c>
+      <c r="AE171">
+        <v>29.2</v>
+      </c>
+      <c r="AF171">
+        <v>6.5711787045591</v>
+      </c>
     </row>
     <row r="172" spans="1:32">
       <c r="A172" t="s">
@@ -16206,6 +17139,15 @@
       <c r="AC172">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD172">
+        <v>0.8</v>
+      </c>
+      <c r="AE172">
+        <v>27.8</v>
+      </c>
+      <c r="AF172">
+        <v>7.2247275580282</v>
+      </c>
     </row>
     <row r="173" spans="1:32">
       <c r="A173" t="s">
@@ -16296,13 +17238,13 @@
         <v>52.32</v>
       </c>
       <c r="AD173">
-        <v>-0.279020145129201</v>
+        <v>-0.3</v>
       </c>
       <c r="AE173">
-        <v>118.195358706681</v>
+        <v>115.9</v>
       </c>
       <c r="AF173">
-        <v>26.0434729497215</v>
+        <v>25.671429569049</v>
       </c>
     </row>
     <row r="174" spans="1:32">
@@ -16394,13 +17336,13 @@
         <v>43.64</v>
       </c>
       <c r="AD174">
-        <v>-0.186511889592285</v>
+        <v>-0.2</v>
       </c>
       <c r="AE174">
-        <v>115.889445482292</v>
+        <v>106.9</v>
       </c>
       <c r="AF174">
-        <v>26.8205974834377</v>
+        <v>26.289376696224</v>
       </c>
     </row>
     <row r="175" spans="1:32">
@@ -16492,13 +17434,13 @@
         <v>54.13</v>
       </c>
       <c r="AD175">
-        <v>0.431910680659726</v>
+        <v>0.4</v>
       </c>
       <c r="AE175">
-        <v>96.136723606367</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AF175">
-        <v>27.7646551590305</v>
+        <v>27.319581557165</v>
       </c>
     </row>
     <row r="176" spans="1:32">
@@ -16590,10 +17532,13 @@
         <v>71.34</v>
       </c>
       <c r="AD176">
-        <v>1.12272670993046</v>
+        <v>1.1</v>
+      </c>
+      <c r="AE176">
+        <v>88.3</v>
       </c>
       <c r="AF176">
-        <v>28.956310897592</v>
+        <v>28.637349286885</v>
       </c>
     </row>
     <row r="177" spans="1:32">
@@ -16685,13 +17630,13 @@
         <v>64.3</v>
       </c>
       <c r="AD177">
-        <v>1.54581033725703</v>
+        <v>0.8</v>
       </c>
       <c r="AE177">
-        <v>85.7693465475141</v>
+        <v>87.7</v>
       </c>
       <c r="AF177">
-        <v>28.6261738973365</v>
+        <v>28.330537826376</v>
       </c>
     </row>
     <row r="178" spans="1:32">
@@ -16783,13 +17728,13 @@
         <v>41.96</v>
       </c>
       <c r="AD178">
-        <v>-2.83277548805149</v>
+        <v>-2.9</v>
       </c>
       <c r="AE178">
-        <v>97.86640033529891</v>
+        <v>101.3</v>
       </c>
       <c r="AF178">
-        <v>26.937333176305</v>
+        <v>27.260581190109</v>
       </c>
     </row>
     <row r="179" spans="1:32">
@@ -16880,6 +17825,15 @@
       <c r="AC179">
         <v>70.86</v>
       </c>
+      <c r="AD179">
+        <v>0.8</v>
+      </c>
+      <c r="AE179">
+        <v>86.3</v>
+      </c>
+      <c r="AF179">
+        <v>28.404488160425</v>
+      </c>
     </row>
     <row r="180" spans="1:32">
       <c r="A180" t="s">
@@ -16969,6 +17923,15 @@
       <c r="AC180">
         <v>100.93</v>
       </c>
+      <c r="AD180">
+        <v>0.3</v>
+      </c>
+      <c r="AE180">
+        <v>70.2</v>
+      </c>
+      <c r="AF180">
+        <v>27.378839663247</v>
+      </c>
     </row>
     <row r="181" spans="1:32">
       <c r="A181" t="s">
@@ -17058,6 +18021,15 @@
       <c r="AC181">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD181">
+        <v>0</v>
+      </c>
+      <c r="AE181">
+        <v>66.5</v>
+      </c>
+      <c r="AF181">
+        <v>27.710601751009</v>
+      </c>
     </row>
     <row r="182" spans="1:32">
       <c r="A182" t="s">
@@ -17130,10 +18102,13 @@
         <v>52.32</v>
       </c>
       <c r="AD182">
-        <v>6.51808860514606</v>
+        <v>5.7</v>
+      </c>
+      <c r="AE182">
+        <v>62.2</v>
       </c>
       <c r="AF182">
-        <v>34.3048945637454</v>
+        <v>34.703991702319</v>
       </c>
     </row>
     <row r="183" spans="1:32">
@@ -17207,10 +18182,13 @@
         <v>43.64</v>
       </c>
       <c r="AD183">
-        <v>1.76831309478703</v>
+        <v>3.8</v>
+      </c>
+      <c r="AE183">
+        <v>57.4</v>
       </c>
       <c r="AF183">
-        <v>28.1318859186068</v>
+        <v>29.82362319951</v>
       </c>
     </row>
     <row r="184" spans="1:32">
@@ -17284,10 +18262,13 @@
         <v>54.13</v>
       </c>
       <c r="AD184">
-        <v>1.78531382277913</v>
+        <v>1.7</v>
+      </c>
+      <c r="AE184">
+        <v>56.2</v>
       </c>
       <c r="AF184">
-        <v>26.299301993104</v>
+        <v>27.212906893936</v>
       </c>
     </row>
     <row r="185" spans="1:32">
@@ -17360,6 +18341,15 @@
       <c r="AC185">
         <v>71.34</v>
       </c>
+      <c r="AD185">
+        <v>1.8</v>
+      </c>
+      <c r="AE185">
+        <v>54.7</v>
+      </c>
+      <c r="AF185">
+        <v>36.049103011627</v>
+      </c>
     </row>
     <row r="186" spans="1:32">
       <c r="A186" t="s">
@@ -17431,6 +18421,15 @@
       <c r="AC186">
         <v>64.3</v>
       </c>
+      <c r="AD186">
+        <v>-0.7</v>
+      </c>
+      <c r="AE186">
+        <v>57.2</v>
+      </c>
+      <c r="AF186">
+        <v>37.219744429045</v>
+      </c>
     </row>
     <row r="187" spans="1:32">
       <c r="A187" t="s">
@@ -17503,10 +18502,13 @@
         <v>41.96</v>
       </c>
       <c r="AD187">
-        <v>-2.25007227885812</v>
+        <v>-3.1</v>
+      </c>
+      <c r="AE187">
+        <v>71.7</v>
       </c>
       <c r="AF187">
-        <v>28.4590147448871</v>
+        <v>34.124509721134</v>
       </c>
     </row>
     <row r="188" spans="1:32">
@@ -17573,6 +18575,15 @@
       <c r="AC188">
         <v>70.86</v>
       </c>
+      <c r="AD188">
+        <v>5.5</v>
+      </c>
+      <c r="AE188">
+        <v>73</v>
+      </c>
+      <c r="AF188">
+        <v>47.453800196364</v>
+      </c>
     </row>
     <row r="189" spans="1:32">
       <c r="A189" t="s">
@@ -17638,6 +18649,15 @@
       <c r="AC189">
         <v>100.93</v>
       </c>
+      <c r="AD189">
+        <v>-4.2</v>
+      </c>
+      <c r="AE189">
+        <v>64.5</v>
+      </c>
+      <c r="AF189">
+        <v>46.120831862921</v>
+      </c>
     </row>
     <row r="190" spans="1:32">
       <c r="A190" t="s">
@@ -17703,6 +18723,15 @@
       <c r="AC190">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD190">
+        <v>0.2</v>
+      </c>
+      <c r="AE190">
+        <v>60</v>
+      </c>
+      <c r="AF190">
+        <v>43.918553599208</v>
+      </c>
     </row>
     <row r="191" spans="1:32">
       <c r="A191" t="s">
@@ -17793,10 +18822,13 @@
         <v>52.32</v>
       </c>
       <c r="AD191">
-        <v>-1.90487703431729</v>
+        <v>-1.2</v>
+      </c>
+      <c r="AE191">
+        <v>60.6</v>
       </c>
       <c r="AF191">
-        <v>19.7095456938961</v>
+        <v>20.89533788906</v>
       </c>
     </row>
     <row r="192" spans="1:32">
@@ -17888,10 +18920,13 @@
         <v>43.64</v>
       </c>
       <c r="AD192">
-        <v>-0.457476308554688</v>
+        <v>-1.5</v>
+      </c>
+      <c r="AE192">
+        <v>60.2</v>
       </c>
       <c r="AF192">
-        <v>20.1305432828484</v>
+        <v>21.088067840973</v>
       </c>
     </row>
     <row r="193" spans="1:32">
@@ -17983,10 +19018,13 @@
         <v>54.13</v>
       </c>
       <c r="AD193">
-        <v>-0.861755832141083</v>
+        <v>-2.1</v>
+      </c>
+      <c r="AE193">
+        <v>59.9</v>
       </c>
       <c r="AF193">
-        <v>19.4078532828264</v>
+        <v>20.873035208705</v>
       </c>
     </row>
     <row r="194" spans="1:32">
@@ -18077,6 +19115,15 @@
       <c r="AC194">
         <v>71.34</v>
       </c>
+      <c r="AD194">
+        <v>-1.2</v>
+      </c>
+      <c r="AE194">
+        <v>60.3</v>
+      </c>
+      <c r="AF194">
+        <v>21.962418568542</v>
+      </c>
     </row>
     <row r="195" spans="1:32">
       <c r="A195" t="s">
@@ -18166,6 +19213,15 @@
       <c r="AC195">
         <v>64.3</v>
       </c>
+      <c r="AD195">
+        <v>-2.9</v>
+      </c>
+      <c r="AE195">
+        <v>62.1</v>
+      </c>
+      <c r="AF195">
+        <v>21.612343845576</v>
+      </c>
     </row>
     <row r="196" spans="1:32">
       <c r="A196" t="s">
@@ -18255,6 +19311,15 @@
       <c r="AC196">
         <v>41.96</v>
       </c>
+      <c r="AD196">
+        <v>-11.5</v>
+      </c>
+      <c r="AE196">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="AF196">
+        <v>21.611363074685</v>
+      </c>
     </row>
     <row r="197" spans="1:32">
       <c r="A197" t="s">
@@ -18344,6 +19409,15 @@
       <c r="AC197">
         <v>70.86</v>
       </c>
+      <c r="AD197">
+        <v>-5.4</v>
+      </c>
+      <c r="AE197">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="AF197">
+        <v>21.347254713947</v>
+      </c>
     </row>
     <row r="198" spans="1:32">
       <c r="A198" t="s">
@@ -18433,6 +19507,15 @@
       <c r="AC198">
         <v>100.93</v>
       </c>
+      <c r="AD198">
+        <v>-2.5</v>
+      </c>
+      <c r="AE198">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AF198">
+        <v>21.30979606428</v>
+      </c>
     </row>
     <row r="199" spans="1:32">
       <c r="A199" t="s">
@@ -18522,6 +19605,15 @@
       <c r="AC199">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD199">
+        <v>-3.2</v>
+      </c>
+      <c r="AE199">
+        <v>75.2</v>
+      </c>
+      <c r="AF199">
+        <v>22.075761552913</v>
+      </c>
     </row>
     <row r="200" spans="1:32">
       <c r="A200" t="s">
@@ -18612,10 +19704,13 @@
         <v>52.32</v>
       </c>
       <c r="AD200">
-        <v>-3.11885188192299</v>
+        <v>-3.9</v>
+      </c>
+      <c r="AE200">
+        <v>51</v>
       </c>
       <c r="AF200">
-        <v>18.3681968714647</v>
+        <v>22.69858412115</v>
       </c>
     </row>
     <row r="201" spans="1:32">
@@ -18707,10 +19802,13 @@
         <v>43.64</v>
       </c>
       <c r="AD201">
-        <v>-1.62118179871436</v>
+        <v>-2.7</v>
+      </c>
+      <c r="AE201">
+        <v>55</v>
       </c>
       <c r="AF201">
-        <v>19.1915888785393</v>
+        <v>23.841111867853</v>
       </c>
     </row>
     <row r="202" spans="1:32">
@@ -18802,10 +19900,13 @@
         <v>54.13</v>
       </c>
       <c r="AD202">
-        <v>-0.845266946151578</v>
+        <v>-1</v>
+      </c>
+      <c r="AE202">
+        <v>52.5</v>
       </c>
       <c r="AF202">
-        <v>19.4469058462512</v>
+        <v>23.984132267382</v>
       </c>
     </row>
     <row r="203" spans="1:32">
@@ -18897,10 +19998,13 @@
         <v>71.34</v>
       </c>
       <c r="AD203">
-        <v>-2.11318831516787</v>
+        <v>-2.1</v>
+      </c>
+      <c r="AE203">
+        <v>52.2</v>
       </c>
       <c r="AF203">
-        <v>18.3342427407296</v>
+        <v>22.831150123991</v>
       </c>
     </row>
     <row r="204" spans="1:32">
@@ -18992,13 +20096,13 @@
         <v>64.3</v>
       </c>
       <c r="AD204">
-        <v>-1.61318460276811</v>
+        <v>-2.3</v>
       </c>
       <c r="AE204">
-        <v>41.3273940627237</v>
+        <v>51.9</v>
       </c>
       <c r="AF204">
-        <v>18.5191670625259</v>
+        <v>22.997031481126</v>
       </c>
     </row>
     <row r="205" spans="1:32">
@@ -19090,13 +20194,13 @@
         <v>41.96</v>
       </c>
       <c r="AD205">
-        <v>-3.63899768692085</v>
+        <v>-4.3</v>
       </c>
       <c r="AE205">
-        <v>45.8373464150183</v>
+        <v>58.5</v>
       </c>
       <c r="AF205">
-        <v>18.6445328298003</v>
+        <v>23.492741374543</v>
       </c>
     </row>
     <row r="206" spans="1:32">
@@ -19188,13 +20292,13 @@
         <v>70.86</v>
       </c>
       <c r="AD206">
-        <v>-3.32386358587642</v>
+        <v>-3.7</v>
       </c>
       <c r="AE206">
-        <v>44.8609558065004</v>
+        <v>56.7</v>
       </c>
       <c r="AF206">
-        <v>18.3430886486889</v>
+        <v>22.937162240865</v>
       </c>
     </row>
     <row r="207" spans="1:32">
@@ -19286,13 +20390,13 @@
         <v>100.93</v>
       </c>
       <c r="AD207">
-        <v>-4.30934820805177</v>
+        <v>-4.3</v>
       </c>
       <c r="AE207">
-        <v>43.9694401566719</v>
+        <v>53.8</v>
       </c>
       <c r="AF207">
-        <v>19.2711611449441</v>
+        <v>24.186707450403</v>
       </c>
     </row>
     <row r="208" spans="1:32">
@@ -19384,13 +20488,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD208">
-        <v>-4.18573429010021</v>
+        <v>-4.3</v>
       </c>
       <c r="AE208">
-        <v>45.055380246523</v>
+        <v>52.8</v>
       </c>
       <c r="AF208">
-        <v>19.0449981034342</v>
+        <v>24.284482760082</v>
       </c>
     </row>
     <row r="209" spans="1:32">
@@ -19482,10 +20586,13 @@
         <v>52.32</v>
       </c>
       <c r="AD209">
-        <v>-0.583201904246945</v>
+        <v>-1.6</v>
+      </c>
+      <c r="AE209">
+        <v>28.9</v>
       </c>
       <c r="AF209">
-        <v>16.7280500642775</v>
+        <v>23.808754837654</v>
       </c>
     </row>
     <row r="210" spans="1:32">
@@ -19577,10 +20684,13 @@
         <v>43.64</v>
       </c>
       <c r="AD210">
-        <v>-0.586115239305093</v>
+        <v>-1.9</v>
+      </c>
+      <c r="AE210">
+        <v>30.9</v>
       </c>
       <c r="AF210">
-        <v>17.3827290426753</v>
+        <v>24.916096353104</v>
       </c>
     </row>
     <row r="211" spans="1:32">
@@ -19672,10 +20782,13 @@
         <v>54.13</v>
       </c>
       <c r="AD211">
-        <v>-0.587948185967631</v>
+        <v>-1.8</v>
+      </c>
+      <c r="AE211">
+        <v>34.7</v>
       </c>
       <c r="AF211">
-        <v>17.8258154423666</v>
+        <v>25.552242979269</v>
       </c>
     </row>
     <row r="212" spans="1:32">
@@ -19767,10 +20880,13 @@
         <v>71.34</v>
       </c>
       <c r="AD212">
-        <v>-1.93864925584338</v>
+        <v>-4.3</v>
+      </c>
+      <c r="AE212">
+        <v>39.1</v>
       </c>
       <c r="AF212">
-        <v>16.9620048772188</v>
+        <v>23.33984371015</v>
       </c>
     </row>
     <row r="213" spans="1:32">
@@ -19862,10 +20978,13 @@
         <v>64.3</v>
       </c>
       <c r="AD213">
-        <v>0.257605882352745</v>
+        <v>-1.1</v>
+      </c>
+      <c r="AE213">
+        <v>44.2</v>
       </c>
       <c r="AF213">
-        <v>18.8466464658517</v>
+        <v>26.532048087316</v>
       </c>
     </row>
     <row r="214" spans="1:32">
@@ -19957,10 +21076,13 @@
         <v>41.96</v>
       </c>
       <c r="AD214">
-        <v>-1.04830949642303</v>
+        <v>-2.6</v>
+      </c>
+      <c r="AE214">
+        <v>49.2</v>
       </c>
       <c r="AF214">
-        <v>18.4889521054397</v>
+        <v>26.351337493527</v>
       </c>
     </row>
     <row r="215" spans="1:32">
@@ -20052,10 +21174,13 @@
         <v>70.86</v>
       </c>
       <c r="AD215">
-        <v>-0.7309295555961109</v>
+        <v>-1.3</v>
+      </c>
+      <c r="AE215">
+        <v>48.4</v>
       </c>
       <c r="AF215">
-        <v>20.5214773588265</v>
+        <v>28.745150540457</v>
       </c>
     </row>
     <row r="216" spans="1:32">
@@ -20147,10 +21272,13 @@
         <v>100.93</v>
       </c>
       <c r="AD216">
-        <v>1.29650798278862</v>
+        <v>0.6</v>
+      </c>
+      <c r="AE216">
+        <v>45.9</v>
       </c>
       <c r="AF216">
-        <v>21.5053904884945</v>
+        <v>29.222204030159</v>
       </c>
     </row>
     <row r="217" spans="1:32">
@@ -20242,10 +21370,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD217">
-        <v>2.65900583968355</v>
+        <v>2.3</v>
+      </c>
+      <c r="AE217">
+        <v>42.4</v>
       </c>
       <c r="AF217">
-        <v>21.5078651205282</v>
+        <v>28.308983963576</v>
       </c>
     </row>
     <row r="218" spans="1:32">
@@ -20337,10 +21468,13 @@
         <v>52.32</v>
       </c>
       <c r="AD218">
-        <v>-4.02680842956423</v>
+        <v>-2.2</v>
+      </c>
+      <c r="AE218">
+        <v>34.1</v>
       </c>
       <c r="AF218">
-        <v>12.8142247025193</v>
+        <v>19.188490194429</v>
       </c>
     </row>
     <row r="219" spans="1:32">
@@ -20432,10 +21566,13 @@
         <v>43.64</v>
       </c>
       <c r="AD219">
-        <v>-3.35818851413364</v>
+        <v>-1.8</v>
+      </c>
+      <c r="AE219">
+        <v>34</v>
       </c>
       <c r="AF219">
-        <v>12.6851464174451</v>
+        <v>19.489345116328</v>
       </c>
     </row>
     <row r="220" spans="1:32">
@@ -20527,10 +21664,13 @@
         <v>54.13</v>
       </c>
       <c r="AD220">
-        <v>-2.8001836747991</v>
+        <v>-1.8</v>
+      </c>
+      <c r="AE220">
+        <v>34.3</v>
       </c>
       <c r="AF220">
-        <v>13.4436093989475</v>
+        <v>19.341593374501</v>
       </c>
     </row>
     <row r="221" spans="1:32">
@@ -20622,10 +21762,13 @@
         <v>71.34</v>
       </c>
       <c r="AD221">
-        <v>-2.62383159040578</v>
+        <v>-2.8</v>
+      </c>
+      <c r="AE221">
+        <v>36.3</v>
       </c>
       <c r="AF221">
-        <v>13.1867976123542</v>
+        <v>18.948854234583</v>
       </c>
     </row>
     <row r="222" spans="1:32">
@@ -20717,10 +21860,13 @@
         <v>64.3</v>
       </c>
       <c r="AD222">
-        <v>-5.58323163423213</v>
+        <v>-2.7</v>
+      </c>
+      <c r="AE222">
+        <v>42.5</v>
       </c>
       <c r="AF222">
-        <v>11.8306567007958</v>
+        <v>17.745742362238</v>
       </c>
     </row>
     <row r="223" spans="1:32">
@@ -20812,10 +21958,13 @@
         <v>41.96</v>
       </c>
       <c r="AD223">
-        <v>-8.237216127450161</v>
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="AE223">
+        <v>62.4</v>
       </c>
       <c r="AF223">
-        <v>11.5147047797974</v>
+        <v>17.340039630612</v>
       </c>
     </row>
     <row r="224" spans="1:32">
@@ -20907,10 +22056,13 @@
         <v>70.86</v>
       </c>
       <c r="AD224">
-        <v>-6.64214833219757</v>
+        <v>-6.4</v>
+      </c>
+      <c r="AE224">
+        <v>58</v>
       </c>
       <c r="AF224">
-        <v>11.1554031256111</v>
+        <v>17.30181626401</v>
       </c>
     </row>
     <row r="225" spans="1:32">
@@ -21001,6 +22153,15 @@
       <c r="AC225">
         <v>100.93</v>
       </c>
+      <c r="AD225">
+        <v>-4</v>
+      </c>
+      <c r="AE225">
+        <v>56.2</v>
+      </c>
+      <c r="AF225">
+        <v>17.366397474296</v>
+      </c>
     </row>
     <row r="226" spans="1:32">
       <c r="A226" t="s">
@@ -21090,6 +22251,15 @@
       <c r="AC226">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD226">
+        <v>-3.9</v>
+      </c>
+      <c r="AE226">
+        <v>54.4</v>
+      </c>
+      <c r="AF226">
+        <v>17.48183179073</v>
+      </c>
     </row>
     <row r="227" spans="1:32">
       <c r="A227" t="s">
@@ -21180,13 +22350,13 @@
         <v>52.32</v>
       </c>
       <c r="AD227">
-        <v>-2.40967246414886</v>
+        <v>-2</v>
       </c>
       <c r="AE227">
-        <v>22.865554469277</v>
+        <v>23.7</v>
       </c>
       <c r="AF227">
-        <v>19.679565807863</v>
+        <v>19.973412793973</v>
       </c>
     </row>
     <row r="228" spans="1:32">
@@ -21278,13 +22448,13 @@
         <v>43.64</v>
       </c>
       <c r="AD228">
-        <v>-1.76643473125096</v>
+        <v>-2.1</v>
       </c>
       <c r="AE228">
-        <v>23.7062564342415</v>
+        <v>23.9</v>
       </c>
       <c r="AF228">
-        <v>18.2765652206734</v>
+        <v>18.386249957765</v>
       </c>
     </row>
     <row r="229" spans="1:32">
@@ -21376,13 +22546,13 @@
         <v>54.13</v>
       </c>
       <c r="AD229">
-        <v>-3.41282464124008</v>
+        <v>-2.8</v>
       </c>
       <c r="AE229">
-        <v>24.7483395120072</v>
+        <v>24.8</v>
       </c>
       <c r="AF229">
-        <v>17.8234033989894</v>
+        <v>17.834306954131</v>
       </c>
     </row>
     <row r="230" spans="1:32">
@@ -21474,13 +22644,13 @@
         <v>71.34</v>
       </c>
       <c r="AD230">
-        <v>-2.10453576583639</v>
+        <v>-1.9</v>
       </c>
       <c r="AE230">
-        <v>25.7290009576063</v>
+        <v>25.7</v>
       </c>
       <c r="AF230">
-        <v>19.0379642707319</v>
+        <v>19.02416548543</v>
       </c>
     </row>
     <row r="231" spans="1:32">
@@ -21572,13 +22742,13 @@
         <v>64.3</v>
       </c>
       <c r="AD231">
-        <v>-2.13920942147812</v>
+        <v>-1.4</v>
       </c>
       <c r="AE231">
-        <v>26.5266050304096</v>
+        <v>26.5</v>
       </c>
       <c r="AF231">
-        <v>19.5290026661565</v>
+        <v>19.45212028537</v>
       </c>
     </row>
     <row r="232" spans="1:32">
@@ -21670,13 +22840,13 @@
         <v>41.96</v>
       </c>
       <c r="AD232">
-        <v>-9.665793376200011</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE232">
-        <v>34.7649150438361</v>
+        <v>34.3</v>
       </c>
       <c r="AF232">
-        <v>18.0501223065786</v>
+        <v>17.484578092332</v>
       </c>
     </row>
     <row r="233" spans="1:32">
@@ -21768,13 +22938,13 @@
         <v>70.86</v>
       </c>
       <c r="AD233">
-        <v>-3.24203590484588</v>
+        <v>-2.5</v>
       </c>
       <c r="AE233">
-        <v>35.2492265648321</v>
+        <v>35.5</v>
       </c>
       <c r="AF233">
-        <v>20.6771966687553</v>
+        <v>20.637421925374</v>
       </c>
     </row>
     <row r="234" spans="1:32">
@@ -21865,6 +23035,15 @@
       <c r="AC234">
         <v>100.93</v>
       </c>
+      <c r="AD234">
+        <v>-1.4</v>
+      </c>
+      <c r="AE234">
+        <v>33.5</v>
+      </c>
+      <c r="AF234">
+        <v>21.721254903689</v>
+      </c>
     </row>
     <row r="235" spans="1:32">
       <c r="A235" t="s">
@@ -21954,6 +23133,15 @@
       <c r="AC235">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD235">
+        <v>-2.7</v>
+      </c>
+      <c r="AE235">
+        <v>32.4</v>
+      </c>
+      <c r="AF235">
+        <v>19.31675130698</v>
+      </c>
     </row>
     <row r="236" spans="1:32">
       <c r="A236" t="s">
@@ -22019,6 +23207,15 @@
       <c r="AC236">
         <v>52.32</v>
       </c>
+      <c r="AD236">
+        <v>-2.1</v>
+      </c>
+      <c r="AE236">
+        <v>52.7</v>
+      </c>
+      <c r="AF236">
+        <v>19.397136882288</v>
+      </c>
     </row>
     <row r="237" spans="1:32">
       <c r="A237" t="s">
@@ -22084,6 +23281,15 @@
       <c r="AC237">
         <v>43.64</v>
       </c>
+      <c r="AD237">
+        <v>-1.8</v>
+      </c>
+      <c r="AE237">
+        <v>49.9</v>
+      </c>
+      <c r="AF237">
+        <v>19.132555811352</v>
+      </c>
     </row>
     <row r="238" spans="1:32">
       <c r="A238" t="s">
@@ -22149,6 +23355,15 @@
       <c r="AC238">
         <v>54.13</v>
       </c>
+      <c r="AD238">
+        <v>-1.1</v>
+      </c>
+      <c r="AE238">
+        <v>51.2</v>
+      </c>
+      <c r="AF238">
+        <v>20.817029075596</v>
+      </c>
     </row>
     <row r="239" spans="1:32">
       <c r="A239" t="s">
@@ -22220,6 +23435,15 @@
       <c r="AC239">
         <v>71.34</v>
       </c>
+      <c r="AD239">
+        <v>0</v>
+      </c>
+      <c r="AE239">
+        <v>52.4</v>
+      </c>
+      <c r="AF239">
+        <v>22.153685052568</v>
+      </c>
     </row>
     <row r="240" spans="1:32">
       <c r="A240" t="s">
@@ -22291,6 +23515,15 @@
       <c r="AC240">
         <v>64.3</v>
       </c>
+      <c r="AD240">
+        <v>1.9</v>
+      </c>
+      <c r="AE240">
+        <v>48.8</v>
+      </c>
+      <c r="AF240">
+        <v>22.967000795425</v>
+      </c>
     </row>
     <row r="241" spans="1:32">
       <c r="A241" t="s">
@@ -22362,6 +23595,15 @@
       <c r="AC241">
         <v>41.96</v>
       </c>
+      <c r="AD241">
+        <v>-0.6</v>
+      </c>
+      <c r="AE241">
+        <v>50.2</v>
+      </c>
+      <c r="AF241">
+        <v>20.811395215793</v>
+      </c>
     </row>
     <row r="242" spans="1:32">
       <c r="A242" t="s">
@@ -22427,6 +23669,15 @@
       <c r="AC242">
         <v>70.86</v>
       </c>
+      <c r="AD242">
+        <v>-0.3</v>
+      </c>
+      <c r="AE242">
+        <v>48.9</v>
+      </c>
+      <c r="AF242">
+        <v>20.9685119887</v>
+      </c>
     </row>
     <row r="243" spans="1:32">
       <c r="A243" t="s">
@@ -22492,6 +23743,15 @@
       <c r="AC243">
         <v>100.93</v>
       </c>
+      <c r="AD243">
+        <v>1.8</v>
+      </c>
+      <c r="AE243">
+        <v>16.7</v>
+      </c>
+      <c r="AF243">
+        <v>22.360481959037</v>
+      </c>
     </row>
     <row r="244" spans="1:32">
       <c r="A244" t="s">
@@ -22557,6 +23817,15 @@
       <c r="AC244">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD244">
+        <v>0.3</v>
+      </c>
+      <c r="AE244">
+        <v>16.6</v>
+      </c>
+      <c r="AF244">
+        <v>22.499683210137</v>
+      </c>
     </row>
     <row r="245" spans="1:32">
       <c r="A245" t="s">
@@ -22647,10 +23916,13 @@
         <v>52.32</v>
       </c>
       <c r="AD245">
-        <v>-0.409459349125011</v>
+        <v>-0.4</v>
+      </c>
+      <c r="AE245">
+        <v>18.6</v>
       </c>
       <c r="AF245">
-        <v>17.358483664503</v>
+        <v>17.540823887257</v>
       </c>
     </row>
     <row r="246" spans="1:32">
@@ -22742,10 +24014,13 @@
         <v>43.64</v>
       </c>
       <c r="AD246">
-        <v>0.172164834815949</v>
+        <v>-0.4</v>
+      </c>
+      <c r="AE246">
+        <v>19.4</v>
       </c>
       <c r="AF246">
-        <v>16.8648796628618</v>
+        <v>17.325488368871</v>
       </c>
     </row>
     <row r="247" spans="1:32">
@@ -22837,10 +24112,13 @@
         <v>54.13</v>
       </c>
       <c r="AD247">
-        <v>-0.435394589337389</v>
+        <v>-0.4</v>
+      </c>
+      <c r="AE247">
+        <v>19.8</v>
       </c>
       <c r="AF247">
-        <v>17.4431333716598</v>
+        <v>17.618199707326</v>
       </c>
     </row>
     <row r="248" spans="1:32">
@@ -22932,10 +24210,13 @@
         <v>71.34</v>
       </c>
       <c r="AD248">
-        <v>-1.0181187376389</v>
+        <v>-1</v>
+      </c>
+      <c r="AE248">
+        <v>22.3</v>
       </c>
       <c r="AF248">
-        <v>17.3317797902031</v>
+        <v>17.473814176292</v>
       </c>
     </row>
     <row r="249" spans="1:32">
@@ -23027,10 +24308,13 @@
         <v>64.3</v>
       </c>
       <c r="AD249">
-        <v>-2.38557658966851</v>
+        <v>-2.4</v>
+      </c>
+      <c r="AE249">
+        <v>25.8</v>
       </c>
       <c r="AF249">
-        <v>17.5461211473444</v>
+        <v>17.679066979882</v>
       </c>
     </row>
     <row r="250" spans="1:32">
@@ -23122,10 +24406,13 @@
         <v>41.96</v>
       </c>
       <c r="AD250">
-        <v>-5.76161004932235</v>
+        <v>-5.7</v>
+      </c>
+      <c r="AE250">
+        <v>36.9</v>
       </c>
       <c r="AF250">
-        <v>16.7319714533199</v>
+        <v>16.912598843579</v>
       </c>
     </row>
     <row r="251" spans="1:32">
@@ -23217,10 +24504,13 @@
         <v>70.86</v>
       </c>
       <c r="AD251">
-        <v>-3.3855465837744</v>
+        <v>-3.4</v>
+      </c>
+      <c r="AE251">
+        <v>37.5</v>
       </c>
       <c r="AF251">
-        <v>16.8868520553405</v>
+        <v>17.060822883301</v>
       </c>
     </row>
     <row r="252" spans="1:32">
@@ -23312,10 +24602,13 @@
         <v>100.93</v>
       </c>
       <c r="AD252">
-        <v>-2.63772983075328</v>
+        <v>-2.6</v>
+      </c>
+      <c r="AE252">
+        <v>40.6</v>
       </c>
       <c r="AF252">
-        <v>17.3957386518946</v>
+        <v>17.568820278653</v>
       </c>
     </row>
     <row r="253" spans="1:32">
@@ -23407,10 +24700,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD253">
-        <v>-3.81724810364245</v>
+        <v>-3.8</v>
+      </c>
+      <c r="AE253">
+        <v>41</v>
       </c>
       <c r="AF253">
-        <v>17.5729662059172</v>
+        <v>17.657296830408</v>
       </c>
     </row>
     <row r="254" spans="1:32">
@@ -23502,13 +24798,13 @@
         <v>52.32</v>
       </c>
       <c r="AD254">
-        <v>-1.30542832718732</v>
+        <v>-3.6</v>
       </c>
       <c r="AE254">
-        <v>51.2784032678648</v>
+        <v>73.5</v>
       </c>
       <c r="AF254">
-        <v>20.8150431413365</v>
+        <v>23.475442198741</v>
       </c>
     </row>
     <row r="255" spans="1:32">
@@ -23600,13 +24896,13 @@
         <v>43.64</v>
       </c>
       <c r="AD255">
-        <v>-0.18585473187881</v>
+        <v>-3.1</v>
       </c>
       <c r="AE255">
-        <v>52.0656561693955</v>
+        <v>75.2</v>
       </c>
       <c r="AF255">
-        <v>23.6888663993406</v>
+        <v>24.357427428073</v>
       </c>
     </row>
     <row r="256" spans="1:32">
@@ -23698,13 +24994,13 @@
         <v>54.13</v>
       </c>
       <c r="AD256">
-        <v>-0.5756729081453</v>
+        <v>-2.5</v>
       </c>
       <c r="AE256">
-        <v>55.248518820306</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AF256">
-        <v>25.0974253686368</v>
+        <v>25.563798925946</v>
       </c>
     </row>
     <row r="257" spans="1:32">
@@ -23796,13 +25092,13 @@
         <v>71.34</v>
       </c>
       <c r="AD257">
-        <v>-0.620271820482421</v>
+        <v>-2.7</v>
       </c>
       <c r="AE257">
-        <v>52.2142820084663</v>
+        <v>77</v>
       </c>
       <c r="AF257">
-        <v>24.9488391040262</v>
+        <v>24.89983636259</v>
       </c>
     </row>
     <row r="258" spans="1:32">
@@ -23894,13 +25190,13 @@
         <v>64.3</v>
       </c>
       <c r="AD258">
-        <v>-0.889843213494666</v>
+        <v>-3.1</v>
       </c>
       <c r="AE258">
-        <v>53.8790393562178</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AF258">
-        <v>24.1024004190298</v>
+        <v>24.710748127642</v>
       </c>
     </row>
     <row r="259" spans="1:32">
@@ -23992,13 +25288,13 @@
         <v>41.96</v>
       </c>
       <c r="AD259">
-        <v>-10.1231120985796</v>
+        <v>-8.1</v>
       </c>
       <c r="AE259">
-        <v>70.3842794023881</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AF259">
-        <v>23.5586663397695</v>
+        <v>24.560865672947</v>
       </c>
     </row>
     <row r="260" spans="1:32">
@@ -24090,13 +25386,13 @@
         <v>70.86</v>
       </c>
       <c r="AD260">
-        <v>-2.89913556178843</v>
+        <v>-5.5</v>
       </c>
       <c r="AE260">
-        <v>66.4690525886664</v>
+        <v>88</v>
       </c>
       <c r="AF260">
-        <v>28.5747339991475</v>
+        <v>25.557972301198</v>
       </c>
     </row>
     <row r="261" spans="1:32">
@@ -24188,13 +25484,13 @@
         <v>100.93</v>
       </c>
       <c r="AD261">
-        <v>-2.727005734525</v>
+        <v>-2.7</v>
       </c>
       <c r="AE261">
-        <v>74.0361190983906</v>
+        <v>83.7</v>
       </c>
       <c r="AF261">
-        <v>28.191923971419</v>
+        <v>25.976506480758</v>
       </c>
     </row>
     <row r="262" spans="1:32">
@@ -24286,13 +25582,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD262">
-        <v>-2.81757812242829</v>
+        <v>-4.7</v>
       </c>
       <c r="AE262">
-        <v>102.190173433284</v>
+        <v>85</v>
       </c>
       <c r="AF262">
-        <v>26.0511443955415</v>
+        <v>25.838070090771</v>
       </c>
     </row>
     <row r="263" spans="1:32">
@@ -24365,6 +25661,15 @@
       <c r="AC263">
         <v>52.32</v>
       </c>
+      <c r="AD263">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="AE263">
+        <v>41.2</v>
+      </c>
+      <c r="AF263">
+        <v>21.589644370223</v>
+      </c>
     </row>
     <row r="264" spans="1:32">
       <c r="A264" t="s">
@@ -24436,6 +25741,15 @@
       <c r="AC264">
         <v>43.64</v>
       </c>
+      <c r="AD264">
+        <v>-10.2</v>
+      </c>
+      <c r="AE264">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AF264">
+        <v>17.722771667668</v>
+      </c>
     </row>
     <row r="265" spans="1:32">
       <c r="A265" t="s">
@@ -24507,6 +25821,15 @@
       <c r="AC265">
         <v>54.13</v>
       </c>
+      <c r="AD265">
+        <v>-8.6</v>
+      </c>
+      <c r="AE265">
+        <v>73</v>
+      </c>
+      <c r="AF265">
+        <v>20.119897619026</v>
+      </c>
     </row>
     <row r="266" spans="1:32">
       <c r="A266" t="s">
@@ -24578,6 +25901,15 @@
       <c r="AC266">
         <v>71.34</v>
       </c>
+      <c r="AD266">
+        <v>-8.6</v>
+      </c>
+      <c r="AE266">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AF266">
+        <v>20.90257966034</v>
+      </c>
     </row>
     <row r="267" spans="1:32">
       <c r="A267" t="s">
@@ -24649,6 +25981,15 @@
       <c r="AC267">
         <v>64.3</v>
       </c>
+      <c r="AD267">
+        <v>-20.2</v>
+      </c>
+      <c r="AE267">
+        <v>84</v>
+      </c>
+      <c r="AF267">
+        <v>20.276977077242</v>
+      </c>
     </row>
     <row r="268" spans="1:32">
       <c r="A268" t="s">
@@ -24720,6 +26061,15 @@
       <c r="AC268">
         <v>41.96</v>
       </c>
+      <c r="AD268">
+        <v>-12</v>
+      </c>
+      <c r="AE268">
+        <v>146.4</v>
+      </c>
+      <c r="AF268">
+        <v>18.249217085754</v>
+      </c>
     </row>
     <row r="269" spans="1:32">
       <c r="A269" t="s">
@@ -24785,6 +26135,15 @@
       <c r="AC269">
         <v>70.86</v>
       </c>
+      <c r="AD269">
+        <v>-5.7</v>
+      </c>
+      <c r="AE269">
+        <v>115.8</v>
+      </c>
+      <c r="AF269">
+        <v>26.361081996692</v>
+      </c>
     </row>
     <row r="270" spans="1:32">
       <c r="A270" t="s">
@@ -24850,6 +26209,15 @@
       <c r="AC270">
         <v>100.93</v>
       </c>
+      <c r="AD270">
+        <v>-2.6</v>
+      </c>
+      <c r="AE270">
+        <v>111.7</v>
+      </c>
+      <c r="AF270">
+        <v>25.639811032126</v>
+      </c>
     </row>
     <row r="271" spans="1:32">
       <c r="A271" t="s">
@@ -24915,6 +26283,15 @@
       <c r="AC271">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD271">
+        <v>-1.7</v>
+      </c>
+      <c r="AE271">
+        <v>97.7</v>
+      </c>
+      <c r="AF271">
+        <v>27.209676284948</v>
+      </c>
     </row>
     <row r="272" spans="1:32">
       <c r="A272" t="s">
@@ -25005,10 +26382,13 @@
         <v>52.32</v>
       </c>
       <c r="AD272">
-        <v>-1.31681775954333</v>
+        <v>-7.4</v>
+      </c>
+      <c r="AE272">
+        <v>43.2</v>
       </c>
       <c r="AF272">
-        <v>35.8629396068095</v>
+        <v>26.761601220404</v>
       </c>
     </row>
     <row r="273" spans="1:32">
@@ -25100,10 +26480,13 @@
         <v>43.64</v>
       </c>
       <c r="AD273">
-        <v>-3.90638326389358</v>
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="AE273">
+        <v>53.3</v>
       </c>
       <c r="AF273">
-        <v>31.2390699061462</v>
+        <v>21.387847319011</v>
       </c>
     </row>
     <row r="274" spans="1:32">
@@ -25195,10 +26578,13 @@
         <v>54.13</v>
       </c>
       <c r="AD274">
-        <v>-6.40135244377081</v>
+        <v>-10.5</v>
+      </c>
+      <c r="AE274">
+        <v>57.2</v>
       </c>
       <c r="AF274">
-        <v>28.7268899879201</v>
+        <v>20.487756070265</v>
       </c>
     </row>
     <row r="275" spans="1:32">
@@ -25290,10 +26676,13 @@
         <v>71.34</v>
       </c>
       <c r="AD275">
-        <v>-3.34668595354151</v>
+        <v>-5.9</v>
+      </c>
+      <c r="AE275">
+        <v>58.1</v>
       </c>
       <c r="AF275">
-        <v>29.5653403216796</v>
+        <v>24.313605927755</v>
       </c>
     </row>
     <row r="276" spans="1:32">
@@ -25385,10 +26774,13 @@
         <v>64.3</v>
       </c>
       <c r="AD276">
-        <v>-10.6222634278285</v>
+        <v>-3.7</v>
+      </c>
+      <c r="AE276">
+        <v>62.9</v>
       </c>
       <c r="AF276">
-        <v>24.2635768758849</v>
+        <v>27.285778597629</v>
       </c>
     </row>
     <row r="277" spans="1:32">
@@ -25479,6 +26871,15 @@
       <c r="AC277">
         <v>41.96</v>
       </c>
+      <c r="AD277">
+        <v>-11.8</v>
+      </c>
+      <c r="AE277">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="AF277">
+        <v>23.274604946051</v>
+      </c>
     </row>
     <row r="278" spans="1:32">
       <c r="A278" t="s">
@@ -25568,6 +26969,15 @@
       <c r="AC278">
         <v>70.86</v>
       </c>
+      <c r="AD278">
+        <v>-8.4</v>
+      </c>
+      <c r="AE278">
+        <v>80.2</v>
+      </c>
+      <c r="AF278">
+        <v>22.996472491453</v>
+      </c>
     </row>
     <row r="279" spans="1:32">
       <c r="A279" t="s">
@@ -25657,6 +27067,15 @@
       <c r="AC279">
         <v>100.93</v>
       </c>
+      <c r="AD279">
+        <v>1</v>
+      </c>
+      <c r="AE279">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AF279">
+        <v>29.222655520854</v>
+      </c>
     </row>
     <row r="280" spans="1:32">
       <c r="A280" t="s">
@@ -25746,6 +27165,15 @@
       <c r="AC280">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD280">
+        <v>-1.2</v>
+      </c>
+      <c r="AE280">
+        <v>78.2</v>
+      </c>
+      <c r="AF280">
+        <v>31.228110301129</v>
+      </c>
     </row>
     <row r="281" spans="1:32">
       <c r="A281" t="s">
@@ -25835,11 +27263,14 @@
       <c r="AC281">
         <v>52.32</v>
       </c>
+      <c r="AD281">
+        <v>-1.9</v>
+      </c>
       <c r="AE281">
-        <v>47.2765585126953</v>
+        <v>57.8</v>
       </c>
       <c r="AF281">
-        <v>28.1236212798537</v>
+        <v>26.494087204264</v>
       </c>
     </row>
     <row r="282" spans="1:32">
@@ -25930,11 +27361,14 @@
       <c r="AC282">
         <v>43.64</v>
       </c>
+      <c r="AD282">
+        <v>-2.7</v>
+      </c>
       <c r="AE282">
-        <v>46.4584676105582</v>
+        <v>56.4</v>
       </c>
       <c r="AF282">
-        <v>33.1100434313663</v>
+        <v>26.986566883822</v>
       </c>
     </row>
     <row r="283" spans="1:32">
@@ -26025,11 +27459,14 @@
       <c r="AC283">
         <v>54.13</v>
       </c>
+      <c r="AD283">
+        <v>-2.5</v>
+      </c>
       <c r="AE283">
-        <v>45.0744196869827</v>
+        <v>55.8</v>
       </c>
       <c r="AF283">
-        <v>29.7075109246204</v>
+        <v>27.217151511328</v>
       </c>
     </row>
     <row r="284" spans="1:32">
@@ -26120,11 +27557,14 @@
       <c r="AC284">
         <v>71.34</v>
       </c>
+      <c r="AD284">
+        <v>-1.9</v>
+      </c>
       <c r="AE284">
-        <v>47.341475064134</v>
+        <v>57.9</v>
       </c>
       <c r="AF284">
-        <v>31.3533848442693</v>
+        <v>28.454606221472</v>
       </c>
     </row>
     <row r="285" spans="1:32">
@@ -26215,11 +27655,14 @@
       <c r="AC285">
         <v>64.3</v>
       </c>
+      <c r="AD285">
+        <v>-2.7</v>
+      </c>
       <c r="AE285">
-        <v>50.1314491818532</v>
+        <v>59.6</v>
       </c>
       <c r="AF285">
-        <v>30.6396644583495</v>
+        <v>27.871529158277</v>
       </c>
     </row>
     <row r="286" spans="1:32">
@@ -26310,11 +27753,14 @@
       <c r="AC286">
         <v>41.96</v>
       </c>
+      <c r="AD286">
+        <v>-4.6</v>
+      </c>
       <c r="AE286">
-        <v>60.4014181135621</v>
+        <v>68.2</v>
       </c>
       <c r="AF286">
-        <v>30.8483157882517</v>
+        <v>28.152322040966</v>
       </c>
     </row>
     <row r="287" spans="1:32">
@@ -26405,11 +27851,14 @@
       <c r="AC287">
         <v>70.86</v>
       </c>
+      <c r="AD287">
+        <v>-2.6</v>
+      </c>
       <c r="AE287">
-        <v>58.113052857752</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AF287">
-        <v>29.1017733541657</v>
+        <v>27.600825237438</v>
       </c>
     </row>
     <row r="288" spans="1:32">
@@ -26500,11 +27949,14 @@
       <c r="AC288">
         <v>100.93</v>
       </c>
+      <c r="AD288">
+        <v>-2.5</v>
+      </c>
       <c r="AE288">
-        <v>54.2372595323111</v>
+        <v>59.4</v>
       </c>
       <c r="AF288">
-        <v>29.6888696320693</v>
+        <v>27.225830232134</v>
       </c>
     </row>
     <row r="289" spans="1:32">
@@ -26595,11 +28047,14 @@
       <c r="AC289">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD289">
+        <v>-3.1</v>
+      </c>
       <c r="AE289">
-        <v>62.3670975853084</v>
+        <v>63</v>
       </c>
       <c r="AF289">
-        <v>30.8302778846325</v>
+        <v>26.96831113044</v>
       </c>
     </row>
     <row r="290" spans="1:32">
@@ -26691,10 +28146,13 @@
         <v>52.32</v>
       </c>
       <c r="AD290">
-        <v>-1.23463766068654</v>
+        <v>-2</v>
+      </c>
+      <c r="AE290">
+        <v>76</v>
       </c>
       <c r="AF290">
-        <v>24.4295333615859</v>
+        <v>25.574785015284</v>
       </c>
     </row>
     <row r="291" spans="1:32">
@@ -26786,10 +28244,13 @@
         <v>43.64</v>
       </c>
       <c r="AD291">
-        <v>2.08176037696373</v>
+        <v>0</v>
+      </c>
+      <c r="AE291">
+        <v>78.09999999999999</v>
       </c>
       <c r="AF291">
-        <v>26.9523610264621</v>
+        <v>27.091906884705</v>
       </c>
     </row>
     <row r="292" spans="1:32">
@@ -26881,10 +28342,13 @@
         <v>54.13</v>
       </c>
       <c r="AD292">
-        <v>-1.54196523776718</v>
+        <v>-1.6</v>
+      </c>
+      <c r="AE292">
+        <v>69.5</v>
       </c>
       <c r="AF292">
-        <v>25.5657309854272</v>
+        <v>25.080008609841</v>
       </c>
     </row>
     <row r="293" spans="1:32">
@@ -26975,6 +28439,15 @@
       <c r="AC293">
         <v>71.34</v>
       </c>
+      <c r="AD293">
+        <v>-1.6</v>
+      </c>
+      <c r="AE293">
+        <v>69.3</v>
+      </c>
+      <c r="AF293">
+        <v>24.642726442952</v>
+      </c>
     </row>
     <row r="294" spans="1:32">
       <c r="A294" t="s">
@@ -27064,6 +28537,15 @@
       <c r="AC294">
         <v>64.3</v>
       </c>
+      <c r="AD294">
+        <v>-3.4</v>
+      </c>
+      <c r="AE294">
+        <v>68</v>
+      </c>
+      <c r="AF294">
+        <v>25.684481352805</v>
+      </c>
     </row>
     <row r="295" spans="1:32">
       <c r="A295" t="s">
@@ -27153,6 +28635,15 @@
       <c r="AC295">
         <v>41.96</v>
       </c>
+      <c r="AD295">
+        <v>-5.9</v>
+      </c>
+      <c r="AE295">
+        <v>81.7</v>
+      </c>
+      <c r="AF295">
+        <v>26.983713475692</v>
+      </c>
     </row>
     <row r="296" spans="1:32">
       <c r="A296" t="s">
@@ -27242,6 +28733,15 @@
       <c r="AC296">
         <v>70.86</v>
       </c>
+      <c r="AD296">
+        <v>-7.2</v>
+      </c>
+      <c r="AE296">
+        <v>88.3</v>
+      </c>
+      <c r="AF296">
+        <v>29.98345285686</v>
+      </c>
     </row>
     <row r="297" spans="1:32">
       <c r="A297" t="s">
@@ -27331,6 +28831,15 @@
       <c r="AC297">
         <v>100.93</v>
       </c>
+      <c r="AD297">
+        <v>-9.4</v>
+      </c>
+      <c r="AE297">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="AF297">
+        <v>27.251410791841</v>
+      </c>
     </row>
     <row r="298" spans="1:32">
       <c r="A298" t="s">
@@ -27420,6 +28929,15 @@
       <c r="AC298">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD298">
+        <v>-12.5</v>
+      </c>
+      <c r="AE298">
+        <v>91.3</v>
+      </c>
+      <c r="AF298">
+        <v>27.233359057137</v>
+      </c>
     </row>
     <row r="299" spans="1:32">
       <c r="A299" t="s">
@@ -27509,6 +29027,15 @@
       <c r="AC299">
         <v>52.32</v>
       </c>
+      <c r="AD299">
+        <v>-8.1</v>
+      </c>
+      <c r="AE299">
+        <v>129.8</v>
+      </c>
+      <c r="AF299">
+        <v>14.884998736729</v>
+      </c>
     </row>
     <row r="300" spans="1:32">
       <c r="A300" t="s">
@@ -27598,6 +29125,15 @@
       <c r="AC300">
         <v>43.64</v>
       </c>
+      <c r="AD300">
+        <v>-8.5</v>
+      </c>
+      <c r="AE300">
+        <v>138.4</v>
+      </c>
+      <c r="AF300">
+        <v>11.223238545101</v>
+      </c>
     </row>
     <row r="301" spans="1:32">
       <c r="A301" t="s">
@@ -27687,6 +29223,15 @@
       <c r="AC301">
         <v>54.13</v>
       </c>
+      <c r="AD301">
+        <v>-13.3</v>
+      </c>
+      <c r="AE301">
+        <v>133.6</v>
+      </c>
+      <c r="AF301">
+        <v>8.493169486935599</v>
+      </c>
     </row>
     <row r="302" spans="1:32">
       <c r="A302" t="s">
@@ -27776,6 +29321,15 @@
       <c r="AC302">
         <v>71.34</v>
       </c>
+      <c r="AD302">
+        <v>-31</v>
+      </c>
+      <c r="AE302">
+        <v>175.3</v>
+      </c>
+      <c r="AF302">
+        <v>6.8844126251794</v>
+      </c>
     </row>
     <row r="303" spans="1:32">
       <c r="A303" t="s">
@@ -27865,6 +29419,15 @@
       <c r="AC303">
         <v>64.3</v>
       </c>
+      <c r="AD303">
+        <v>-10.9</v>
+      </c>
+      <c r="AE303">
+        <v>206</v>
+      </c>
+      <c r="AF303">
+        <v>10.089038802382</v>
+      </c>
     </row>
     <row r="304" spans="1:32">
       <c r="A304" t="s">
@@ -27954,8 +29517,17 @@
       <c r="AC304">
         <v>41.96</v>
       </c>
-    </row>
-    <row r="305" spans="1:29">
+      <c r="AD304">
+        <v>-6.6</v>
+      </c>
+      <c r="AE304">
+        <v>336.5</v>
+      </c>
+      <c r="AF304">
+        <v>4.5309807354375</v>
+      </c>
+    </row>
+    <row r="305" spans="1:32">
       <c r="A305" t="s">
         <v>65</v>
       </c>
@@ -28043,8 +29615,17 @@
       <c r="AC305">
         <v>70.86</v>
       </c>
-    </row>
-    <row r="306" spans="1:29">
+      <c r="AD305">
+        <v>-5.8</v>
+      </c>
+      <c r="AE305">
+        <v>254.2</v>
+      </c>
+      <c r="AF305">
+        <v>7.2837669267974</v>
+      </c>
+    </row>
+    <row r="306" spans="1:32">
       <c r="A306" t="s">
         <v>65</v>
       </c>
@@ -28132,8 +29713,17 @@
       <c r="AC306">
         <v>100.93</v>
       </c>
-    </row>
-    <row r="307" spans="1:29">
+      <c r="AD306">
+        <v>-5.3</v>
+      </c>
+      <c r="AE306">
+        <v>164.4</v>
+      </c>
+      <c r="AF306">
+        <v>9.849302608263301</v>
+      </c>
+    </row>
+    <row r="307" spans="1:32">
       <c r="A307" t="s">
         <v>65</v>
       </c>
@@ -28220,6 +29810,15 @@
       </c>
       <c r="AC307">
         <v>82.48999999999999</v>
+      </c>
+      <c r="AD307">
+        <v>-1.2</v>
+      </c>
+      <c r="AE307">
+        <v>138.5</v>
+      </c>
+      <c r="AF307">
+        <v>11.872607940332</v>
       </c>
     </row>
   </sheetData>
